--- a/public/templates/colosseum-shipping-template.xlsx
+++ b/public/templates/colosseum-shipping-template.xlsx
@@ -4954,7275 +4954,772 @@
       <c r="AS2" s="23"/>
       <c r="AT2" s="26"/>
     </row>
-    <row r="3" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="62"/>
-      <c r="AB3" s="64"/>
-      <c r="AC3" s="64"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="23"/>
-      <c r="AG3" s="23"/>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="23"/>
-      <c r="AT3" s="36"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-    </row>
-    <row r="4" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="62"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="64"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="23"/>
-      <c r="AG4" s="23"/>
-      <c r="AH4" s="23"/>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="23"/>
-      <c r="AQ4" s="23"/>
-      <c r="AR4" s="23"/>
-      <c r="AS4" s="23"/>
-      <c r="AT4" s="36"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-    </row>
-    <row r="5" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="22"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="62"/>
-      <c r="AB5" s="64"/>
-      <c r="AC5" s="64"/>
-      <c r="AD5" s="34"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="23"/>
-      <c r="AH5" s="23"/>
-      <c r="AI5" s="23"/>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="23"/>
-      <c r="AL5" s="23"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
-      <c r="AR5" s="23"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="36"/>
-    </row>
-    <row r="6" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="22"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="62"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="64"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="23"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="23"/>
-      <c r="AO6" s="23"/>
-      <c r="AP6" s="23"/>
-      <c r="AQ6" s="23"/>
-      <c r="AR6" s="23"/>
-      <c r="AS6" s="23"/>
-      <c r="AT6" s="36"/>
-    </row>
-    <row r="7" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="22"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="62"/>
-      <c r="Y7" s="62"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="62"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="23"/>
-      <c r="AI7" s="23"/>
-      <c r="AJ7" s="35"/>
-      <c r="AK7" s="23"/>
-      <c r="AL7" s="23"/>
-      <c r="AM7" s="23"/>
-      <c r="AN7" s="23"/>
-      <c r="AO7" s="23"/>
-      <c r="AP7" s="23"/>
-      <c r="AQ7" s="23"/>
-      <c r="AR7" s="23"/>
-      <c r="AS7" s="23"/>
-      <c r="AT7" s="36"/>
-    </row>
-    <row r="8" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="22"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="62"/>
-      <c r="Z8" s="62"/>
-      <c r="AA8" s="62"/>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="64"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="35"/>
-      <c r="AK8" s="23"/>
-      <c r="AL8" s="23"/>
-      <c r="AM8" s="23"/>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="23"/>
-      <c r="AQ8" s="23"/>
-      <c r="AR8" s="23"/>
-      <c r="AS8" s="23"/>
-      <c r="AT8" s="36"/>
-    </row>
-    <row r="9" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="22"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="61"/>
-      <c r="S9" s="61"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="62"/>
-      <c r="Z9" s="62"/>
-      <c r="AA9" s="62"/>
-      <c r="AB9" s="64"/>
-      <c r="AC9" s="64"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="23"/>
-      <c r="AG9" s="23"/>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="23"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="23"/>
-      <c r="AL9" s="23"/>
-      <c r="AM9" s="23"/>
-      <c r="AN9" s="23"/>
-      <c r="AO9" s="23"/>
-      <c r="AP9" s="23"/>
-      <c r="AQ9" s="23"/>
-      <c r="AR9" s="23"/>
-      <c r="AS9" s="23"/>
-      <c r="AT9" s="36"/>
-    </row>
-    <row r="10" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="22"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="61"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="64"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="62"/>
-      <c r="AA10" s="62"/>
-      <c r="AB10" s="64"/>
-      <c r="AC10" s="64"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="23"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="23"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="23"/>
-      <c r="AL10" s="23"/>
-      <c r="AM10" s="23"/>
-      <c r="AN10" s="23"/>
-      <c r="AO10" s="23"/>
-      <c r="AP10" s="23"/>
-      <c r="AQ10" s="23"/>
-      <c r="AR10" s="23"/>
-      <c r="AS10" s="23"/>
-      <c r="AT10" s="36"/>
-    </row>
-    <row r="11" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="22"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="64"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="62"/>
-      <c r="AA11" s="62"/>
-      <c r="AB11" s="64"/>
-      <c r="AC11" s="64"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="23"/>
-      <c r="AG11" s="23"/>
-      <c r="AH11" s="23"/>
-      <c r="AI11" s="23"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="23"/>
-      <c r="AL11" s="23"/>
-      <c r="AM11" s="23"/>
-      <c r="AN11" s="23"/>
-      <c r="AO11" s="23"/>
-      <c r="AP11" s="23"/>
-      <c r="AQ11" s="23"/>
-      <c r="AR11" s="23"/>
-      <c r="AS11" s="23"/>
-      <c r="AT11" s="36"/>
-    </row>
-    <row r="12" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="64"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="64"/>
-      <c r="AC12" s="64"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="23"/>
-      <c r="AG12" s="23"/>
-      <c r="AH12" s="23"/>
-      <c r="AI12" s="23"/>
-      <c r="AJ12" s="35"/>
-      <c r="AK12" s="23"/>
-      <c r="AL12" s="23"/>
-      <c r="AM12" s="23"/>
-      <c r="AN12" s="23"/>
-      <c r="AO12" s="23"/>
-      <c r="AP12" s="23"/>
-      <c r="AQ12" s="23"/>
-      <c r="AR12" s="23"/>
-      <c r="AS12" s="23"/>
-      <c r="AT12" s="36"/>
-    </row>
-    <row r="13" spans="1:52" s="22" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="22"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="64"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
-      <c r="Z13" s="62"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="64"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="23"/>
-      <c r="AG13" s="23"/>
-      <c r="AH13" s="23"/>
-      <c r="AI13" s="23"/>
-      <c r="AJ13" s="35"/>
-      <c r="AK13" s="23"/>
-      <c r="AL13" s="23"/>
-      <c r="AM13" s="23"/>
-      <c r="AN13" s="23"/>
-      <c r="AO13" s="23"/>
-      <c r="AP13" s="23"/>
-      <c r="AQ13" s="23"/>
-      <c r="AR13" s="23"/>
-      <c r="AS13" s="23"/>
-      <c r="AT13" s="36"/>
-    </row>
-    <row r="14" spans="1:52" s="22" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="22"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="61"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="64"/>
-      <c r="AC14" s="64"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="23"/>
-      <c r="AJ14" s="35"/>
-      <c r="AK14" s="23"/>
-      <c r="AL14" s="23"/>
-      <c r="AM14" s="23"/>
-      <c r="AN14" s="23"/>
-      <c r="AO14" s="23"/>
-      <c r="AP14" s="23"/>
-      <c r="AQ14" s="23"/>
-      <c r="AR14" s="23"/>
-      <c r="AS14" s="23"/>
-      <c r="AT14" s="36"/>
-    </row>
-    <row r="15" spans="1:52" s="22" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="22"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="64"/>
-      <c r="AC15" s="64"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="23"/>
-      <c r="AG15" s="23"/>
-      <c r="AH15" s="23"/>
-      <c r="AI15" s="23"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="23"/>
-      <c r="AL15" s="23"/>
-      <c r="AM15" s="23"/>
-      <c r="AN15" s="23"/>
-      <c r="AO15" s="23"/>
-      <c r="AP15" s="23"/>
-      <c r="AQ15" s="23"/>
-      <c r="AR15" s="23"/>
-      <c r="AS15" s="23"/>
-      <c r="AT15" s="36"/>
-    </row>
-    <row r="16" spans="1:52" s="22" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="40"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="42"/>
-      <c r="W16" s="64"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="64"/>
-      <c r="AC16" s="64"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
-      <c r="AH16" s="23"/>
-      <c r="AI16" s="23"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="23"/>
-      <c r="AL16" s="23"/>
-      <c r="AM16" s="23"/>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="23"/>
-      <c r="AP16" s="23"/>
-      <c r="AQ16" s="23"/>
-      <c r="AR16" s="23"/>
-      <c r="AS16" s="23"/>
-      <c r="AT16" s="36"/>
-    </row>
-    <row r="17" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="40"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="27"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="23"/>
-      <c r="AG17" s="23"/>
-      <c r="AH17" s="23"/>
-      <c r="AI17" s="23"/>
-      <c r="AJ17" s="35"/>
-      <c r="AK17" s="23"/>
-      <c r="AL17" s="23"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="23"/>
-      <c r="AR17" s="23"/>
-      <c r="AS17" s="23"/>
-      <c r="AT17" s="44"/>
-    </row>
-    <row r="18" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="40"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="27"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="32"/>
-      <c r="AB18" s="43"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="39"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="23"/>
-      <c r="AG18" s="23"/>
-      <c r="AH18" s="23"/>
-      <c r="AI18" s="23"/>
-      <c r="AJ18" s="35"/>
-      <c r="AK18" s="23"/>
-      <c r="AL18" s="23"/>
-      <c r="AM18" s="23"/>
-      <c r="AN18" s="23"/>
-      <c r="AO18" s="23"/>
-      <c r="AP18" s="23"/>
-      <c r="AQ18" s="23"/>
-      <c r="AR18" s="23"/>
-      <c r="AS18" s="23"/>
-      <c r="AT18" s="44"/>
-    </row>
-    <row r="19" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="40"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="27"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="39"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="23"/>
-      <c r="AG19" s="23"/>
-      <c r="AH19" s="23"/>
-      <c r="AI19" s="23"/>
-      <c r="AJ19" s="35"/>
-      <c r="AK19" s="23"/>
-      <c r="AL19" s="23"/>
-      <c r="AM19" s="23"/>
-      <c r="AN19" s="23"/>
-      <c r="AO19" s="23"/>
-      <c r="AP19" s="23"/>
-      <c r="AQ19" s="23"/>
-      <c r="AR19" s="23"/>
-      <c r="AS19" s="23"/>
-      <c r="AT19" s="44"/>
-    </row>
-    <row r="20" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="40"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="27"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="33"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="23"/>
-      <c r="AG20" s="23"/>
-      <c r="AH20" s="23"/>
-      <c r="AI20" s="23"/>
-      <c r="AJ20" s="35"/>
-      <c r="AK20" s="23"/>
-      <c r="AL20" s="23"/>
-      <c r="AM20" s="23"/>
-      <c r="AN20" s="23"/>
-      <c r="AO20" s="23"/>
-      <c r="AP20" s="23"/>
-      <c r="AQ20" s="23"/>
-      <c r="AR20" s="23"/>
-      <c r="AS20" s="23"/>
-      <c r="AT20" s="44"/>
-    </row>
-    <row r="21" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="40"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="27"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="43"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="39"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="23"/>
-      <c r="AG21" s="23"/>
-      <c r="AH21" s="23"/>
-      <c r="AI21" s="23"/>
-      <c r="AJ21" s="35"/>
-      <c r="AK21" s="23"/>
-      <c r="AL21" s="23"/>
-      <c r="AM21" s="23"/>
-      <c r="AN21" s="23"/>
-      <c r="AO21" s="23"/>
-      <c r="AP21" s="23"/>
-      <c r="AQ21" s="23"/>
-      <c r="AR21" s="23"/>
-      <c r="AS21" s="23"/>
-      <c r="AT21" s="44"/>
-    </row>
-    <row r="22" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="40"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="27"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="39"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="23"/>
-      <c r="AG22" s="23"/>
-      <c r="AH22" s="23"/>
-      <c r="AI22" s="23"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="23"/>
-      <c r="AL22" s="23"/>
-      <c r="AM22" s="23"/>
-      <c r="AN22" s="23"/>
-      <c r="AO22" s="23"/>
-      <c r="AP22" s="23"/>
-      <c r="AQ22" s="23"/>
-      <c r="AR22" s="23"/>
-      <c r="AS22" s="23"/>
-      <c r="AT22" s="44"/>
-    </row>
-    <row r="23" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="40"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="27"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="41"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="43"/>
-      <c r="AC23" s="33"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="23"/>
-      <c r="AG23" s="23"/>
-      <c r="AH23" s="23"/>
-      <c r="AI23" s="23"/>
-      <c r="AJ23" s="35"/>
-      <c r="AK23" s="23"/>
-      <c r="AL23" s="23"/>
-      <c r="AM23" s="23"/>
-      <c r="AN23" s="23"/>
-      <c r="AO23" s="23"/>
-      <c r="AP23" s="23"/>
-      <c r="AQ23" s="23"/>
-      <c r="AR23" s="23"/>
-      <c r="AS23" s="23"/>
-      <c r="AT23" s="44"/>
-    </row>
-    <row r="24" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="27"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="42"/>
-      <c r="V24" s="42"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="43"/>
-      <c r="AC24" s="33"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="23"/>
-      <c r="AG24" s="23"/>
-      <c r="AH24" s="23"/>
-      <c r="AI24" s="23"/>
-      <c r="AJ24" s="35"/>
-      <c r="AK24" s="23"/>
-      <c r="AL24" s="23"/>
-      <c r="AM24" s="23"/>
-      <c r="AN24" s="23"/>
-      <c r="AO24" s="23"/>
-      <c r="AP24" s="23"/>
-      <c r="AQ24" s="23"/>
-      <c r="AR24" s="23"/>
-      <c r="AS24" s="23"/>
-      <c r="AT24" s="44"/>
-    </row>
-    <row r="25" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="27"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="42"/>
-      <c r="V25" s="42"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="32"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="43"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="23"/>
-      <c r="AG25" s="23"/>
-      <c r="AH25" s="23"/>
-      <c r="AI25" s="23"/>
-      <c r="AJ25" s="35"/>
-      <c r="AK25" s="23"/>
-      <c r="AL25" s="23"/>
-      <c r="AM25" s="23"/>
-      <c r="AN25" s="23"/>
-      <c r="AO25" s="23"/>
-      <c r="AP25" s="23"/>
-      <c r="AQ25" s="23"/>
-      <c r="AR25" s="23"/>
-      <c r="AS25" s="23"/>
-      <c r="AT25" s="44"/>
-    </row>
-    <row r="26" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="27"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="39"/>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="23"/>
-      <c r="AG26" s="23"/>
-      <c r="AH26" s="23"/>
-      <c r="AI26" s="23"/>
-      <c r="AJ26" s="35"/>
-      <c r="AK26" s="23"/>
-      <c r="AL26" s="23"/>
-      <c r="AM26" s="23"/>
-      <c r="AN26" s="23"/>
-      <c r="AO26" s="23"/>
-      <c r="AP26" s="23"/>
-      <c r="AQ26" s="23"/>
-      <c r="AR26" s="23"/>
-      <c r="AS26" s="23"/>
-      <c r="AT26" s="44"/>
-    </row>
-    <row r="27" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="27"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="42"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="43"/>
-      <c r="AC27" s="33"/>
-      <c r="AD27" s="39"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="23"/>
-      <c r="AG27" s="23"/>
-      <c r="AH27" s="23"/>
-      <c r="AI27" s="23"/>
-      <c r="AJ27" s="35"/>
-      <c r="AK27" s="23"/>
-      <c r="AL27" s="23"/>
-      <c r="AM27" s="23"/>
-      <c r="AN27" s="23"/>
-      <c r="AO27" s="23"/>
-      <c r="AP27" s="23"/>
-      <c r="AQ27" s="23"/>
-      <c r="AR27" s="23"/>
-      <c r="AS27" s="23"/>
-      <c r="AT27" s="44"/>
-    </row>
-    <row r="28" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="47"/>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="23"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="23"/>
-      <c r="AG28" s="23"/>
-      <c r="AH28" s="23"/>
-      <c r="AI28" s="23"/>
-      <c r="AJ28" s="35"/>
-      <c r="AK28" s="23"/>
-      <c r="AL28" s="23"/>
-      <c r="AM28" s="23"/>
-      <c r="AN28" s="23"/>
-      <c r="AO28" s="23"/>
-      <c r="AP28" s="23"/>
-      <c r="AQ28" s="23"/>
-      <c r="AR28" s="23"/>
-      <c r="AS28" s="23"/>
-      <c r="AT28" s="44"/>
-    </row>
-    <row r="29" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-      <c r="AB29" s="47"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="23"/>
-      <c r="AE29" s="24"/>
-      <c r="AF29" s="23"/>
-      <c r="AG29" s="23"/>
-      <c r="AH29" s="23"/>
-      <c r="AI29" s="23"/>
-      <c r="AJ29" s="35"/>
-      <c r="AK29" s="23"/>
-      <c r="AL29" s="23"/>
-      <c r="AM29" s="23"/>
-      <c r="AN29" s="23"/>
-      <c r="AO29" s="23"/>
-      <c r="AP29" s="23"/>
-      <c r="AQ29" s="23"/>
-      <c r="AR29" s="23"/>
-      <c r="AS29" s="23"/>
-      <c r="AT29" s="44"/>
-    </row>
-    <row r="30" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-      <c r="AB30" s="47"/>
-      <c r="AC30" s="25"/>
-      <c r="AD30" s="23"/>
-      <c r="AE30" s="24"/>
-      <c r="AF30" s="23"/>
-      <c r="AG30" s="23"/>
-      <c r="AH30" s="23"/>
-      <c r="AI30" s="23"/>
-      <c r="AJ30" s="35"/>
-      <c r="AK30" s="23"/>
-      <c r="AL30" s="23"/>
-      <c r="AM30" s="23"/>
-      <c r="AN30" s="23"/>
-      <c r="AO30" s="23"/>
-      <c r="AP30" s="23"/>
-      <c r="AQ30" s="23"/>
-      <c r="AR30" s="23"/>
-      <c r="AS30" s="23"/>
-      <c r="AT30" s="44"/>
-    </row>
-    <row r="31" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="23"/>
-      <c r="AA31" s="23"/>
-      <c r="AB31" s="47"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="23"/>
-      <c r="AE31" s="24"/>
-      <c r="AF31" s="23"/>
-      <c r="AG31" s="23"/>
-      <c r="AH31" s="23"/>
-      <c r="AI31" s="23"/>
-      <c r="AJ31" s="35"/>
-      <c r="AK31" s="23"/>
-      <c r="AL31" s="23"/>
-      <c r="AM31" s="23"/>
-      <c r="AN31" s="23"/>
-      <c r="AO31" s="23"/>
-      <c r="AP31" s="23"/>
-      <c r="AQ31" s="23"/>
-      <c r="AR31" s="23"/>
-      <c r="AS31" s="23"/>
-      <c r="AT31" s="44"/>
-    </row>
-    <row r="32" spans="1:46" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="23"/>
-      <c r="AA32" s="23"/>
-      <c r="AB32" s="47"/>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="23"/>
-      <c r="AE32" s="24"/>
-      <c r="AF32" s="23"/>
-      <c r="AG32" s="23"/>
-      <c r="AH32" s="23"/>
-      <c r="AI32" s="23"/>
-      <c r="AJ32" s="35"/>
-      <c r="AK32" s="23"/>
-      <c r="AL32" s="23"/>
-      <c r="AM32" s="23"/>
-      <c r="AN32" s="23"/>
-      <c r="AO32" s="23"/>
-      <c r="AP32" s="23"/>
-      <c r="AQ32" s="23"/>
-      <c r="AR32" s="23"/>
-      <c r="AS32" s="23"/>
-      <c r="AT32" s="44"/>
-    </row>
-    <row r="33" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A33" s="48"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="AT33" s="52"/>
-      <c r="AY33" s="49"/>
-    </row>
-    <row r="34" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A34" s="48"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="AT34" s="52"/>
-      <c r="AY34" s="49"/>
-    </row>
-    <row r="35" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="AT35" s="52"/>
-      <c r="AY35" s="49"/>
-    </row>
-    <row r="36" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A36" s="48"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="AT36" s="52"/>
-      <c r="AY36" s="49"/>
-    </row>
-    <row r="37" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A37" s="48"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="AT37" s="52"/>
-      <c r="AY37" s="49"/>
-    </row>
-    <row r="38" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A38" s="48"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="AT38" s="52"/>
-      <c r="AY38" s="49"/>
-    </row>
-    <row r="39" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A39" s="48"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="AT39" s="52"/>
-      <c r="AY39" s="49"/>
-    </row>
-    <row r="40" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A40" s="48"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="AT40" s="52"/>
-      <c r="AY40" s="49"/>
-    </row>
-    <row r="41" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A41" s="48"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="AT41" s="52"/>
-      <c r="AY41" s="49"/>
-    </row>
-    <row r="42" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A42" s="48"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="AT42" s="52"/>
-      <c r="AY42" s="49"/>
-    </row>
-    <row r="43" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A43" s="48"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="AT43" s="52"/>
-      <c r="AY43" s="49"/>
-    </row>
-    <row r="44" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A44" s="48"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="AT44" s="52"/>
-      <c r="AY44" s="49"/>
-    </row>
-    <row r="45" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A45" s="48"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="AT45" s="52"/>
-      <c r="AY45" s="49"/>
-    </row>
-    <row r="46" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A46" s="48"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="AT46" s="52"/>
-      <c r="AY46" s="49"/>
-    </row>
-    <row r="47" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A47" s="48"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="AT47" s="52"/>
-      <c r="AY47" s="49"/>
-    </row>
-    <row r="48" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A48" s="48"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="AT48" s="52"/>
-      <c r="AY48" s="49"/>
-    </row>
-    <row r="49" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A49" s="48"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="AT49" s="52"/>
-      <c r="AY49" s="49"/>
-    </row>
-    <row r="50" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A50" s="48"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="AT50" s="52"/>
-      <c r="AY50" s="49"/>
-    </row>
-    <row r="51" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A51" s="48"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="49"/>
-      <c r="F51" s="49"/>
-      <c r="AT51" s="52"/>
-      <c r="AY51" s="49"/>
-    </row>
-    <row r="52" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A52" s="48"/>
-      <c r="B52" s="49"/>
-      <c r="C52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="AT52" s="52"/>
-      <c r="AY52" s="49"/>
-    </row>
-    <row r="53" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A53" s="48"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="AT53" s="52"/>
-      <c r="AY53" s="49"/>
-    </row>
-    <row r="54" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A54" s="48"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="F54" s="49"/>
-      <c r="AT54" s="52"/>
-      <c r="AY54" s="49"/>
-    </row>
-    <row r="55" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A55" s="48"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="AT55" s="52"/>
-      <c r="AY55" s="49"/>
-    </row>
-    <row r="56" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A56" s="48"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="AT56" s="52"/>
-      <c r="AY56" s="49"/>
-    </row>
-    <row r="57" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A57" s="48"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="AT57" s="52"/>
-      <c r="AY57" s="49"/>
-    </row>
-    <row r="58" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A58" s="48"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="AT58" s="52"/>
-      <c r="AY58" s="49"/>
-    </row>
-    <row r="59" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A59" s="48"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="AT59" s="52"/>
-      <c r="AY59" s="49"/>
-    </row>
-    <row r="60" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A60" s="48"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="AT60" s="52"/>
-      <c r="AY60" s="49"/>
-    </row>
-    <row r="61" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A61" s="48"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="AT61" s="52"/>
-      <c r="AY61" s="49"/>
-    </row>
-    <row r="62" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A62" s="48"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="AT62" s="52"/>
-      <c r="AY62" s="49"/>
-    </row>
-    <row r="63" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A63" s="48"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="AT63" s="52"/>
-      <c r="AY63" s="49"/>
-    </row>
-    <row r="64" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A64" s="48"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="AT64" s="52"/>
-      <c r="AY64" s="49"/>
-    </row>
-    <row r="65" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A65" s="48"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49"/>
-      <c r="F65" s="49"/>
-      <c r="AT65" s="52"/>
-      <c r="AY65" s="49"/>
-    </row>
-    <row r="66" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A66" s="48"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49"/>
-      <c r="F66" s="49"/>
-      <c r="AT66" s="52"/>
-      <c r="AY66" s="49"/>
-    </row>
-    <row r="67" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A67" s="48"/>
-      <c r="B67" s="49"/>
-      <c r="C67" s="49"/>
-      <c r="F67" s="49"/>
-      <c r="AT67" s="52"/>
-      <c r="AY67" s="49"/>
-    </row>
-    <row r="68" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A68" s="48"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
-      <c r="F68" s="49"/>
-      <c r="AT68" s="52"/>
-      <c r="AY68" s="49"/>
-    </row>
-    <row r="69" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A69" s="48"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="AT69" s="52"/>
-      <c r="AY69" s="49"/>
-    </row>
-    <row r="70" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A70" s="48"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="AT70" s="52"/>
-      <c r="AY70" s="49"/>
-    </row>
-    <row r="71" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A71" s="48"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="AT71" s="52"/>
-      <c r="AY71" s="49"/>
-    </row>
-    <row r="72" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A72" s="48"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="AT72" s="52"/>
-      <c r="AY72" s="49"/>
-    </row>
-    <row r="73" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A73" s="48"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
-      <c r="F73" s="49"/>
-      <c r="AT73" s="52"/>
-      <c r="AY73" s="49"/>
-    </row>
-    <row r="74" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A74" s="48"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="AT74" s="52"/>
-      <c r="AY74" s="49"/>
-    </row>
-    <row r="75" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A75" s="48"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="AT75" s="52"/>
-      <c r="AY75" s="49"/>
-    </row>
-    <row r="76" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A76" s="48"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="AT76" s="52"/>
-      <c r="AY76" s="49"/>
-    </row>
-    <row r="77" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A77" s="48"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="49"/>
-      <c r="F77" s="49"/>
-      <c r="AT77" s="52"/>
-      <c r="AY77" s="49"/>
-    </row>
-    <row r="78" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A78" s="48"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="AT78" s="52"/>
-      <c r="AY78" s="49"/>
-    </row>
-    <row r="79" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A79" s="48"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="AT79" s="52"/>
-      <c r="AY79" s="49"/>
-    </row>
-    <row r="80" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A80" s="48"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="AT80" s="52"/>
-      <c r="AY80" s="49"/>
-    </row>
-    <row r="81" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A81" s="48"/>
-      <c r="B81" s="49"/>
-      <c r="C81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="AT81" s="52"/>
-      <c r="AY81" s="49"/>
-    </row>
-    <row r="82" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A82" s="48"/>
-      <c r="B82" s="49"/>
-      <c r="C82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="AT82" s="52"/>
-      <c r="AY82" s="49"/>
-    </row>
-    <row r="83" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A83" s="48"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="49"/>
-      <c r="F83" s="49"/>
-      <c r="AT83" s="52"/>
-      <c r="AY83" s="49"/>
-    </row>
-    <row r="84" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A84" s="48"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="AT84" s="52"/>
-      <c r="AY84" s="49"/>
-    </row>
-    <row r="85" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A85" s="48"/>
-      <c r="B85" s="49"/>
-      <c r="C85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="AT85" s="52"/>
-      <c r="AY85" s="49"/>
-    </row>
-    <row r="86" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A86" s="48"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="AT86" s="52"/>
-      <c r="AY86" s="49"/>
-    </row>
-    <row r="87" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A87" s="48"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="AT87" s="52"/>
-      <c r="AY87" s="49"/>
-    </row>
-    <row r="88" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A88" s="48"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="AT88" s="52"/>
-      <c r="AY88" s="49"/>
-    </row>
-    <row r="89" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A89" s="48"/>
-      <c r="B89" s="49"/>
-      <c r="C89" s="49"/>
-      <c r="F89" s="49"/>
-      <c r="AT89" s="52"/>
-      <c r="AY89" s="49"/>
-    </row>
-    <row r="90" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A90" s="48"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="49"/>
-      <c r="F90" s="49"/>
-      <c r="AT90" s="52"/>
-      <c r="AY90" s="49"/>
-    </row>
-    <row r="91" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A91" s="48"/>
-      <c r="B91" s="49"/>
-      <c r="C91" s="49"/>
-      <c r="F91" s="49"/>
-      <c r="AT91" s="52"/>
-      <c r="AY91" s="49"/>
-    </row>
-    <row r="92" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A92" s="48"/>
-      <c r="B92" s="49"/>
-      <c r="C92" s="49"/>
-      <c r="F92" s="49"/>
-      <c r="AT92" s="52"/>
-      <c r="AY92" s="49"/>
-    </row>
-    <row r="93" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A93" s="48"/>
-      <c r="B93" s="49"/>
-      <c r="C93" s="49"/>
-      <c r="F93" s="49"/>
-      <c r="AT93" s="52"/>
-      <c r="AY93" s="49"/>
-    </row>
-    <row r="94" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A94" s="48"/>
-      <c r="B94" s="49"/>
-      <c r="C94" s="49"/>
-      <c r="F94" s="49"/>
-      <c r="AT94" s="52"/>
-      <c r="AY94" s="49"/>
-    </row>
-    <row r="95" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A95" s="48"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="49"/>
-      <c r="F95" s="49"/>
-      <c r="AT95" s="52"/>
-      <c r="AY95" s="49"/>
-    </row>
-    <row r="96" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A96" s="48"/>
-      <c r="B96" s="49"/>
-      <c r="C96" s="49"/>
-      <c r="F96" s="49"/>
-      <c r="AT96" s="52"/>
-      <c r="AY96" s="49"/>
-    </row>
-    <row r="97" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A97" s="48"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="49"/>
-      <c r="F97" s="49"/>
-      <c r="AT97" s="52"/>
-      <c r="AY97" s="49"/>
-    </row>
-    <row r="98" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A98" s="48"/>
-      <c r="B98" s="49"/>
-      <c r="C98" s="49"/>
-      <c r="F98" s="49"/>
-      <c r="AT98" s="52"/>
-      <c r="AY98" s="49"/>
-    </row>
-    <row r="99" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A99" s="48"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="49"/>
-      <c r="F99" s="49"/>
-      <c r="AT99" s="52"/>
-      <c r="AY99" s="49"/>
-    </row>
-    <row r="100" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A100" s="48"/>
-      <c r="B100" s="49"/>
-      <c r="C100" s="49"/>
-      <c r="F100" s="49"/>
-      <c r="AT100" s="52"/>
-      <c r="AY100" s="49"/>
-    </row>
-    <row r="101" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A101" s="48"/>
-      <c r="B101" s="49"/>
-      <c r="C101" s="49"/>
-      <c r="F101" s="49"/>
-      <c r="AT101" s="52"/>
-      <c r="AY101" s="49"/>
-    </row>
-    <row r="102" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A102" s="48"/>
-      <c r="B102" s="49"/>
-      <c r="C102" s="49"/>
-      <c r="F102" s="49"/>
-      <c r="AT102" s="52"/>
-      <c r="AY102" s="49"/>
-    </row>
-    <row r="103" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A103" s="48"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="49"/>
-      <c r="F103" s="49"/>
-      <c r="AT103" s="52"/>
-      <c r="AY103" s="49"/>
-    </row>
-    <row r="104" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A104" s="48"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="49"/>
-      <c r="F104" s="49"/>
-      <c r="AT104" s="52"/>
-      <c r="AY104" s="49"/>
-    </row>
-    <row r="105" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A105" s="48"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="49"/>
-      <c r="F105" s="49"/>
-      <c r="AT105" s="52"/>
-      <c r="AY105" s="49"/>
-    </row>
-    <row r="106" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A106" s="48"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="AT106" s="52"/>
-      <c r="AY106" s="49"/>
-    </row>
-    <row r="107" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A107" s="48"/>
-      <c r="B107" s="49"/>
-      <c r="C107" s="49"/>
-      <c r="F107" s="49"/>
-      <c r="AT107" s="52"/>
-      <c r="AY107" s="49"/>
-    </row>
-    <row r="108" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A108" s="48"/>
-      <c r="B108" s="49"/>
-      <c r="C108" s="49"/>
-      <c r="F108" s="49"/>
-      <c r="AT108" s="52"/>
-      <c r="AY108" s="49"/>
-    </row>
-    <row r="109" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A109" s="48"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="49"/>
-      <c r="F109" s="49"/>
-      <c r="AT109" s="52"/>
-      <c r="AY109" s="49"/>
-    </row>
-    <row r="110" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A110" s="48"/>
-      <c r="B110" s="49"/>
-      <c r="C110" s="49"/>
-      <c r="F110" s="49"/>
-      <c r="AT110" s="52"/>
-      <c r="AY110" s="49"/>
-    </row>
-    <row r="111" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A111" s="48"/>
-      <c r="B111" s="49"/>
-      <c r="C111" s="49"/>
-      <c r="F111" s="49"/>
-      <c r="AT111" s="52"/>
-      <c r="AY111" s="49"/>
-    </row>
-    <row r="112" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A112" s="48"/>
-      <c r="B112" s="49"/>
-      <c r="C112" s="49"/>
-      <c r="F112" s="49"/>
-      <c r="AT112" s="52"/>
-      <c r="AY112" s="49"/>
-    </row>
-    <row r="113" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A113" s="48"/>
-      <c r="B113" s="49"/>
-      <c r="C113" s="49"/>
-      <c r="F113" s="49"/>
-      <c r="AT113" s="52"/>
-      <c r="AY113" s="49"/>
-    </row>
-    <row r="114" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A114" s="48"/>
-      <c r="B114" s="49"/>
-      <c r="C114" s="49"/>
-      <c r="F114" s="49"/>
-      <c r="AT114" s="52"/>
-      <c r="AY114" s="49"/>
-    </row>
-    <row r="115" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A115" s="48"/>
-      <c r="B115" s="49"/>
-      <c r="C115" s="49"/>
-      <c r="F115" s="49"/>
-      <c r="AT115" s="52"/>
-      <c r="AY115" s="49"/>
-    </row>
-    <row r="116" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A116" s="48"/>
-      <c r="B116" s="49"/>
-      <c r="C116" s="49"/>
-      <c r="F116" s="49"/>
-      <c r="AT116" s="52"/>
-      <c r="AY116" s="49"/>
-    </row>
-    <row r="117" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A117" s="48"/>
-      <c r="B117" s="49"/>
-      <c r="C117" s="49"/>
-      <c r="F117" s="49"/>
-      <c r="AT117" s="52"/>
-      <c r="AY117" s="49"/>
-    </row>
-    <row r="118" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A118" s="48"/>
-      <c r="B118" s="49"/>
-      <c r="C118" s="49"/>
-      <c r="F118" s="49"/>
-      <c r="AT118" s="52"/>
-      <c r="AY118" s="49"/>
-    </row>
-    <row r="119" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A119" s="48"/>
-      <c r="B119" s="49"/>
-      <c r="C119" s="49"/>
-      <c r="F119" s="49"/>
-      <c r="AT119" s="52"/>
-      <c r="AY119" s="49"/>
-    </row>
-    <row r="120" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A120" s="48"/>
-      <c r="B120" s="49"/>
-      <c r="C120" s="49"/>
-      <c r="F120" s="49"/>
-      <c r="AT120" s="52"/>
-      <c r="AY120" s="49"/>
-    </row>
-    <row r="121" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A121" s="48"/>
-      <c r="B121" s="49"/>
-      <c r="C121" s="49"/>
-      <c r="F121" s="49"/>
-      <c r="AT121" s="52"/>
-      <c r="AY121" s="49"/>
-    </row>
-    <row r="122" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A122" s="48"/>
-      <c r="B122" s="49"/>
-      <c r="C122" s="49"/>
-      <c r="F122" s="49"/>
-      <c r="AT122" s="52"/>
-      <c r="AY122" s="49"/>
-    </row>
-    <row r="123" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A123" s="48"/>
-      <c r="B123" s="49"/>
-      <c r="C123" s="49"/>
-      <c r="F123" s="49"/>
-      <c r="AT123" s="52"/>
-      <c r="AY123" s="49"/>
-    </row>
-    <row r="124" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A124" s="48"/>
-      <c r="B124" s="49"/>
-      <c r="C124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="AT124" s="52"/>
-      <c r="AY124" s="49"/>
-    </row>
-    <row r="125" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A125" s="48"/>
-      <c r="B125" s="49"/>
-      <c r="C125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="AT125" s="52"/>
-      <c r="AY125" s="49"/>
-    </row>
-    <row r="126" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A126" s="48"/>
-      <c r="B126" s="49"/>
-      <c r="C126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="AT126" s="52"/>
-      <c r="AY126" s="49"/>
-    </row>
-    <row r="127" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A127" s="48"/>
-      <c r="B127" s="49"/>
-      <c r="C127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="AT127" s="52"/>
-      <c r="AY127" s="49"/>
-    </row>
-    <row r="128" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A128" s="48"/>
-      <c r="B128" s="49"/>
-      <c r="C128" s="49"/>
-      <c r="F128" s="49"/>
-      <c r="AT128" s="52"/>
-      <c r="AY128" s="49"/>
-    </row>
-    <row r="129" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A129" s="48"/>
-      <c r="B129" s="49"/>
-      <c r="C129" s="49"/>
-      <c r="F129" s="49"/>
-      <c r="AT129" s="52"/>
-      <c r="AY129" s="49"/>
-    </row>
-    <row r="130" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A130" s="48"/>
-      <c r="B130" s="49"/>
-      <c r="C130" s="49"/>
-      <c r="F130" s="49"/>
-      <c r="AT130" s="52"/>
-      <c r="AY130" s="49"/>
-    </row>
-    <row r="131" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A131" s="48"/>
-      <c r="B131" s="49"/>
-      <c r="C131" s="49"/>
-      <c r="F131" s="49"/>
-      <c r="AT131" s="52"/>
-      <c r="AY131" s="49"/>
-    </row>
-    <row r="132" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A132" s="48"/>
-      <c r="B132" s="49"/>
-      <c r="C132" s="49"/>
-      <c r="F132" s="49"/>
-      <c r="AT132" s="52"/>
-      <c r="AY132" s="49"/>
-    </row>
-    <row r="133" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A133" s="48"/>
-      <c r="B133" s="49"/>
-      <c r="C133" s="49"/>
-      <c r="F133" s="49"/>
-      <c r="AT133" s="52"/>
-      <c r="AY133" s="49"/>
-    </row>
-    <row r="134" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A134" s="48"/>
-      <c r="B134" s="49"/>
-      <c r="C134" s="49"/>
-      <c r="F134" s="49"/>
-      <c r="AT134" s="52"/>
-      <c r="AY134" s="49"/>
-    </row>
-    <row r="135" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A135" s="48"/>
-      <c r="B135" s="49"/>
-      <c r="C135" s="49"/>
-      <c r="F135" s="49"/>
-      <c r="AT135" s="52"/>
-      <c r="AY135" s="49"/>
-    </row>
-    <row r="136" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A136" s="48"/>
-      <c r="B136" s="49"/>
-      <c r="C136" s="49"/>
-      <c r="F136" s="49"/>
-      <c r="AT136" s="52"/>
-      <c r="AY136" s="49"/>
-    </row>
-    <row r="137" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A137" s="48"/>
-      <c r="B137" s="49"/>
-      <c r="C137" s="49"/>
-      <c r="F137" s="49"/>
-      <c r="AT137" s="52"/>
-      <c r="AY137" s="49"/>
-    </row>
-    <row r="138" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A138" s="48"/>
-      <c r="B138" s="49"/>
-      <c r="C138" s="49"/>
-      <c r="F138" s="49"/>
-      <c r="AT138" s="52"/>
-      <c r="AY138" s="49"/>
-    </row>
-    <row r="139" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A139" s="48"/>
-      <c r="B139" s="49"/>
-      <c r="C139" s="49"/>
-      <c r="F139" s="49"/>
-      <c r="AT139" s="52"/>
-      <c r="AY139" s="49"/>
-    </row>
-    <row r="140" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A140" s="48"/>
-      <c r="B140" s="49"/>
-      <c r="C140" s="49"/>
-      <c r="F140" s="49"/>
-      <c r="AT140" s="52"/>
-      <c r="AY140" s="49"/>
-    </row>
-    <row r="141" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A141" s="48"/>
-      <c r="B141" s="49"/>
-      <c r="C141" s="49"/>
-      <c r="F141" s="49"/>
-      <c r="AT141" s="52"/>
-      <c r="AY141" s="49"/>
-    </row>
-    <row r="142" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A142" s="48"/>
-      <c r="B142" s="49"/>
-      <c r="C142" s="49"/>
-      <c r="F142" s="49"/>
-      <c r="AT142" s="52"/>
-      <c r="AY142" s="49"/>
-    </row>
-    <row r="143" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A143" s="48"/>
-      <c r="B143" s="49"/>
-      <c r="C143" s="49"/>
-      <c r="F143" s="49"/>
-      <c r="AT143" s="52"/>
-      <c r="AY143" s="49"/>
-    </row>
-    <row r="144" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A144" s="48"/>
-      <c r="B144" s="49"/>
-      <c r="C144" s="49"/>
-      <c r="F144" s="49"/>
-      <c r="AT144" s="52"/>
-      <c r="AY144" s="49"/>
-    </row>
-    <row r="145" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A145" s="48"/>
-      <c r="B145" s="49"/>
-      <c r="C145" s="49"/>
-      <c r="F145" s="49"/>
-      <c r="AT145" s="52"/>
-      <c r="AY145" s="49"/>
-    </row>
-    <row r="146" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A146" s="48"/>
-      <c r="B146" s="49"/>
-      <c r="C146" s="49"/>
-      <c r="F146" s="49"/>
-      <c r="AT146" s="52"/>
-      <c r="AY146" s="49"/>
-    </row>
-    <row r="147" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A147" s="48"/>
-      <c r="B147" s="49"/>
-      <c r="C147" s="49"/>
-      <c r="F147" s="49"/>
-      <c r="AT147" s="52"/>
-      <c r="AY147" s="49"/>
-    </row>
-    <row r="148" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A148" s="48"/>
-      <c r="B148" s="49"/>
-      <c r="C148" s="49"/>
-      <c r="F148" s="49"/>
-      <c r="AT148" s="52"/>
-      <c r="AY148" s="49"/>
-    </row>
-    <row r="149" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A149" s="48"/>
-      <c r="B149" s="49"/>
-      <c r="C149" s="49"/>
-      <c r="F149" s="49"/>
-      <c r="AT149" s="52"/>
-      <c r="AY149" s="49"/>
-    </row>
-    <row r="150" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A150" s="48"/>
-      <c r="B150" s="49"/>
-      <c r="C150" s="49"/>
-      <c r="F150" s="49"/>
-      <c r="AT150" s="52"/>
-      <c r="AY150" s="49"/>
-    </row>
-    <row r="151" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A151" s="48"/>
-      <c r="B151" s="49"/>
-      <c r="C151" s="49"/>
-      <c r="F151" s="49"/>
-      <c r="AT151" s="52"/>
-      <c r="AY151" s="49"/>
-    </row>
-    <row r="152" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A152" s="48"/>
-      <c r="B152" s="49"/>
-      <c r="C152" s="49"/>
-      <c r="F152" s="49"/>
-      <c r="AT152" s="52"/>
-      <c r="AY152" s="49"/>
-    </row>
-    <row r="153" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A153" s="48"/>
-      <c r="B153" s="49"/>
-      <c r="C153" s="49"/>
-      <c r="F153" s="49"/>
-      <c r="AT153" s="52"/>
-      <c r="AY153" s="49"/>
-    </row>
-    <row r="154" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A154" s="48"/>
-      <c r="B154" s="49"/>
-      <c r="C154" s="49"/>
-      <c r="F154" s="49"/>
-      <c r="AT154" s="52"/>
-      <c r="AY154" s="49"/>
-    </row>
-    <row r="155" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A155" s="48"/>
-      <c r="B155" s="49"/>
-      <c r="C155" s="49"/>
-      <c r="F155" s="49"/>
-      <c r="AT155" s="52"/>
-      <c r="AY155" s="49"/>
-    </row>
-    <row r="156" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A156" s="48"/>
-      <c r="B156" s="49"/>
-      <c r="C156" s="49"/>
-      <c r="F156" s="49"/>
-      <c r="AT156" s="52"/>
-      <c r="AY156" s="49"/>
-    </row>
-    <row r="157" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A157" s="48"/>
-      <c r="B157" s="49"/>
-      <c r="C157" s="49"/>
-      <c r="F157" s="49"/>
-      <c r="AT157" s="52"/>
-      <c r="AY157" s="49"/>
-    </row>
-    <row r="158" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A158" s="48"/>
-      <c r="B158" s="49"/>
-      <c r="C158" s="49"/>
-      <c r="F158" s="49"/>
-      <c r="AT158" s="52"/>
-      <c r="AY158" s="49"/>
-    </row>
-    <row r="159" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A159" s="48"/>
-      <c r="B159" s="49"/>
-      <c r="C159" s="49"/>
-      <c r="F159" s="49"/>
-      <c r="AT159" s="52"/>
-      <c r="AY159" s="49"/>
-    </row>
-    <row r="160" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A160" s="48"/>
-      <c r="B160" s="49"/>
-      <c r="C160" s="49"/>
-      <c r="F160" s="49"/>
-      <c r="AT160" s="52"/>
-      <c r="AY160" s="49"/>
-    </row>
-    <row r="161" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A161" s="48"/>
-      <c r="B161" s="49"/>
-      <c r="C161" s="49"/>
-      <c r="F161" s="49"/>
-      <c r="AT161" s="52"/>
-      <c r="AY161" s="49"/>
-    </row>
-    <row r="162" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A162" s="48"/>
-      <c r="B162" s="49"/>
-      <c r="C162" s="49"/>
-      <c r="F162" s="49"/>
-      <c r="AT162" s="52"/>
-      <c r="AY162" s="49"/>
-    </row>
-    <row r="163" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A163" s="48"/>
-      <c r="B163" s="49"/>
-      <c r="C163" s="49"/>
-      <c r="F163" s="49"/>
-      <c r="AT163" s="52"/>
-      <c r="AY163" s="49"/>
-    </row>
-    <row r="164" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A164" s="48"/>
-      <c r="B164" s="49"/>
-      <c r="C164" s="49"/>
-      <c r="F164" s="49"/>
-      <c r="AT164" s="52"/>
-      <c r="AY164" s="49"/>
-    </row>
-    <row r="165" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A165" s="48"/>
-      <c r="B165" s="49"/>
-      <c r="C165" s="49"/>
-      <c r="F165" s="49"/>
-      <c r="AT165" s="52"/>
-      <c r="AY165" s="49"/>
-    </row>
-    <row r="166" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A166" s="48"/>
-      <c r="B166" s="49"/>
-      <c r="C166" s="49"/>
-      <c r="F166" s="49"/>
-      <c r="AT166" s="52"/>
-      <c r="AY166" s="49"/>
-    </row>
-    <row r="167" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A167" s="48"/>
-      <c r="B167" s="49"/>
-      <c r="C167" s="49"/>
-      <c r="F167" s="49"/>
-      <c r="AT167" s="52"/>
-      <c r="AY167" s="49"/>
-    </row>
-    <row r="168" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A168" s="48"/>
-      <c r="B168" s="49"/>
-      <c r="C168" s="49"/>
-      <c r="F168" s="49"/>
-      <c r="AT168" s="52"/>
-      <c r="AY168" s="49"/>
-    </row>
-    <row r="169" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A169" s="48"/>
-      <c r="B169" s="49"/>
-      <c r="C169" s="49"/>
-      <c r="F169" s="49"/>
-      <c r="AT169" s="52"/>
-      <c r="AY169" s="49"/>
-    </row>
-    <row r="170" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A170" s="48"/>
-      <c r="B170" s="49"/>
-      <c r="C170" s="49"/>
-      <c r="F170" s="49"/>
-      <c r="AT170" s="52"/>
-      <c r="AY170" s="49"/>
-    </row>
-    <row r="171" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A171" s="48"/>
-      <c r="B171" s="49"/>
-      <c r="C171" s="49"/>
-      <c r="F171" s="49"/>
-      <c r="AT171" s="52"/>
-      <c r="AY171" s="49"/>
-    </row>
-    <row r="172" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A172" s="48"/>
-      <c r="B172" s="49"/>
-      <c r="C172" s="49"/>
-      <c r="F172" s="49"/>
-      <c r="AT172" s="52"/>
-      <c r="AY172" s="49"/>
-    </row>
-    <row r="173" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A173" s="48"/>
-      <c r="B173" s="49"/>
-      <c r="C173" s="49"/>
-      <c r="F173" s="49"/>
-      <c r="AT173" s="52"/>
-      <c r="AY173" s="49"/>
-    </row>
-    <row r="174" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A174" s="48"/>
-      <c r="B174" s="49"/>
-      <c r="C174" s="49"/>
-      <c r="F174" s="49"/>
-      <c r="AT174" s="52"/>
-      <c r="AY174" s="49"/>
-    </row>
-    <row r="175" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A175" s="48"/>
-      <c r="B175" s="49"/>
-      <c r="C175" s="49"/>
-      <c r="F175" s="49"/>
-      <c r="AT175" s="52"/>
-      <c r="AY175" s="49"/>
-    </row>
-    <row r="176" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A176" s="48"/>
-      <c r="B176" s="49"/>
-      <c r="C176" s="49"/>
-      <c r="F176" s="49"/>
-      <c r="AT176" s="52"/>
-      <c r="AY176" s="49"/>
-    </row>
-    <row r="177" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A177" s="48"/>
-      <c r="B177" s="49"/>
-      <c r="C177" s="49"/>
-      <c r="F177" s="49"/>
-      <c r="AT177" s="52"/>
-      <c r="AY177" s="49"/>
-    </row>
-    <row r="178" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A178" s="48"/>
-      <c r="B178" s="49"/>
-      <c r="C178" s="49"/>
-      <c r="F178" s="49"/>
-      <c r="AT178" s="52"/>
-      <c r="AY178" s="49"/>
-    </row>
-    <row r="179" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A179" s="48"/>
-      <c r="B179" s="49"/>
-      <c r="C179" s="49"/>
-      <c r="F179" s="49"/>
-      <c r="AT179" s="52"/>
-      <c r="AY179" s="49"/>
-    </row>
-    <row r="180" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A180" s="48"/>
-      <c r="B180" s="49"/>
-      <c r="C180" s="49"/>
-      <c r="F180" s="49"/>
-      <c r="AT180" s="52"/>
-      <c r="AY180" s="49"/>
-    </row>
-    <row r="181" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A181" s="48"/>
-      <c r="B181" s="49"/>
-      <c r="C181" s="49"/>
-      <c r="F181" s="49"/>
-      <c r="AT181" s="52"/>
-      <c r="AY181" s="49"/>
-    </row>
-    <row r="182" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A182" s="48"/>
-      <c r="B182" s="49"/>
-      <c r="C182" s="49"/>
-      <c r="F182" s="49"/>
-      <c r="AT182" s="52"/>
-      <c r="AY182" s="49"/>
-    </row>
-    <row r="183" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A183" s="48"/>
-      <c r="B183" s="49"/>
-      <c r="C183" s="49"/>
-      <c r="F183" s="49"/>
-      <c r="AT183" s="52"/>
-      <c r="AY183" s="49"/>
-    </row>
-    <row r="184" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A184" s="48"/>
-      <c r="B184" s="49"/>
-      <c r="C184" s="49"/>
-      <c r="F184" s="49"/>
-      <c r="AT184" s="52"/>
-      <c r="AY184" s="49"/>
-    </row>
-    <row r="185" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A185" s="48"/>
-      <c r="B185" s="49"/>
-      <c r="C185" s="49"/>
-      <c r="F185" s="49"/>
-      <c r="AT185" s="52"/>
-      <c r="AY185" s="49"/>
-    </row>
-    <row r="186" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A186" s="48"/>
-      <c r="B186" s="49"/>
-      <c r="C186" s="49"/>
-      <c r="F186" s="49"/>
-      <c r="AT186" s="52"/>
-      <c r="AY186" s="49"/>
-    </row>
-    <row r="187" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A187" s="48"/>
-      <c r="B187" s="49"/>
-      <c r="C187" s="49"/>
-      <c r="F187" s="49"/>
-      <c r="AT187" s="52"/>
-      <c r="AY187" s="49"/>
-    </row>
-    <row r="188" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A188" s="48"/>
-      <c r="B188" s="49"/>
-      <c r="C188" s="49"/>
-      <c r="F188" s="49"/>
-      <c r="AT188" s="52"/>
-      <c r="AY188" s="49"/>
-    </row>
-    <row r="189" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A189" s="48"/>
-      <c r="B189" s="49"/>
-      <c r="C189" s="49"/>
-      <c r="F189" s="49"/>
-      <c r="AT189" s="52"/>
-      <c r="AY189" s="49"/>
-    </row>
-    <row r="190" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A190" s="48"/>
-      <c r="B190" s="49"/>
-      <c r="C190" s="49"/>
-      <c r="F190" s="49"/>
-      <c r="AT190" s="52"/>
-      <c r="AY190" s="49"/>
-    </row>
-    <row r="191" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A191" s="48"/>
-      <c r="B191" s="49"/>
-      <c r="C191" s="49"/>
-      <c r="F191" s="49"/>
-      <c r="AT191" s="52"/>
-      <c r="AY191" s="49"/>
-    </row>
-    <row r="192" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A192" s="48"/>
-      <c r="B192" s="49"/>
-      <c r="C192" s="49"/>
-      <c r="F192" s="49"/>
-      <c r="AT192" s="52"/>
-      <c r="AY192" s="49"/>
-    </row>
-    <row r="193" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A193" s="48"/>
-      <c r="B193" s="49"/>
-      <c r="C193" s="49"/>
-      <c r="F193" s="49"/>
-      <c r="AT193" s="52"/>
-      <c r="AY193" s="49"/>
-    </row>
-    <row r="194" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A194" s="48"/>
-      <c r="B194" s="49"/>
-      <c r="C194" s="49"/>
-      <c r="F194" s="49"/>
-      <c r="AT194" s="52"/>
-      <c r="AY194" s="49"/>
-    </row>
-    <row r="195" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A195" s="48"/>
-      <c r="B195" s="49"/>
-      <c r="C195" s="49"/>
-      <c r="F195" s="49"/>
-      <c r="AT195" s="52"/>
-      <c r="AY195" s="49"/>
-    </row>
-    <row r="196" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A196" s="48"/>
-      <c r="B196" s="49"/>
-      <c r="C196" s="49"/>
-      <c r="F196" s="49"/>
-      <c r="AT196" s="52"/>
-      <c r="AY196" s="49"/>
-    </row>
-    <row r="197" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A197" s="48"/>
-      <c r="B197" s="49"/>
-      <c r="C197" s="49"/>
-      <c r="F197" s="49"/>
-      <c r="AT197" s="52"/>
-      <c r="AY197" s="49"/>
-    </row>
-    <row r="198" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A198" s="48"/>
-      <c r="B198" s="49"/>
-      <c r="C198" s="49"/>
-      <c r="F198" s="49"/>
-      <c r="AT198" s="52"/>
-      <c r="AY198" s="49"/>
-    </row>
-    <row r="199" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A199" s="48"/>
-      <c r="B199" s="49"/>
-      <c r="C199" s="49"/>
-      <c r="F199" s="49"/>
-      <c r="AT199" s="52"/>
-      <c r="AY199" s="49"/>
-    </row>
-    <row r="200" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A200" s="48"/>
-      <c r="B200" s="49"/>
-      <c r="C200" s="49"/>
-      <c r="F200" s="49"/>
-      <c r="AT200" s="52"/>
-      <c r="AY200" s="49"/>
-    </row>
-    <row r="201" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A201" s="48"/>
-      <c r="B201" s="49"/>
-      <c r="C201" s="49"/>
-      <c r="F201" s="49"/>
-      <c r="AT201" s="52"/>
-      <c r="AY201" s="49"/>
-    </row>
-    <row r="202" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A202" s="48"/>
-      <c r="B202" s="49"/>
-      <c r="C202" s="49"/>
-      <c r="F202" s="49"/>
-      <c r="AT202" s="52"/>
-      <c r="AY202" s="49"/>
-    </row>
-    <row r="203" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A203" s="48"/>
-      <c r="B203" s="49"/>
-      <c r="C203" s="49"/>
-      <c r="F203" s="49"/>
-      <c r="AT203" s="52"/>
-      <c r="AY203" s="49"/>
-    </row>
-    <row r="204" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A204" s="48"/>
-      <c r="B204" s="49"/>
-      <c r="C204" s="49"/>
-      <c r="F204" s="49"/>
-      <c r="AT204" s="52"/>
-      <c r="AY204" s="49"/>
-    </row>
-    <row r="205" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A205" s="48"/>
-      <c r="B205" s="49"/>
-      <c r="C205" s="49"/>
-      <c r="F205" s="49"/>
-      <c r="AT205" s="52"/>
-      <c r="AY205" s="49"/>
-    </row>
-    <row r="206" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A206" s="48"/>
-      <c r="B206" s="49"/>
-      <c r="C206" s="49"/>
-      <c r="F206" s="49"/>
-      <c r="AT206" s="52"/>
-      <c r="AY206" s="49"/>
-    </row>
-    <row r="207" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A207" s="48"/>
-      <c r="B207" s="49"/>
-      <c r="C207" s="49"/>
-      <c r="F207" s="49"/>
-      <c r="AT207" s="52"/>
-      <c r="AY207" s="49"/>
-    </row>
-    <row r="208" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A208" s="48"/>
-      <c r="B208" s="49"/>
-      <c r="C208" s="49"/>
-      <c r="F208" s="49"/>
-      <c r="AT208" s="52"/>
-      <c r="AY208" s="49"/>
-    </row>
-    <row r="209" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A209" s="48"/>
-      <c r="B209" s="49"/>
-      <c r="C209" s="49"/>
-      <c r="F209" s="49"/>
-      <c r="AT209" s="52"/>
-      <c r="AY209" s="49"/>
-    </row>
-    <row r="210" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A210" s="48"/>
-      <c r="B210" s="49"/>
-      <c r="C210" s="49"/>
-      <c r="F210" s="49"/>
-      <c r="AT210" s="52"/>
-      <c r="AY210" s="49"/>
-    </row>
-    <row r="211" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A211" s="48"/>
-      <c r="B211" s="49"/>
-      <c r="C211" s="49"/>
-      <c r="F211" s="49"/>
-      <c r="AT211" s="52"/>
-      <c r="AY211" s="49"/>
-    </row>
-    <row r="212" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A212" s="48"/>
-      <c r="B212" s="49"/>
-      <c r="C212" s="49"/>
-      <c r="F212" s="49"/>
-      <c r="AT212" s="52"/>
-      <c r="AY212" s="49"/>
-    </row>
-    <row r="213" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A213" s="48"/>
-      <c r="B213" s="49"/>
-      <c r="C213" s="49"/>
-      <c r="F213" s="49"/>
-      <c r="AT213" s="52"/>
-      <c r="AY213" s="49"/>
-    </row>
-    <row r="214" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A214" s="48"/>
-      <c r="B214" s="49"/>
-      <c r="C214" s="49"/>
-      <c r="F214" s="49"/>
-      <c r="AT214" s="52"/>
-      <c r="AY214" s="49"/>
-    </row>
-    <row r="215" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A215" s="48"/>
-      <c r="B215" s="49"/>
-      <c r="C215" s="49"/>
-      <c r="F215" s="49"/>
-      <c r="AT215" s="52"/>
-      <c r="AY215" s="49"/>
-    </row>
-    <row r="216" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A216" s="48"/>
-      <c r="B216" s="49"/>
-      <c r="C216" s="49"/>
-      <c r="F216" s="49"/>
-      <c r="AT216" s="52"/>
-      <c r="AY216" s="49"/>
-    </row>
-    <row r="217" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A217" s="48"/>
-      <c r="B217" s="49"/>
-      <c r="C217" s="49"/>
-      <c r="F217" s="49"/>
-      <c r="AT217" s="52"/>
-      <c r="AY217" s="49"/>
-    </row>
-    <row r="218" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A218" s="48"/>
-      <c r="B218" s="49"/>
-      <c r="C218" s="49"/>
-      <c r="F218" s="49"/>
-      <c r="AT218" s="52"/>
-      <c r="AY218" s="49"/>
-    </row>
-    <row r="219" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A219" s="48"/>
-      <c r="B219" s="49"/>
-      <c r="C219" s="49"/>
-      <c r="F219" s="49"/>
-      <c r="AT219" s="52"/>
-      <c r="AY219" s="49"/>
-    </row>
-    <row r="220" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A220" s="48"/>
-      <c r="B220" s="49"/>
-      <c r="C220" s="49"/>
-      <c r="F220" s="49"/>
-      <c r="AT220" s="52"/>
-      <c r="AY220" s="49"/>
-    </row>
-    <row r="221" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A221" s="48"/>
-      <c r="B221" s="49"/>
-      <c r="C221" s="49"/>
-      <c r="F221" s="49"/>
-      <c r="AT221" s="52"/>
-      <c r="AY221" s="49"/>
-    </row>
-    <row r="222" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A222" s="48"/>
-      <c r="B222" s="49"/>
-      <c r="C222" s="49"/>
-      <c r="F222" s="49"/>
-      <c r="AT222" s="52"/>
-      <c r="AY222" s="49"/>
-    </row>
-    <row r="223" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A223" s="48"/>
-      <c r="B223" s="49"/>
-      <c r="C223" s="49"/>
-      <c r="F223" s="49"/>
-      <c r="AT223" s="52"/>
-      <c r="AY223" s="49"/>
-    </row>
-    <row r="224" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A224" s="48"/>
-      <c r="B224" s="49"/>
-      <c r="C224" s="49"/>
-      <c r="F224" s="49"/>
-      <c r="AT224" s="52"/>
-      <c r="AY224" s="49"/>
-    </row>
-    <row r="225" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A225" s="48"/>
-      <c r="B225" s="49"/>
-      <c r="C225" s="49"/>
-      <c r="F225" s="49"/>
-      <c r="AT225" s="52"/>
-      <c r="AY225" s="49"/>
-    </row>
-    <row r="226" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A226" s="48"/>
-      <c r="B226" s="49"/>
-      <c r="C226" s="49"/>
-      <c r="F226" s="49"/>
-      <c r="AT226" s="52"/>
-      <c r="AY226" s="49"/>
-    </row>
-    <row r="227" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A227" s="48"/>
-      <c r="B227" s="49"/>
-      <c r="C227" s="49"/>
-      <c r="F227" s="49"/>
-      <c r="AT227" s="52"/>
-      <c r="AY227" s="49"/>
-    </row>
-    <row r="228" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A228" s="48"/>
-      <c r="B228" s="49"/>
-      <c r="C228" s="49"/>
-      <c r="F228" s="49"/>
-      <c r="AT228" s="52"/>
-      <c r="AY228" s="49"/>
-    </row>
-    <row r="229" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A229" s="48"/>
-      <c r="B229" s="49"/>
-      <c r="C229" s="49"/>
-      <c r="F229" s="49"/>
-      <c r="AT229" s="52"/>
-      <c r="AY229" s="49"/>
-    </row>
-    <row r="230" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A230" s="48"/>
-      <c r="B230" s="49"/>
-      <c r="C230" s="49"/>
-      <c r="F230" s="49"/>
-      <c r="AT230" s="52"/>
-      <c r="AY230" s="49"/>
-    </row>
-    <row r="231" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A231" s="48"/>
-      <c r="B231" s="49"/>
-      <c r="C231" s="49"/>
-      <c r="F231" s="49"/>
-      <c r="AT231" s="52"/>
-      <c r="AY231" s="49"/>
-    </row>
-    <row r="232" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A232" s="48"/>
-      <c r="B232" s="49"/>
-      <c r="C232" s="49"/>
-      <c r="F232" s="49"/>
-      <c r="AT232" s="52"/>
-      <c r="AY232" s="49"/>
-    </row>
-    <row r="233" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A233" s="48"/>
-      <c r="B233" s="49"/>
-      <c r="C233" s="49"/>
-      <c r="F233" s="49"/>
-      <c r="AT233" s="52"/>
-      <c r="AY233" s="49"/>
-    </row>
-    <row r="234" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A234" s="48"/>
-      <c r="B234" s="49"/>
-      <c r="C234" s="49"/>
-      <c r="F234" s="49"/>
-      <c r="AT234" s="52"/>
-      <c r="AY234" s="49"/>
-    </row>
-    <row r="235" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A235" s="48"/>
-      <c r="B235" s="49"/>
-      <c r="C235" s="49"/>
-      <c r="F235" s="49"/>
-      <c r="AT235" s="52"/>
-      <c r="AY235" s="49"/>
-    </row>
-    <row r="236" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A236" s="48"/>
-      <c r="B236" s="49"/>
-      <c r="C236" s="49"/>
-      <c r="F236" s="49"/>
-      <c r="AT236" s="52"/>
-      <c r="AY236" s="49"/>
-    </row>
-    <row r="237" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A237" s="48"/>
-      <c r="B237" s="49"/>
-      <c r="C237" s="49"/>
-      <c r="F237" s="49"/>
-      <c r="AT237" s="52"/>
-      <c r="AY237" s="49"/>
-    </row>
-    <row r="238" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A238" s="48"/>
-      <c r="B238" s="49"/>
-      <c r="C238" s="49"/>
-      <c r="F238" s="49"/>
-      <c r="AT238" s="52"/>
-      <c r="AY238" s="49"/>
-    </row>
-    <row r="239" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A239" s="48"/>
-      <c r="B239" s="49"/>
-      <c r="C239" s="49"/>
-      <c r="F239" s="49"/>
-      <c r="AT239" s="52"/>
-      <c r="AY239" s="49"/>
-    </row>
-    <row r="240" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A240" s="48"/>
-      <c r="B240" s="49"/>
-      <c r="C240" s="49"/>
-      <c r="F240" s="49"/>
-      <c r="AT240" s="52"/>
-      <c r="AY240" s="49"/>
-    </row>
-    <row r="241" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A241" s="48"/>
-      <c r="B241" s="49"/>
-      <c r="C241" s="49"/>
-      <c r="F241" s="49"/>
-      <c r="AT241" s="52"/>
-      <c r="AY241" s="49"/>
-    </row>
-    <row r="242" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A242" s="48"/>
-      <c r="B242" s="49"/>
-      <c r="C242" s="49"/>
-      <c r="F242" s="49"/>
-      <c r="AT242" s="52"/>
-      <c r="AY242" s="49"/>
-    </row>
-    <row r="243" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A243" s="48"/>
-      <c r="B243" s="49"/>
-      <c r="C243" s="49"/>
-      <c r="F243" s="49"/>
-      <c r="AT243" s="52"/>
-      <c r="AY243" s="49"/>
-    </row>
-    <row r="244" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A244" s="48"/>
-      <c r="B244" s="49"/>
-      <c r="C244" s="49"/>
-      <c r="F244" s="49"/>
-      <c r="AT244" s="52"/>
-      <c r="AY244" s="49"/>
-    </row>
-    <row r="245" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A245" s="48"/>
-      <c r="B245" s="49"/>
-      <c r="C245" s="49"/>
-      <c r="F245" s="49"/>
-      <c r="AT245" s="52"/>
-      <c r="AY245" s="49"/>
-    </row>
-    <row r="246" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A246" s="48"/>
-      <c r="B246" s="49"/>
-      <c r="C246" s="49"/>
-      <c r="F246" s="49"/>
-      <c r="AT246" s="52"/>
-      <c r="AY246" s="49"/>
-    </row>
-    <row r="247" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A247" s="48"/>
-      <c r="B247" s="49"/>
-      <c r="C247" s="49"/>
-      <c r="F247" s="49"/>
-      <c r="AT247" s="52"/>
-      <c r="AY247" s="49"/>
-    </row>
-    <row r="248" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A248" s="48"/>
-      <c r="B248" s="49"/>
-      <c r="C248" s="49"/>
-      <c r="F248" s="49"/>
-      <c r="AT248" s="52"/>
-      <c r="AY248" s="49"/>
-    </row>
-    <row r="249" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A249" s="48"/>
-      <c r="B249" s="49"/>
-      <c r="C249" s="49"/>
-      <c r="F249" s="49"/>
-      <c r="AT249" s="52"/>
-      <c r="AY249" s="49"/>
-    </row>
-    <row r="250" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A250" s="48"/>
-      <c r="B250" s="49"/>
-      <c r="C250" s="49"/>
-      <c r="F250" s="49"/>
-      <c r="AT250" s="52"/>
-      <c r="AY250" s="49"/>
-    </row>
-    <row r="251" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A251" s="48"/>
-      <c r="B251" s="49"/>
-      <c r="C251" s="49"/>
-      <c r="F251" s="49"/>
-      <c r="AT251" s="52"/>
-      <c r="AY251" s="49"/>
-    </row>
-    <row r="252" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A252" s="48"/>
-      <c r="B252" s="49"/>
-      <c r="C252" s="49"/>
-      <c r="F252" s="49"/>
-      <c r="AT252" s="52"/>
-      <c r="AY252" s="49"/>
-    </row>
-    <row r="253" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A253" s="48"/>
-      <c r="B253" s="49"/>
-      <c r="C253" s="49"/>
-      <c r="F253" s="49"/>
-      <c r="AT253" s="52"/>
-      <c r="AY253" s="49"/>
-    </row>
-    <row r="254" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A254" s="48"/>
-      <c r="B254" s="49"/>
-      <c r="C254" s="49"/>
-      <c r="F254" s="49"/>
-      <c r="AT254" s="52"/>
-      <c r="AY254" s="49"/>
-    </row>
-    <row r="255" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A255" s="48"/>
-      <c r="B255" s="49"/>
-      <c r="C255" s="49"/>
-      <c r="F255" s="49"/>
-      <c r="AT255" s="52"/>
-      <c r="AY255" s="49"/>
-    </row>
-    <row r="256" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A256" s="48"/>
-      <c r="B256" s="49"/>
-      <c r="C256" s="49"/>
-      <c r="F256" s="49"/>
-      <c r="AT256" s="52"/>
-      <c r="AY256" s="49"/>
-    </row>
-    <row r="257" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A257" s="48"/>
-      <c r="B257" s="49"/>
-      <c r="C257" s="49"/>
-      <c r="F257" s="49"/>
-      <c r="AT257" s="52"/>
-      <c r="AY257" s="49"/>
-    </row>
-    <row r="258" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A258" s="48"/>
-      <c r="B258" s="49"/>
-      <c r="C258" s="49"/>
-      <c r="F258" s="49"/>
-      <c r="AT258" s="52"/>
-      <c r="AY258" s="49"/>
-    </row>
-    <row r="259" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A259" s="48"/>
-      <c r="B259" s="49"/>
-      <c r="C259" s="49"/>
-      <c r="F259" s="49"/>
-      <c r="AT259" s="52"/>
-      <c r="AY259" s="49"/>
-    </row>
-    <row r="260" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A260" s="48"/>
-      <c r="B260" s="49"/>
-      <c r="C260" s="49"/>
-      <c r="F260" s="49"/>
-      <c r="AT260" s="52"/>
-      <c r="AY260" s="49"/>
-    </row>
-    <row r="261" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A261" s="48"/>
-      <c r="B261" s="49"/>
-      <c r="C261" s="49"/>
-      <c r="F261" s="49"/>
-      <c r="AT261" s="52"/>
-      <c r="AY261" s="49"/>
-    </row>
-    <row r="262" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A262" s="48"/>
-      <c r="B262" s="49"/>
-      <c r="C262" s="49"/>
-      <c r="F262" s="49"/>
-      <c r="AT262" s="52"/>
-      <c r="AY262" s="49"/>
-    </row>
-    <row r="263" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A263" s="48"/>
-      <c r="B263" s="49"/>
-      <c r="C263" s="49"/>
-      <c r="F263" s="49"/>
-      <c r="AT263" s="52"/>
-      <c r="AY263" s="49"/>
-    </row>
-    <row r="264" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A264" s="48"/>
-      <c r="B264" s="49"/>
-      <c r="C264" s="49"/>
-      <c r="F264" s="49"/>
-      <c r="AT264" s="52"/>
-      <c r="AY264" s="49"/>
-    </row>
-    <row r="265" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A265" s="48"/>
-      <c r="B265" s="49"/>
-      <c r="C265" s="49"/>
-      <c r="F265" s="49"/>
-      <c r="AT265" s="52"/>
-      <c r="AY265" s="49"/>
-    </row>
-    <row r="266" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A266" s="48"/>
-      <c r="B266" s="49"/>
-      <c r="C266" s="49"/>
-      <c r="F266" s="49"/>
-      <c r="AT266" s="52"/>
-      <c r="AY266" s="49"/>
-    </row>
-    <row r="267" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A267" s="48"/>
-      <c r="B267" s="49"/>
-      <c r="C267" s="49"/>
-      <c r="F267" s="49"/>
-      <c r="AT267" s="52"/>
-      <c r="AY267" s="49"/>
-    </row>
-    <row r="268" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A268" s="48"/>
-      <c r="B268" s="49"/>
-      <c r="C268" s="49"/>
-      <c r="F268" s="49"/>
-      <c r="AT268" s="52"/>
-      <c r="AY268" s="49"/>
-    </row>
-    <row r="269" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A269" s="48"/>
-      <c r="B269" s="49"/>
-      <c r="C269" s="49"/>
-      <c r="F269" s="49"/>
-      <c r="AT269" s="52"/>
-      <c r="AY269" s="49"/>
-    </row>
-    <row r="270" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A270" s="48"/>
-      <c r="B270" s="49"/>
-      <c r="C270" s="49"/>
-      <c r="F270" s="49"/>
-      <c r="AT270" s="52"/>
-      <c r="AY270" s="49"/>
-    </row>
-    <row r="271" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A271" s="48"/>
-      <c r="B271" s="49"/>
-      <c r="C271" s="49"/>
-      <c r="F271" s="49"/>
-      <c r="AT271" s="52"/>
-      <c r="AY271" s="49"/>
-    </row>
-    <row r="272" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A272" s="48"/>
-      <c r="B272" s="49"/>
-      <c r="C272" s="49"/>
-      <c r="F272" s="49"/>
-      <c r="AT272" s="52"/>
-      <c r="AY272" s="49"/>
-    </row>
-    <row r="273" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A273" s="48"/>
-      <c r="B273" s="49"/>
-      <c r="C273" s="49"/>
-      <c r="F273" s="49"/>
-      <c r="AT273" s="52"/>
-      <c r="AY273" s="49"/>
-    </row>
-    <row r="274" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A274" s="48"/>
-      <c r="B274" s="49"/>
-      <c r="C274" s="49"/>
-      <c r="F274" s="49"/>
-      <c r="AT274" s="52"/>
-      <c r="AY274" s="49"/>
-    </row>
-    <row r="275" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A275" s="48"/>
-      <c r="B275" s="49"/>
-      <c r="C275" s="49"/>
-      <c r="F275" s="49"/>
-      <c r="AT275" s="52"/>
-      <c r="AY275" s="49"/>
-    </row>
-    <row r="276" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A276" s="48"/>
-      <c r="B276" s="49"/>
-      <c r="C276" s="49"/>
-      <c r="F276" s="49"/>
-      <c r="AT276" s="52"/>
-      <c r="AY276" s="49"/>
-    </row>
-    <row r="277" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A277" s="48"/>
-      <c r="B277" s="49"/>
-      <c r="C277" s="49"/>
-      <c r="F277" s="49"/>
-      <c r="AT277" s="52"/>
-      <c r="AY277" s="49"/>
-    </row>
-    <row r="278" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A278" s="48"/>
-      <c r="B278" s="49"/>
-      <c r="C278" s="49"/>
-      <c r="F278" s="49"/>
-      <c r="AT278" s="52"/>
-      <c r="AY278" s="49"/>
-    </row>
-    <row r="279" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A279" s="48"/>
-      <c r="B279" s="49"/>
-      <c r="C279" s="49"/>
-      <c r="F279" s="49"/>
-      <c r="AT279" s="52"/>
-      <c r="AY279" s="49"/>
-    </row>
-    <row r="280" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A280" s="48"/>
-      <c r="B280" s="49"/>
-      <c r="C280" s="49"/>
-      <c r="F280" s="49"/>
-      <c r="AT280" s="52"/>
-      <c r="AY280" s="49"/>
-    </row>
-    <row r="281" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A281" s="48"/>
-      <c r="B281" s="49"/>
-      <c r="C281" s="49"/>
-      <c r="F281" s="49"/>
-      <c r="AT281" s="52"/>
-      <c r="AY281" s="49"/>
-    </row>
-    <row r="282" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A282" s="48"/>
-      <c r="B282" s="49"/>
-      <c r="C282" s="49"/>
-      <c r="F282" s="49"/>
-      <c r="AT282" s="52"/>
-      <c r="AY282" s="49"/>
-    </row>
-    <row r="283" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A283" s="48"/>
-      <c r="B283" s="49"/>
-      <c r="C283" s="49"/>
-      <c r="F283" s="49"/>
-      <c r="AT283" s="52"/>
-      <c r="AY283" s="49"/>
-    </row>
-    <row r="284" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A284" s="48"/>
-      <c r="B284" s="49"/>
-      <c r="C284" s="49"/>
-      <c r="F284" s="49"/>
-      <c r="AT284" s="52"/>
-      <c r="AY284" s="49"/>
-    </row>
-    <row r="285" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A285" s="48"/>
-      <c r="B285" s="49"/>
-      <c r="C285" s="49"/>
-      <c r="F285" s="49"/>
-      <c r="AT285" s="52"/>
-      <c r="AY285" s="49"/>
-    </row>
-    <row r="286" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A286" s="48"/>
-      <c r="B286" s="49"/>
-      <c r="C286" s="49"/>
-      <c r="F286" s="49"/>
-      <c r="AT286" s="52"/>
-      <c r="AY286" s="49"/>
-    </row>
-    <row r="287" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A287" s="48"/>
-      <c r="B287" s="49"/>
-      <c r="C287" s="49"/>
-      <c r="F287" s="49"/>
-      <c r="AT287" s="52"/>
-      <c r="AY287" s="49"/>
-    </row>
-    <row r="288" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A288" s="48"/>
-      <c r="B288" s="49"/>
-      <c r="C288" s="49"/>
-      <c r="F288" s="49"/>
-      <c r="AT288" s="52"/>
-      <c r="AY288" s="49"/>
-    </row>
-    <row r="289" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A289" s="48"/>
-      <c r="B289" s="49"/>
-      <c r="C289" s="49"/>
-      <c r="F289" s="49"/>
-      <c r="AT289" s="52"/>
-      <c r="AY289" s="49"/>
-    </row>
-    <row r="290" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A290" s="48"/>
-      <c r="B290" s="49"/>
-      <c r="C290" s="49"/>
-      <c r="F290" s="49"/>
-      <c r="AT290" s="52"/>
-      <c r="AY290" s="49"/>
-    </row>
-    <row r="291" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A291" s="48"/>
-      <c r="B291" s="49"/>
-      <c r="C291" s="49"/>
-      <c r="F291" s="49"/>
-      <c r="AT291" s="52"/>
-      <c r="AY291" s="49"/>
-    </row>
-    <row r="292" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A292" s="48"/>
-      <c r="B292" s="49"/>
-      <c r="C292" s="49"/>
-      <c r="F292" s="49"/>
-      <c r="AT292" s="52"/>
-      <c r="AY292" s="49"/>
-    </row>
-    <row r="293" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A293" s="48"/>
-      <c r="B293" s="49"/>
-      <c r="C293" s="49"/>
-      <c r="F293" s="49"/>
-      <c r="AT293" s="52"/>
-      <c r="AY293" s="49"/>
-    </row>
-    <row r="294" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A294" s="48"/>
-      <c r="B294" s="49"/>
-      <c r="C294" s="49"/>
-      <c r="F294" s="49"/>
-      <c r="AT294" s="52"/>
-      <c r="AY294" s="49"/>
-    </row>
-    <row r="295" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A295" s="48"/>
-      <c r="B295" s="49"/>
-      <c r="C295" s="49"/>
-      <c r="F295" s="49"/>
-      <c r="AT295" s="52"/>
-      <c r="AY295" s="49"/>
-    </row>
-    <row r="296" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A296" s="48"/>
-      <c r="B296" s="49"/>
-      <c r="C296" s="49"/>
-      <c r="F296" s="49"/>
-      <c r="AT296" s="52"/>
-      <c r="AY296" s="49"/>
-    </row>
-    <row r="297" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A297" s="48"/>
-      <c r="B297" s="49"/>
-      <c r="C297" s="49"/>
-      <c r="F297" s="49"/>
-      <c r="AT297" s="52"/>
-      <c r="AY297" s="49"/>
-    </row>
-    <row r="298" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A298" s="48"/>
-      <c r="B298" s="49"/>
-      <c r="C298" s="49"/>
-      <c r="F298" s="49"/>
-      <c r="AT298" s="52"/>
-      <c r="AY298" s="49"/>
-    </row>
-    <row r="299" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A299" s="48"/>
-      <c r="B299" s="49"/>
-      <c r="C299" s="49"/>
-      <c r="F299" s="49"/>
-      <c r="AT299" s="52"/>
-      <c r="AY299" s="49"/>
-    </row>
-    <row r="300" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A300" s="48"/>
-      <c r="B300" s="49"/>
-      <c r="C300" s="49"/>
-      <c r="F300" s="49"/>
-      <c r="AT300" s="52"/>
-      <c r="AY300" s="49"/>
-    </row>
-    <row r="301" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A301" s="48"/>
-      <c r="B301" s="49"/>
-      <c r="C301" s="49"/>
-      <c r="F301" s="49"/>
-      <c r="AT301" s="52"/>
-      <c r="AY301" s="49"/>
-    </row>
-    <row r="302" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A302" s="48"/>
-      <c r="B302" s="49"/>
-      <c r="C302" s="49"/>
-      <c r="F302" s="49"/>
-      <c r="AT302" s="52"/>
-      <c r="AY302" s="49"/>
-    </row>
-    <row r="303" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A303" s="48"/>
-      <c r="B303" s="49"/>
-      <c r="C303" s="49"/>
-      <c r="F303" s="49"/>
-      <c r="AT303" s="52"/>
-      <c r="AY303" s="49"/>
-    </row>
-    <row r="304" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A304" s="48"/>
-      <c r="B304" s="49"/>
-      <c r="C304" s="49"/>
-      <c r="F304" s="49"/>
-      <c r="AT304" s="52"/>
-      <c r="AY304" s="49"/>
-    </row>
-    <row r="305" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A305" s="48"/>
-      <c r="B305" s="49"/>
-      <c r="C305" s="49"/>
-      <c r="F305" s="49"/>
-      <c r="AT305" s="52"/>
-      <c r="AY305" s="49"/>
-    </row>
-    <row r="306" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A306" s="48"/>
-      <c r="B306" s="49"/>
-      <c r="C306" s="49"/>
-      <c r="F306" s="49"/>
-      <c r="AT306" s="52"/>
-      <c r="AY306" s="49"/>
-    </row>
-    <row r="307" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A307" s="48"/>
-      <c r="B307" s="49"/>
-      <c r="C307" s="49"/>
-      <c r="F307" s="49"/>
-      <c r="AT307" s="52"/>
-      <c r="AY307" s="49"/>
-    </row>
-    <row r="308" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A308" s="48"/>
-      <c r="B308" s="49"/>
-      <c r="C308" s="49"/>
-      <c r="F308" s="49"/>
-      <c r="AT308" s="52"/>
-      <c r="AY308" s="49"/>
-    </row>
-    <row r="309" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A309" s="48"/>
-      <c r="B309" s="49"/>
-      <c r="C309" s="49"/>
-      <c r="F309" s="49"/>
-      <c r="AT309" s="52"/>
-      <c r="AY309" s="49"/>
-    </row>
-    <row r="310" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A310" s="48"/>
-      <c r="B310" s="49"/>
-      <c r="C310" s="49"/>
-      <c r="F310" s="49"/>
-      <c r="AT310" s="52"/>
-      <c r="AY310" s="49"/>
-    </row>
-    <row r="311" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A311" s="48"/>
-      <c r="B311" s="49"/>
-      <c r="C311" s="49"/>
-      <c r="F311" s="49"/>
-      <c r="AT311" s="52"/>
-      <c r="AY311" s="49"/>
-    </row>
-    <row r="312" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A312" s="48"/>
-      <c r="B312" s="49"/>
-      <c r="C312" s="49"/>
-      <c r="F312" s="49"/>
-      <c r="AT312" s="52"/>
-      <c r="AY312" s="49"/>
-    </row>
-    <row r="313" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A313" s="48"/>
-      <c r="B313" s="49"/>
-      <c r="C313" s="49"/>
-      <c r="F313" s="49"/>
-      <c r="AT313" s="52"/>
-      <c r="AY313" s="49"/>
-    </row>
-    <row r="314" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A314" s="48"/>
-      <c r="B314" s="49"/>
-      <c r="C314" s="49"/>
-      <c r="F314" s="49"/>
-      <c r="AT314" s="52"/>
-      <c r="AY314" s="49"/>
-    </row>
-    <row r="315" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A315" s="48"/>
-      <c r="B315" s="49"/>
-      <c r="C315" s="49"/>
-      <c r="F315" s="49"/>
-      <c r="AT315" s="52"/>
-      <c r="AY315" s="49"/>
-    </row>
-    <row r="316" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A316" s="48"/>
-      <c r="B316" s="49"/>
-      <c r="C316" s="49"/>
-      <c r="F316" s="49"/>
-      <c r="AT316" s="52"/>
-      <c r="AY316" s="49"/>
-    </row>
-    <row r="317" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A317" s="48"/>
-      <c r="B317" s="49"/>
-      <c r="C317" s="49"/>
-      <c r="F317" s="49"/>
-      <c r="AT317" s="52"/>
-      <c r="AY317" s="49"/>
-    </row>
-    <row r="318" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A318" s="48"/>
-      <c r="B318" s="49"/>
-      <c r="C318" s="49"/>
-      <c r="F318" s="49"/>
-      <c r="AT318" s="52"/>
-      <c r="AY318" s="49"/>
-    </row>
-    <row r="319" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A319" s="48"/>
-      <c r="B319" s="49"/>
-      <c r="C319" s="49"/>
-      <c r="F319" s="49"/>
-      <c r="AT319" s="52"/>
-      <c r="AY319" s="49"/>
-    </row>
-    <row r="320" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A320" s="48"/>
-      <c r="B320" s="49"/>
-      <c r="C320" s="49"/>
-      <c r="F320" s="49"/>
-      <c r="AT320" s="52"/>
-      <c r="AY320" s="49"/>
-    </row>
-    <row r="321" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A321" s="48"/>
-      <c r="B321" s="49"/>
-      <c r="C321" s="49"/>
-      <c r="F321" s="49"/>
-      <c r="AT321" s="52"/>
-      <c r="AY321" s="49"/>
-    </row>
-    <row r="322" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A322" s="48"/>
-      <c r="B322" s="49"/>
-      <c r="C322" s="49"/>
-      <c r="F322" s="49"/>
-      <c r="AT322" s="52"/>
-      <c r="AY322" s="49"/>
-    </row>
-    <row r="323" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A323" s="48"/>
-      <c r="B323" s="49"/>
-      <c r="C323" s="49"/>
-      <c r="F323" s="49"/>
-      <c r="AT323" s="52"/>
-      <c r="AY323" s="49"/>
-    </row>
-    <row r="324" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A324" s="48"/>
-      <c r="B324" s="49"/>
-      <c r="C324" s="49"/>
-      <c r="F324" s="49"/>
-      <c r="AT324" s="52"/>
-      <c r="AY324" s="49"/>
-    </row>
-    <row r="325" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A325" s="48"/>
-      <c r="B325" s="49"/>
-      <c r="C325" s="49"/>
-      <c r="F325" s="49"/>
-      <c r="AT325" s="52"/>
-      <c r="AY325" s="49"/>
-    </row>
-    <row r="326" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A326" s="48"/>
-      <c r="B326" s="49"/>
-      <c r="C326" s="49"/>
-      <c r="F326" s="49"/>
-      <c r="AT326" s="52"/>
-      <c r="AY326" s="49"/>
-    </row>
-    <row r="327" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A327" s="48"/>
-      <c r="B327" s="49"/>
-      <c r="C327" s="49"/>
-      <c r="F327" s="49"/>
-      <c r="AT327" s="52"/>
-      <c r="AY327" s="49"/>
-    </row>
-    <row r="328" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A328" s="48"/>
-      <c r="B328" s="49"/>
-      <c r="C328" s="49"/>
-      <c r="F328" s="49"/>
-      <c r="AT328" s="52"/>
-      <c r="AY328" s="49"/>
-    </row>
-    <row r="329" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A329" s="48"/>
-      <c r="B329" s="49"/>
-      <c r="C329" s="49"/>
-      <c r="F329" s="49"/>
-      <c r="AT329" s="52"/>
-      <c r="AY329" s="49"/>
-    </row>
-    <row r="330" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A330" s="48"/>
-      <c r="B330" s="49"/>
-      <c r="C330" s="49"/>
-      <c r="F330" s="49"/>
-      <c r="AT330" s="52"/>
-      <c r="AY330" s="49"/>
-    </row>
-    <row r="331" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A331" s="48"/>
-      <c r="B331" s="49"/>
-      <c r="C331" s="49"/>
-      <c r="F331" s="49"/>
-      <c r="AT331" s="52"/>
-      <c r="AY331" s="49"/>
-    </row>
-    <row r="332" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A332" s="48"/>
-      <c r="B332" s="49"/>
-      <c r="C332" s="49"/>
-      <c r="F332" s="49"/>
-      <c r="AT332" s="52"/>
-      <c r="AY332" s="49"/>
-    </row>
-    <row r="333" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A333" s="48"/>
-      <c r="B333" s="49"/>
-      <c r="C333" s="49"/>
-      <c r="F333" s="49"/>
-      <c r="AT333" s="52"/>
-      <c r="AY333" s="49"/>
-    </row>
-    <row r="334" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A334" s="48"/>
-      <c r="B334" s="49"/>
-      <c r="C334" s="49"/>
-      <c r="F334" s="49"/>
-      <c r="AT334" s="52"/>
-      <c r="AY334" s="49"/>
-    </row>
-    <row r="335" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A335" s="48"/>
-      <c r="B335" s="49"/>
-      <c r="C335" s="49"/>
-      <c r="F335" s="49"/>
-      <c r="AT335" s="52"/>
-      <c r="AY335" s="49"/>
-    </row>
-    <row r="336" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A336" s="48"/>
-      <c r="B336" s="49"/>
-      <c r="C336" s="49"/>
-      <c r="F336" s="49"/>
-      <c r="AT336" s="52"/>
-      <c r="AY336" s="49"/>
-    </row>
-    <row r="337" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A337" s="48"/>
-      <c r="B337" s="49"/>
-      <c r="C337" s="49"/>
-      <c r="F337" s="49"/>
-      <c r="AT337" s="52"/>
-      <c r="AY337" s="49"/>
-    </row>
-    <row r="338" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A338" s="48"/>
-      <c r="B338" s="49"/>
-      <c r="C338" s="49"/>
-      <c r="F338" s="49"/>
-      <c r="AT338" s="52"/>
-      <c r="AY338" s="49"/>
-    </row>
-    <row r="339" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A339" s="48"/>
-      <c r="B339" s="49"/>
-      <c r="C339" s="49"/>
-      <c r="F339" s="49"/>
-      <c r="AT339" s="52"/>
-      <c r="AY339" s="49"/>
-    </row>
-    <row r="340" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A340" s="48"/>
-      <c r="B340" s="49"/>
-      <c r="C340" s="49"/>
-      <c r="F340" s="49"/>
-      <c r="AT340" s="52"/>
-      <c r="AY340" s="49"/>
-    </row>
-    <row r="341" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A341" s="48"/>
-      <c r="B341" s="49"/>
-      <c r="C341" s="49"/>
-      <c r="F341" s="49"/>
-      <c r="AT341" s="52"/>
-      <c r="AY341" s="49"/>
-    </row>
-    <row r="342" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A342" s="48"/>
-      <c r="B342" s="49"/>
-      <c r="C342" s="49"/>
-      <c r="F342" s="49"/>
-      <c r="AT342" s="52"/>
-      <c r="AY342" s="49"/>
-    </row>
-    <row r="343" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A343" s="48"/>
-      <c r="B343" s="49"/>
-      <c r="C343" s="49"/>
-      <c r="F343" s="49"/>
-      <c r="AT343" s="52"/>
-      <c r="AY343" s="49"/>
-    </row>
-    <row r="344" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A344" s="48"/>
-      <c r="B344" s="49"/>
-      <c r="C344" s="49"/>
-      <c r="F344" s="49"/>
-      <c r="AT344" s="52"/>
-      <c r="AY344" s="49"/>
-    </row>
-    <row r="345" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A345" s="48"/>
-      <c r="B345" s="49"/>
-      <c r="C345" s="49"/>
-      <c r="F345" s="49"/>
-      <c r="AT345" s="52"/>
-      <c r="AY345" s="49"/>
-    </row>
-    <row r="346" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A346" s="48"/>
-      <c r="B346" s="49"/>
-      <c r="C346" s="49"/>
-      <c r="F346" s="49"/>
-      <c r="AT346" s="52"/>
-      <c r="AY346" s="49"/>
-    </row>
-    <row r="347" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A347" s="48"/>
-      <c r="B347" s="49"/>
-      <c r="C347" s="49"/>
-      <c r="F347" s="49"/>
-      <c r="AT347" s="52"/>
-      <c r="AY347" s="49"/>
-    </row>
-    <row r="348" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A348" s="48"/>
-      <c r="B348" s="49"/>
-      <c r="C348" s="49"/>
-      <c r="F348" s="49"/>
-      <c r="AT348" s="52"/>
-      <c r="AY348" s="49"/>
-    </row>
-    <row r="349" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A349" s="48"/>
-      <c r="B349" s="49"/>
-      <c r="C349" s="49"/>
-      <c r="F349" s="49"/>
-      <c r="AT349" s="52"/>
-      <c r="AY349" s="49"/>
-    </row>
-    <row r="350" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A350" s="48"/>
-      <c r="B350" s="49"/>
-      <c r="C350" s="49"/>
-      <c r="F350" s="49"/>
-      <c r="AT350" s="52"/>
-      <c r="AY350" s="49"/>
-    </row>
-    <row r="351" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A351" s="48"/>
-      <c r="B351" s="49"/>
-      <c r="C351" s="49"/>
-      <c r="F351" s="49"/>
-      <c r="AT351" s="52"/>
-      <c r="AY351" s="49"/>
-    </row>
-    <row r="352" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A352" s="48"/>
-      <c r="B352" s="49"/>
-      <c r="C352" s="49"/>
-      <c r="F352" s="49"/>
-      <c r="AT352" s="52"/>
-      <c r="AY352" s="49"/>
-    </row>
-    <row r="353" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A353" s="48"/>
-      <c r="B353" s="49"/>
-      <c r="C353" s="49"/>
-      <c r="F353" s="49"/>
-      <c r="AT353" s="52"/>
-      <c r="AY353" s="49"/>
-    </row>
-    <row r="354" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A354" s="48"/>
-      <c r="B354" s="49"/>
-      <c r="C354" s="49"/>
-      <c r="F354" s="49"/>
-      <c r="AT354" s="52"/>
-      <c r="AY354" s="49"/>
-    </row>
-    <row r="355" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A355" s="48"/>
-      <c r="B355" s="49"/>
-      <c r="C355" s="49"/>
-      <c r="F355" s="49"/>
-      <c r="AT355" s="52"/>
-      <c r="AY355" s="49"/>
-    </row>
-    <row r="356" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A356" s="48"/>
-      <c r="B356" s="49"/>
-      <c r="C356" s="49"/>
-      <c r="F356" s="49"/>
-      <c r="AT356" s="52"/>
-      <c r="AY356" s="49"/>
-    </row>
-    <row r="357" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A357" s="48"/>
-      <c r="B357" s="49"/>
-      <c r="C357" s="49"/>
-      <c r="F357" s="49"/>
-      <c r="AT357" s="52"/>
-      <c r="AY357" s="49"/>
-    </row>
-    <row r="358" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A358" s="48"/>
-      <c r="B358" s="49"/>
-      <c r="C358" s="49"/>
-      <c r="F358" s="49"/>
-      <c r="AT358" s="52"/>
-      <c r="AY358" s="49"/>
-    </row>
-    <row r="359" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A359" s="48"/>
-      <c r="B359" s="49"/>
-      <c r="C359" s="49"/>
-      <c r="F359" s="49"/>
-      <c r="AT359" s="52"/>
-      <c r="AY359" s="49"/>
-    </row>
-    <row r="360" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A360" s="48"/>
-      <c r="B360" s="49"/>
-      <c r="C360" s="49"/>
-      <c r="F360" s="49"/>
-      <c r="AT360" s="52"/>
-      <c r="AY360" s="49"/>
-    </row>
-    <row r="361" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A361" s="48"/>
-      <c r="B361" s="49"/>
-      <c r="C361" s="49"/>
-      <c r="F361" s="49"/>
-      <c r="AT361" s="52"/>
-      <c r="AY361" s="49"/>
-    </row>
-    <row r="362" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A362" s="48"/>
-      <c r="B362" s="49"/>
-      <c r="C362" s="49"/>
-      <c r="F362" s="49"/>
-      <c r="AT362" s="52"/>
-      <c r="AY362" s="49"/>
-    </row>
-    <row r="363" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A363" s="48"/>
-      <c r="B363" s="49"/>
-      <c r="C363" s="49"/>
-      <c r="F363" s="49"/>
-      <c r="AT363" s="52"/>
-      <c r="AY363" s="49"/>
-    </row>
-    <row r="364" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A364" s="48"/>
-      <c r="B364" s="49"/>
-      <c r="C364" s="49"/>
-      <c r="F364" s="49"/>
-      <c r="AT364" s="52"/>
-      <c r="AY364" s="49"/>
-    </row>
-    <row r="365" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A365" s="48"/>
-      <c r="B365" s="49"/>
-      <c r="C365" s="49"/>
-      <c r="F365" s="49"/>
-      <c r="AT365" s="52"/>
-      <c r="AY365" s="49"/>
-    </row>
-    <row r="366" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A366" s="48"/>
-      <c r="B366" s="49"/>
-      <c r="C366" s="49"/>
-      <c r="F366" s="49"/>
-      <c r="AT366" s="52"/>
-      <c r="AY366" s="49"/>
-    </row>
-    <row r="367" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A367" s="48"/>
-      <c r="B367" s="49"/>
-      <c r="C367" s="49"/>
-      <c r="F367" s="49"/>
-      <c r="AT367" s="52"/>
-      <c r="AY367" s="49"/>
-    </row>
-    <row r="368" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A368" s="48"/>
-      <c r="B368" s="49"/>
-      <c r="C368" s="49"/>
-      <c r="F368" s="49"/>
-      <c r="AT368" s="52"/>
-      <c r="AY368" s="49"/>
-    </row>
-    <row r="369" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A369" s="48"/>
-      <c r="B369" s="49"/>
-      <c r="C369" s="49"/>
-      <c r="F369" s="49"/>
-      <c r="AT369" s="52"/>
-      <c r="AY369" s="49"/>
-    </row>
-    <row r="370" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A370" s="48"/>
-      <c r="B370" s="49"/>
-      <c r="C370" s="49"/>
-      <c r="F370" s="49"/>
-      <c r="AT370" s="52"/>
-      <c r="AY370" s="49"/>
-    </row>
-    <row r="371" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A371" s="48"/>
-      <c r="B371" s="49"/>
-      <c r="C371" s="49"/>
-      <c r="F371" s="49"/>
-      <c r="AT371" s="52"/>
-      <c r="AY371" s="49"/>
-    </row>
-    <row r="372" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A372" s="48"/>
-      <c r="B372" s="49"/>
-      <c r="C372" s="49"/>
-      <c r="F372" s="49"/>
-      <c r="AT372" s="52"/>
-      <c r="AY372" s="49"/>
-    </row>
-    <row r="373" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A373" s="48"/>
-      <c r="B373" s="49"/>
-      <c r="C373" s="49"/>
-      <c r="F373" s="49"/>
-      <c r="AT373" s="52"/>
-      <c r="AY373" s="49"/>
-    </row>
-    <row r="374" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A374" s="48"/>
-      <c r="B374" s="49"/>
-      <c r="C374" s="49"/>
-      <c r="F374" s="49"/>
-      <c r="AT374" s="52"/>
-      <c r="AY374" s="49"/>
-    </row>
-    <row r="375" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A375" s="48"/>
-      <c r="B375" s="49"/>
-      <c r="C375" s="49"/>
-      <c r="F375" s="49"/>
-      <c r="AT375" s="52"/>
-      <c r="AY375" s="49"/>
-    </row>
-    <row r="376" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A376" s="48"/>
-      <c r="B376" s="49"/>
-      <c r="C376" s="49"/>
-      <c r="F376" s="49"/>
-      <c r="AT376" s="52"/>
-      <c r="AY376" s="49"/>
-    </row>
-    <row r="377" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A377" s="48"/>
-      <c r="B377" s="49"/>
-      <c r="C377" s="49"/>
-      <c r="F377" s="49"/>
-      <c r="AT377" s="52"/>
-      <c r="AY377" s="49"/>
-    </row>
-    <row r="378" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A378" s="48"/>
-      <c r="B378" s="49"/>
-      <c r="C378" s="49"/>
-      <c r="F378" s="49"/>
-      <c r="AT378" s="52"/>
-      <c r="AY378" s="49"/>
-    </row>
-    <row r="379" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A379" s="48"/>
-      <c r="B379" s="49"/>
-      <c r="C379" s="49"/>
-      <c r="F379" s="49"/>
-      <c r="AT379" s="52"/>
-      <c r="AY379" s="49"/>
-    </row>
-    <row r="380" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A380" s="48"/>
-      <c r="B380" s="49"/>
-      <c r="C380" s="49"/>
-      <c r="F380" s="49"/>
-      <c r="AT380" s="52"/>
-      <c r="AY380" s="49"/>
-    </row>
-    <row r="381" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A381" s="48"/>
-      <c r="B381" s="49"/>
-      <c r="C381" s="49"/>
-      <c r="F381" s="49"/>
-      <c r="AT381" s="52"/>
-      <c r="AY381" s="49"/>
-    </row>
-    <row r="382" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A382" s="48"/>
-      <c r="B382" s="49"/>
-      <c r="C382" s="49"/>
-      <c r="F382" s="49"/>
-      <c r="AT382" s="52"/>
-      <c r="AY382" s="49"/>
-    </row>
-    <row r="383" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A383" s="48"/>
-      <c r="B383" s="49"/>
-      <c r="C383" s="49"/>
-      <c r="F383" s="49"/>
-      <c r="AT383" s="52"/>
-      <c r="AY383" s="49"/>
-    </row>
-    <row r="384" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A384" s="48"/>
-      <c r="B384" s="49"/>
-      <c r="C384" s="49"/>
-      <c r="F384" s="49"/>
-      <c r="AT384" s="52"/>
-      <c r="AY384" s="49"/>
-    </row>
-    <row r="385" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A385" s="48"/>
-      <c r="B385" s="49"/>
-      <c r="C385" s="49"/>
-      <c r="F385" s="49"/>
-      <c r="AT385" s="52"/>
-      <c r="AY385" s="49"/>
-    </row>
-    <row r="386" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A386" s="48"/>
-      <c r="B386" s="49"/>
-      <c r="C386" s="49"/>
-      <c r="F386" s="49"/>
-      <c r="AT386" s="52"/>
-      <c r="AY386" s="49"/>
-    </row>
-    <row r="387" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A387" s="48"/>
-      <c r="B387" s="49"/>
-      <c r="C387" s="49"/>
-      <c r="F387" s="49"/>
-      <c r="AT387" s="52"/>
-      <c r="AY387" s="49"/>
-    </row>
-    <row r="388" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A388" s="48"/>
-      <c r="B388" s="49"/>
-      <c r="C388" s="49"/>
-      <c r="F388" s="49"/>
-      <c r="AT388" s="52"/>
-      <c r="AY388" s="49"/>
-    </row>
-    <row r="389" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A389" s="48"/>
-      <c r="B389" s="49"/>
-      <c r="C389" s="49"/>
-      <c r="F389" s="49"/>
-      <c r="AT389" s="52"/>
-      <c r="AY389" s="49"/>
-    </row>
-    <row r="390" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A390" s="48"/>
-      <c r="B390" s="49"/>
-      <c r="C390" s="49"/>
-      <c r="F390" s="49"/>
-      <c r="AT390" s="52"/>
-      <c r="AY390" s="49"/>
-    </row>
-    <row r="391" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A391" s="48"/>
-      <c r="B391" s="49"/>
-      <c r="C391" s="49"/>
-      <c r="F391" s="49"/>
-      <c r="AT391" s="52"/>
-      <c r="AY391" s="49"/>
-    </row>
-    <row r="392" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A392" s="48"/>
-      <c r="B392" s="49"/>
-      <c r="C392" s="49"/>
-      <c r="F392" s="49"/>
-      <c r="AT392" s="52"/>
-      <c r="AY392" s="49"/>
-    </row>
-    <row r="393" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A393" s="48"/>
-      <c r="B393" s="49"/>
-      <c r="C393" s="49"/>
-      <c r="F393" s="49"/>
-      <c r="AT393" s="52"/>
-      <c r="AY393" s="49"/>
-    </row>
-    <row r="394" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A394" s="48"/>
-      <c r="B394" s="49"/>
-      <c r="C394" s="49"/>
-      <c r="F394" s="49"/>
-      <c r="AT394" s="52"/>
-      <c r="AY394" s="49"/>
-    </row>
-    <row r="395" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A395" s="48"/>
-      <c r="B395" s="49"/>
-      <c r="C395" s="49"/>
-      <c r="F395" s="49"/>
-      <c r="AT395" s="52"/>
-      <c r="AY395" s="49"/>
-    </row>
-    <row r="396" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A396" s="48"/>
-      <c r="B396" s="49"/>
-      <c r="C396" s="49"/>
-      <c r="F396" s="49"/>
-      <c r="AT396" s="52"/>
-      <c r="AY396" s="49"/>
-    </row>
-    <row r="397" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A397" s="48"/>
-      <c r="B397" s="49"/>
-      <c r="C397" s="49"/>
-      <c r="F397" s="49"/>
-      <c r="AT397" s="52"/>
-      <c r="AY397" s="49"/>
-    </row>
-    <row r="398" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A398" s="48"/>
-      <c r="B398" s="49"/>
-      <c r="C398" s="49"/>
-      <c r="F398" s="49"/>
-      <c r="AT398" s="52"/>
-      <c r="AY398" s="49"/>
-    </row>
-    <row r="399" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A399" s="48"/>
-      <c r="B399" s="49"/>
-      <c r="C399" s="49"/>
-      <c r="F399" s="49"/>
-      <c r="AT399" s="52"/>
-      <c r="AY399" s="49"/>
-    </row>
-    <row r="400" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A400" s="48"/>
-      <c r="B400" s="49"/>
-      <c r="C400" s="49"/>
-      <c r="F400" s="49"/>
-      <c r="AT400" s="52"/>
-      <c r="AY400" s="49"/>
-    </row>
-    <row r="401" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A401" s="48"/>
-      <c r="B401" s="49"/>
-      <c r="C401" s="49"/>
-      <c r="F401" s="49"/>
-      <c r="AT401" s="52"/>
-      <c r="AY401" s="49"/>
-    </row>
-    <row r="402" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A402" s="48"/>
-      <c r="B402" s="49"/>
-      <c r="C402" s="49"/>
-      <c r="F402" s="49"/>
-      <c r="AT402" s="52"/>
-      <c r="AY402" s="49"/>
-    </row>
-    <row r="403" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A403" s="48"/>
-      <c r="B403" s="49"/>
-      <c r="C403" s="49"/>
-      <c r="F403" s="49"/>
-      <c r="AT403" s="52"/>
-      <c r="AY403" s="49"/>
-    </row>
-    <row r="404" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A404" s="48"/>
-      <c r="B404" s="49"/>
-      <c r="C404" s="49"/>
-      <c r="F404" s="49"/>
-      <c r="AT404" s="52"/>
-      <c r="AY404" s="49"/>
-    </row>
-    <row r="405" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A405" s="48"/>
-      <c r="B405" s="49"/>
-      <c r="C405" s="49"/>
-      <c r="F405" s="49"/>
-      <c r="AT405" s="52"/>
-      <c r="AY405" s="49"/>
-    </row>
-    <row r="406" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A406" s="48"/>
-      <c r="B406" s="49"/>
-      <c r="C406" s="49"/>
-      <c r="F406" s="49"/>
-      <c r="AT406" s="52"/>
-      <c r="AY406" s="49"/>
-    </row>
-    <row r="407" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A407" s="48"/>
-      <c r="B407" s="49"/>
-      <c r="C407" s="49"/>
-      <c r="F407" s="49"/>
-      <c r="AT407" s="52"/>
-      <c r="AY407" s="49"/>
-    </row>
-    <row r="408" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A408" s="48"/>
-      <c r="B408" s="49"/>
-      <c r="C408" s="49"/>
-      <c r="F408" s="49"/>
-      <c r="AT408" s="52"/>
-      <c r="AY408" s="49"/>
-    </row>
-    <row r="409" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A409" s="48"/>
-      <c r="B409" s="49"/>
-      <c r="C409" s="49"/>
-      <c r="F409" s="49"/>
-      <c r="AT409" s="52"/>
-      <c r="AY409" s="49"/>
-    </row>
-    <row r="410" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A410" s="48"/>
-      <c r="B410" s="49"/>
-      <c r="C410" s="49"/>
-      <c r="F410" s="49"/>
-      <c r="AT410" s="52"/>
-      <c r="AY410" s="49"/>
-    </row>
-    <row r="411" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A411" s="48"/>
-      <c r="B411" s="49"/>
-      <c r="C411" s="49"/>
-      <c r="F411" s="49"/>
-      <c r="AT411" s="52"/>
-      <c r="AY411" s="49"/>
-    </row>
-    <row r="412" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A412" s="48"/>
-      <c r="B412" s="49"/>
-      <c r="C412" s="49"/>
-      <c r="F412" s="49"/>
-      <c r="AT412" s="52"/>
-      <c r="AY412" s="49"/>
-    </row>
-    <row r="413" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A413" s="48"/>
-      <c r="B413" s="49"/>
-      <c r="C413" s="49"/>
-      <c r="F413" s="49"/>
-      <c r="AT413" s="52"/>
-      <c r="AY413" s="49"/>
-    </row>
-    <row r="414" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A414" s="48"/>
-      <c r="B414" s="49"/>
-      <c r="C414" s="49"/>
-      <c r="F414" s="49"/>
-      <c r="AT414" s="52"/>
-      <c r="AY414" s="49"/>
-    </row>
-    <row r="415" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A415" s="48"/>
-      <c r="B415" s="49"/>
-      <c r="C415" s="49"/>
-      <c r="F415" s="49"/>
-      <c r="AT415" s="52"/>
-      <c r="AY415" s="49"/>
-    </row>
-    <row r="416" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A416" s="48"/>
-      <c r="B416" s="49"/>
-      <c r="C416" s="49"/>
-      <c r="F416" s="49"/>
-      <c r="AT416" s="52"/>
-      <c r="AY416" s="49"/>
-    </row>
-    <row r="417" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A417" s="48"/>
-      <c r="B417" s="49"/>
-      <c r="C417" s="49"/>
-      <c r="F417" s="49"/>
-      <c r="AT417" s="52"/>
-      <c r="AY417" s="49"/>
-    </row>
-    <row r="418" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A418" s="48"/>
-      <c r="B418" s="49"/>
-      <c r="C418" s="49"/>
-      <c r="F418" s="49"/>
-      <c r="AT418" s="52"/>
-      <c r="AY418" s="49"/>
-    </row>
-    <row r="419" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A419" s="48"/>
-      <c r="B419" s="49"/>
-      <c r="C419" s="49"/>
-      <c r="F419" s="49"/>
-      <c r="AT419" s="52"/>
-      <c r="AY419" s="49"/>
-    </row>
-    <row r="420" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A420" s="48"/>
-      <c r="B420" s="49"/>
-      <c r="C420" s="49"/>
-      <c r="F420" s="49"/>
-      <c r="AT420" s="52"/>
-      <c r="AY420" s="49"/>
-    </row>
-    <row r="421" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A421" s="48"/>
-      <c r="B421" s="49"/>
-      <c r="C421" s="49"/>
-      <c r="F421" s="49"/>
-      <c r="AT421" s="52"/>
-      <c r="AY421" s="49"/>
-    </row>
-    <row r="422" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A422" s="48"/>
-      <c r="B422" s="49"/>
-      <c r="C422" s="49"/>
-      <c r="F422" s="49"/>
-      <c r="AT422" s="52"/>
-      <c r="AY422" s="49"/>
-    </row>
-    <row r="423" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A423" s="48"/>
-      <c r="B423" s="49"/>
-      <c r="C423" s="49"/>
-      <c r="F423" s="49"/>
-      <c r="AT423" s="52"/>
-      <c r="AY423" s="49"/>
-    </row>
-    <row r="424" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A424" s="48"/>
-      <c r="B424" s="49"/>
-      <c r="C424" s="49"/>
-      <c r="F424" s="49"/>
-      <c r="AT424" s="52"/>
-      <c r="AY424" s="49"/>
-    </row>
-    <row r="425" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A425" s="48"/>
-      <c r="B425" s="49"/>
-      <c r="C425" s="49"/>
-      <c r="F425" s="49"/>
-      <c r="AT425" s="52"/>
-      <c r="AY425" s="49"/>
-    </row>
-    <row r="426" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A426" s="48"/>
-      <c r="B426" s="49"/>
-      <c r="C426" s="49"/>
-      <c r="F426" s="49"/>
-      <c r="AT426" s="52"/>
-      <c r="AY426" s="49"/>
-    </row>
-    <row r="427" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A427" s="48"/>
-      <c r="B427" s="49"/>
-      <c r="C427" s="49"/>
-      <c r="F427" s="49"/>
-      <c r="AT427" s="52"/>
-      <c r="AY427" s="49"/>
-    </row>
-    <row r="428" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A428" s="48"/>
-      <c r="B428" s="49"/>
-      <c r="C428" s="49"/>
-      <c r="F428" s="49"/>
-      <c r="AT428" s="52"/>
-      <c r="AY428" s="49"/>
-    </row>
-    <row r="429" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A429" s="48"/>
-      <c r="B429" s="49"/>
-      <c r="C429" s="49"/>
-      <c r="F429" s="49"/>
-      <c r="AT429" s="52"/>
-      <c r="AY429" s="49"/>
-    </row>
-    <row r="430" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A430" s="48"/>
-      <c r="B430" s="49"/>
-      <c r="C430" s="49"/>
-      <c r="F430" s="49"/>
-      <c r="AT430" s="52"/>
-      <c r="AY430" s="49"/>
-    </row>
-    <row r="431" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A431" s="48"/>
-      <c r="B431" s="49"/>
-      <c r="C431" s="49"/>
-      <c r="F431" s="49"/>
-      <c r="AT431" s="52"/>
-      <c r="AY431" s="49"/>
-    </row>
-    <row r="432" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A432" s="48"/>
-      <c r="B432" s="49"/>
-      <c r="C432" s="49"/>
-      <c r="F432" s="49"/>
-      <c r="AT432" s="52"/>
-      <c r="AY432" s="49"/>
-    </row>
-    <row r="433" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A433" s="48"/>
-      <c r="B433" s="49"/>
-      <c r="C433" s="49"/>
-      <c r="F433" s="49"/>
-      <c r="AT433" s="52"/>
-      <c r="AY433" s="49"/>
-    </row>
-    <row r="434" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A434" s="48"/>
-      <c r="B434" s="49"/>
-      <c r="C434" s="49"/>
-      <c r="F434" s="49"/>
-      <c r="AT434" s="52"/>
-      <c r="AY434" s="49"/>
-    </row>
-    <row r="435" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A435" s="48"/>
-      <c r="B435" s="49"/>
-      <c r="C435" s="49"/>
-      <c r="F435" s="49"/>
-      <c r="AT435" s="52"/>
-      <c r="AY435" s="49"/>
-    </row>
-    <row r="436" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A436" s="48"/>
-      <c r="B436" s="49"/>
-      <c r="C436" s="49"/>
-      <c r="F436" s="49"/>
-      <c r="AT436" s="52"/>
-      <c r="AY436" s="49"/>
-    </row>
-    <row r="437" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A437" s="48"/>
-      <c r="B437" s="49"/>
-      <c r="C437" s="49"/>
-      <c r="F437" s="49"/>
-      <c r="AT437" s="52"/>
-      <c r="AY437" s="49"/>
-    </row>
-    <row r="438" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A438" s="48"/>
-      <c r="B438" s="49"/>
-      <c r="C438" s="49"/>
-      <c r="F438" s="49"/>
-      <c r="AT438" s="52"/>
-      <c r="AY438" s="49"/>
-    </row>
-    <row r="439" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A439" s="48"/>
-      <c r="B439" s="49"/>
-      <c r="C439" s="49"/>
-      <c r="F439" s="49"/>
-      <c r="AT439" s="52"/>
-      <c r="AY439" s="49"/>
-    </row>
-    <row r="440" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A440" s="48"/>
-      <c r="B440" s="49"/>
-      <c r="C440" s="49"/>
-      <c r="F440" s="49"/>
-      <c r="AT440" s="52"/>
-      <c r="AY440" s="49"/>
-    </row>
-    <row r="441" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A441" s="48"/>
-      <c r="B441" s="49"/>
-      <c r="C441" s="49"/>
-      <c r="F441" s="49"/>
-      <c r="AT441" s="52"/>
-      <c r="AY441" s="49"/>
-    </row>
-    <row r="442" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A442" s="48"/>
-      <c r="B442" s="49"/>
-      <c r="C442" s="49"/>
-      <c r="F442" s="49"/>
-      <c r="AT442" s="52"/>
-      <c r="AY442" s="49"/>
-    </row>
-    <row r="443" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A443" s="48"/>
-      <c r="B443" s="49"/>
-      <c r="C443" s="49"/>
-      <c r="F443" s="49"/>
-      <c r="AT443" s="52"/>
-      <c r="AY443" s="49"/>
-    </row>
-    <row r="444" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A444" s="48"/>
-      <c r="B444" s="49"/>
-      <c r="C444" s="49"/>
-      <c r="F444" s="49"/>
-      <c r="AT444" s="52"/>
-      <c r="AY444" s="49"/>
-    </row>
-    <row r="445" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A445" s="48"/>
-      <c r="B445" s="49"/>
-      <c r="C445" s="49"/>
-      <c r="F445" s="49"/>
-      <c r="AT445" s="52"/>
-      <c r="AY445" s="49"/>
-    </row>
-    <row r="446" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A446" s="48"/>
-      <c r="B446" s="49"/>
-      <c r="C446" s="49"/>
-      <c r="F446" s="49"/>
-      <c r="AT446" s="52"/>
-      <c r="AY446" s="49"/>
-    </row>
-    <row r="447" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A447" s="48"/>
-      <c r="B447" s="49"/>
-      <c r="C447" s="49"/>
-      <c r="F447" s="49"/>
-      <c r="AT447" s="52"/>
-      <c r="AY447" s="49"/>
-    </row>
-    <row r="448" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A448" s="48"/>
-      <c r="B448" s="49"/>
-      <c r="C448" s="49"/>
-      <c r="F448" s="49"/>
-      <c r="AT448" s="52"/>
-      <c r="AY448" s="49"/>
-    </row>
-    <row r="449" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A449" s="48"/>
-      <c r="B449" s="49"/>
-      <c r="C449" s="49"/>
-      <c r="F449" s="49"/>
-      <c r="AT449" s="52"/>
-      <c r="AY449" s="49"/>
-    </row>
-    <row r="450" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A450" s="48"/>
-      <c r="B450" s="49"/>
-      <c r="C450" s="49"/>
-      <c r="F450" s="49"/>
-      <c r="AT450" s="52"/>
-      <c r="AY450" s="49"/>
-    </row>
-    <row r="451" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A451" s="48"/>
-      <c r="B451" s="49"/>
-      <c r="C451" s="49"/>
-      <c r="F451" s="49"/>
-      <c r="AT451" s="52"/>
-      <c r="AY451" s="49"/>
-    </row>
-    <row r="452" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A452" s="48"/>
-      <c r="B452" s="49"/>
-      <c r="C452" s="49"/>
-      <c r="F452" s="49"/>
-      <c r="AT452" s="52"/>
-      <c r="AY452" s="49"/>
-    </row>
-    <row r="453" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A453" s="48"/>
-      <c r="B453" s="49"/>
-      <c r="C453" s="49"/>
-      <c r="F453" s="49"/>
-      <c r="AT453" s="52"/>
-      <c r="AY453" s="49"/>
-    </row>
-    <row r="454" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A454" s="48"/>
-      <c r="B454" s="49"/>
-      <c r="C454" s="49"/>
-      <c r="F454" s="49"/>
-      <c r="AT454" s="52"/>
-      <c r="AY454" s="49"/>
-    </row>
-    <row r="455" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A455" s="48"/>
-      <c r="B455" s="49"/>
-      <c r="C455" s="49"/>
-      <c r="F455" s="49"/>
-      <c r="AT455" s="52"/>
-      <c r="AY455" s="49"/>
-    </row>
-    <row r="456" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A456" s="48"/>
-      <c r="B456" s="49"/>
-      <c r="C456" s="49"/>
-      <c r="F456" s="49"/>
-      <c r="AT456" s="52"/>
-      <c r="AY456" s="49"/>
-    </row>
-    <row r="457" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A457" s="48"/>
-      <c r="B457" s="49"/>
-      <c r="C457" s="49"/>
-      <c r="F457" s="49"/>
-      <c r="AT457" s="52"/>
-      <c r="AY457" s="49"/>
-    </row>
-    <row r="458" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A458" s="48"/>
-      <c r="B458" s="49"/>
-      <c r="C458" s="49"/>
-      <c r="F458" s="49"/>
-      <c r="AT458" s="52"/>
-      <c r="AY458" s="49"/>
-    </row>
-    <row r="459" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A459" s="48"/>
-      <c r="B459" s="49"/>
-      <c r="C459" s="49"/>
-      <c r="F459" s="49"/>
-      <c r="AT459" s="52"/>
-      <c r="AY459" s="49"/>
-    </row>
-    <row r="460" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A460" s="48"/>
-      <c r="B460" s="49"/>
-      <c r="C460" s="49"/>
-      <c r="F460" s="49"/>
-      <c r="AT460" s="52"/>
-      <c r="AY460" s="49"/>
-    </row>
-    <row r="461" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A461" s="48"/>
-      <c r="B461" s="49"/>
-      <c r="C461" s="49"/>
-      <c r="F461" s="49"/>
-      <c r="AT461" s="52"/>
-      <c r="AY461" s="49"/>
-    </row>
-    <row r="462" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A462" s="48"/>
-      <c r="B462" s="49"/>
-      <c r="C462" s="49"/>
-      <c r="F462" s="49"/>
-      <c r="AT462" s="52"/>
-      <c r="AY462" s="49"/>
-    </row>
-    <row r="463" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A463" s="48"/>
-      <c r="B463" s="49"/>
-      <c r="C463" s="49"/>
-      <c r="F463" s="49"/>
-      <c r="AT463" s="52"/>
-      <c r="AY463" s="49"/>
-    </row>
-    <row r="464" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A464" s="48"/>
-      <c r="B464" s="49"/>
-      <c r="C464" s="49"/>
-      <c r="F464" s="49"/>
-      <c r="AT464" s="52"/>
-      <c r="AY464" s="49"/>
-    </row>
-    <row r="465" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A465" s="48"/>
-      <c r="B465" s="49"/>
-      <c r="C465" s="49"/>
-      <c r="F465" s="49"/>
-      <c r="AT465" s="52"/>
-      <c r="AY465" s="49"/>
-    </row>
-    <row r="466" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A466" s="48"/>
-      <c r="B466" s="49"/>
-      <c r="C466" s="49"/>
-      <c r="F466" s="49"/>
-      <c r="AT466" s="52"/>
-      <c r="AY466" s="49"/>
-    </row>
-    <row r="467" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A467" s="48"/>
-      <c r="B467" s="49"/>
-      <c r="C467" s="49"/>
-      <c r="F467" s="49"/>
-      <c r="AT467" s="52"/>
-      <c r="AY467" s="49"/>
-    </row>
-    <row r="468" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A468" s="48"/>
-      <c r="B468" s="49"/>
-      <c r="C468" s="49"/>
-      <c r="F468" s="49"/>
-      <c r="AT468" s="52"/>
-      <c r="AY468" s="49"/>
-    </row>
-    <row r="469" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A469" s="48"/>
-      <c r="B469" s="49"/>
-      <c r="C469" s="49"/>
-      <c r="F469" s="49"/>
-      <c r="AT469" s="52"/>
-      <c r="AY469" s="49"/>
-    </row>
-    <row r="470" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A470" s="48"/>
-      <c r="B470" s="49"/>
-      <c r="C470" s="49"/>
-      <c r="F470" s="49"/>
-      <c r="AT470" s="52"/>
-      <c r="AY470" s="49"/>
-    </row>
-    <row r="471" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A471" s="48"/>
-      <c r="B471" s="49"/>
-      <c r="C471" s="49"/>
-      <c r="F471" s="49"/>
-      <c r="AT471" s="52"/>
-      <c r="AY471" s="49"/>
-    </row>
-    <row r="472" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A472" s="48"/>
-      <c r="B472" s="49"/>
-      <c r="C472" s="49"/>
-      <c r="F472" s="49"/>
-      <c r="AT472" s="52"/>
-      <c r="AY472" s="49"/>
-    </row>
-    <row r="473" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A473" s="48"/>
-      <c r="B473" s="49"/>
-      <c r="C473" s="49"/>
-      <c r="F473" s="49"/>
-      <c r="AT473" s="52"/>
-      <c r="AY473" s="49"/>
-    </row>
-    <row r="474" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A474" s="48"/>
-      <c r="B474" s="49"/>
-      <c r="C474" s="49"/>
-      <c r="F474" s="49"/>
-      <c r="AT474" s="52"/>
-      <c r="AY474" s="49"/>
-    </row>
-    <row r="475" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A475" s="48"/>
-      <c r="B475" s="49"/>
-      <c r="C475" s="49"/>
-      <c r="F475" s="49"/>
-      <c r="AT475" s="52"/>
-      <c r="AY475" s="49"/>
-    </row>
-    <row r="476" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A476" s="48"/>
-      <c r="B476" s="49"/>
-      <c r="C476" s="49"/>
-      <c r="F476" s="49"/>
-      <c r="AT476" s="52"/>
-      <c r="AY476" s="49"/>
-    </row>
-    <row r="477" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A477" s="48"/>
-      <c r="B477" s="49"/>
-      <c r="C477" s="49"/>
-      <c r="F477" s="49"/>
-      <c r="AT477" s="52"/>
-      <c r="AY477" s="49"/>
-    </row>
-    <row r="478" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A478" s="48"/>
-      <c r="B478" s="49"/>
-      <c r="C478" s="49"/>
-      <c r="F478" s="49"/>
-      <c r="AT478" s="52"/>
-      <c r="AY478" s="49"/>
-    </row>
-    <row r="479" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A479" s="48"/>
-      <c r="B479" s="49"/>
-      <c r="C479" s="49"/>
-      <c r="F479" s="49"/>
-      <c r="AT479" s="52"/>
-      <c r="AY479" s="49"/>
-    </row>
-    <row r="480" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A480" s="48"/>
-      <c r="B480" s="49"/>
-      <c r="C480" s="49"/>
-      <c r="F480" s="49"/>
-      <c r="AT480" s="52"/>
-      <c r="AY480" s="49"/>
-    </row>
-    <row r="481" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A481" s="48"/>
-      <c r="B481" s="49"/>
-      <c r="C481" s="49"/>
-      <c r="F481" s="49"/>
-      <c r="AT481" s="52"/>
-      <c r="AY481" s="49"/>
-    </row>
-    <row r="482" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A482" s="48"/>
-      <c r="B482" s="49"/>
-      <c r="C482" s="49"/>
-      <c r="F482" s="49"/>
-      <c r="AT482" s="52"/>
-      <c r="AY482" s="49"/>
-    </row>
-    <row r="483" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A483" s="48"/>
-      <c r="B483" s="49"/>
-      <c r="C483" s="49"/>
-      <c r="F483" s="49"/>
-      <c r="AT483" s="52"/>
-      <c r="AY483" s="49"/>
-    </row>
-    <row r="484" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A484" s="48"/>
-      <c r="B484" s="49"/>
-      <c r="C484" s="49"/>
-      <c r="F484" s="49"/>
-      <c r="AT484" s="52"/>
-      <c r="AY484" s="49"/>
-    </row>
-    <row r="485" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A485" s="48"/>
-      <c r="B485" s="49"/>
-      <c r="C485" s="49"/>
-      <c r="F485" s="49"/>
-      <c r="AT485" s="52"/>
-      <c r="AY485" s="49"/>
-    </row>
-    <row r="486" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A486" s="48"/>
-      <c r="B486" s="49"/>
-      <c r="C486" s="49"/>
-      <c r="F486" s="49"/>
-      <c r="AT486" s="52"/>
-      <c r="AY486" s="49"/>
-    </row>
-    <row r="487" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A487" s="48"/>
-      <c r="B487" s="49"/>
-      <c r="C487" s="49"/>
-      <c r="F487" s="49"/>
-      <c r="AT487" s="52"/>
-      <c r="AY487" s="49"/>
-    </row>
-    <row r="488" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A488" s="48"/>
-      <c r="B488" s="49"/>
-      <c r="C488" s="49"/>
-      <c r="F488" s="49"/>
-      <c r="AT488" s="52"/>
-      <c r="AY488" s="49"/>
-    </row>
-    <row r="489" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A489" s="48"/>
-      <c r="B489" s="49"/>
-      <c r="C489" s="49"/>
-      <c r="F489" s="49"/>
-      <c r="AT489" s="52"/>
-      <c r="AY489" s="49"/>
-    </row>
-    <row r="490" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A490" s="48"/>
-      <c r="B490" s="49"/>
-      <c r="C490" s="49"/>
-      <c r="F490" s="49"/>
-      <c r="AT490" s="52"/>
-      <c r="AY490" s="49"/>
-    </row>
-    <row r="491" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A491" s="48"/>
-      <c r="B491" s="49"/>
-      <c r="C491" s="49"/>
-      <c r="F491" s="49"/>
-      <c r="AT491" s="52"/>
-      <c r="AY491" s="49"/>
-    </row>
-    <row r="492" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A492" s="48"/>
-      <c r="B492" s="49"/>
-      <c r="C492" s="49"/>
-      <c r="F492" s="49"/>
-      <c r="AT492" s="52"/>
-      <c r="AY492" s="49"/>
-    </row>
-    <row r="493" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A493" s="48"/>
-      <c r="B493" s="49"/>
-      <c r="C493" s="49"/>
-      <c r="F493" s="49"/>
-      <c r="AT493" s="52"/>
-      <c r="AY493" s="49"/>
-    </row>
-    <row r="494" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A494" s="48"/>
-      <c r="B494" s="49"/>
-      <c r="C494" s="49"/>
-      <c r="F494" s="49"/>
-      <c r="AT494" s="52"/>
-      <c r="AY494" s="49"/>
-    </row>
-    <row r="495" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A495" s="48"/>
-      <c r="B495" s="49"/>
-      <c r="C495" s="49"/>
-      <c r="F495" s="49"/>
-      <c r="AT495" s="52"/>
-      <c r="AY495" s="49"/>
-    </row>
-    <row r="496" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A496" s="48"/>
-      <c r="B496" s="49"/>
-      <c r="C496" s="49"/>
-      <c r="F496" s="49"/>
-      <c r="AT496" s="52"/>
-      <c r="AY496" s="49"/>
-    </row>
-    <row r="497" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A497" s="48"/>
-      <c r="B497" s="49"/>
-      <c r="C497" s="49"/>
-      <c r="F497" s="49"/>
-      <c r="AT497" s="52"/>
-      <c r="AY497" s="49"/>
-    </row>
-    <row r="498" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A498" s="48"/>
-      <c r="B498" s="49"/>
-      <c r="C498" s="49"/>
-      <c r="F498" s="49"/>
-      <c r="AT498" s="52"/>
-      <c r="AY498" s="49"/>
-    </row>
-    <row r="499" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A499" s="48"/>
-      <c r="B499" s="49"/>
-      <c r="C499" s="49"/>
-      <c r="F499" s="49"/>
-      <c r="AT499" s="52"/>
-      <c r="AY499" s="49"/>
-    </row>
-    <row r="500" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A500" s="48"/>
-      <c r="B500" s="49"/>
-      <c r="C500" s="49"/>
-      <c r="F500" s="49"/>
-      <c r="AT500" s="52"/>
-      <c r="AY500" s="49"/>
-    </row>
-    <row r="501" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A501" s="48"/>
-      <c r="B501" s="49"/>
-      <c r="C501" s="49"/>
-      <c r="F501" s="49"/>
-      <c r="AT501" s="52"/>
-      <c r="AY501" s="49"/>
-    </row>
-    <row r="502" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A502" s="48"/>
-      <c r="B502" s="49"/>
-      <c r="C502" s="49"/>
-      <c r="F502" s="49"/>
-      <c r="AT502" s="52"/>
-      <c r="AY502" s="49"/>
-    </row>
-    <row r="503" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A503" s="48"/>
-      <c r="B503" s="49"/>
-      <c r="C503" s="49"/>
-      <c r="F503" s="49"/>
-      <c r="AT503" s="52"/>
-      <c r="AY503" s="49"/>
-    </row>
-    <row r="504" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A504" s="48"/>
-      <c r="B504" s="49"/>
-      <c r="C504" s="49"/>
-      <c r="F504" s="49"/>
-      <c r="AT504" s="52"/>
-      <c r="AY504" s="49"/>
-    </row>
-    <row r="505" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A505" s="48"/>
-      <c r="B505" s="49"/>
-      <c r="C505" s="49"/>
-      <c r="F505" s="49"/>
-      <c r="AT505" s="52"/>
-      <c r="AY505" s="49"/>
-    </row>
-    <row r="506" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A506" s="48"/>
-      <c r="B506" s="49"/>
-      <c r="C506" s="49"/>
-      <c r="F506" s="49"/>
-      <c r="AT506" s="52"/>
-      <c r="AY506" s="49"/>
-    </row>
-    <row r="507" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A507" s="48"/>
-      <c r="B507" s="49"/>
-      <c r="C507" s="49"/>
-      <c r="F507" s="49"/>
-      <c r="AT507" s="52"/>
-      <c r="AY507" s="49"/>
-    </row>
-    <row r="508" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A508" s="48"/>
-      <c r="B508" s="49"/>
-      <c r="C508" s="49"/>
-      <c r="F508" s="49"/>
-      <c r="AT508" s="52"/>
-      <c r="AY508" s="49"/>
-    </row>
-    <row r="509" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A509" s="48"/>
-      <c r="B509" s="49"/>
-      <c r="C509" s="49"/>
-      <c r="F509" s="49"/>
-      <c r="AT509" s="52"/>
-      <c r="AY509" s="49"/>
-    </row>
-    <row r="510" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A510" s="48"/>
-      <c r="B510" s="49"/>
-      <c r="C510" s="49"/>
-      <c r="F510" s="49"/>
-      <c r="AT510" s="52"/>
-      <c r="AY510" s="49"/>
-    </row>
-    <row r="511" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A511" s="48"/>
-      <c r="B511" s="49"/>
-      <c r="C511" s="49"/>
-      <c r="F511" s="49"/>
-      <c r="AT511" s="52"/>
-      <c r="AY511" s="49"/>
-    </row>
-    <row r="512" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A512" s="48"/>
-      <c r="B512" s="49"/>
-      <c r="C512" s="49"/>
-      <c r="F512" s="49"/>
-      <c r="AT512" s="52"/>
-      <c r="AY512" s="49"/>
-    </row>
-    <row r="513" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A513" s="48"/>
-      <c r="B513" s="49"/>
-      <c r="C513" s="49"/>
-      <c r="F513" s="49"/>
-      <c r="AT513" s="52"/>
-      <c r="AY513" s="49"/>
-    </row>
-    <row r="514" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A514" s="48"/>
-      <c r="B514" s="49"/>
-      <c r="C514" s="49"/>
-      <c r="F514" s="49"/>
-      <c r="AT514" s="52"/>
-      <c r="AY514" s="49"/>
-    </row>
-    <row r="515" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A515" s="48"/>
-      <c r="B515" s="49"/>
-      <c r="C515" s="49"/>
-      <c r="F515" s="49"/>
-      <c r="AT515" s="52"/>
-      <c r="AY515" s="49"/>
-    </row>
-    <row r="516" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A516" s="48"/>
-      <c r="B516" s="49"/>
-      <c r="C516" s="49"/>
-      <c r="F516" s="49"/>
-      <c r="AT516" s="52"/>
-      <c r="AY516" s="49"/>
-    </row>
-    <row r="517" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A517" s="48"/>
-      <c r="B517" s="49"/>
-      <c r="C517" s="49"/>
-      <c r="F517" s="49"/>
-      <c r="AT517" s="52"/>
-      <c r="AY517" s="49"/>
-    </row>
-    <row r="518" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A518" s="48"/>
-      <c r="B518" s="49"/>
-      <c r="C518" s="49"/>
-      <c r="F518" s="49"/>
-      <c r="AT518" s="52"/>
-      <c r="AY518" s="49"/>
-    </row>
-    <row r="519" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A519" s="48"/>
-      <c r="B519" s="49"/>
-      <c r="C519" s="49"/>
-      <c r="F519" s="49"/>
-      <c r="AT519" s="52"/>
-      <c r="AY519" s="49"/>
-    </row>
-    <row r="520" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A520" s="48"/>
-      <c r="B520" s="49"/>
-      <c r="C520" s="49"/>
-      <c r="F520" s="49"/>
-      <c r="AT520" s="52"/>
-      <c r="AY520" s="49"/>
-    </row>
-    <row r="521" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A521" s="48"/>
-      <c r="B521" s="49"/>
-      <c r="C521" s="49"/>
-      <c r="F521" s="49"/>
-      <c r="AT521" s="52"/>
-      <c r="AY521" s="49"/>
-    </row>
-    <row r="522" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A522" s="48"/>
-      <c r="B522" s="49"/>
-      <c r="C522" s="49"/>
-      <c r="F522" s="49"/>
-      <c r="AT522" s="52"/>
-      <c r="AY522" s="49"/>
-    </row>
-    <row r="523" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A523" s="48"/>
-      <c r="B523" s="49"/>
-      <c r="C523" s="49"/>
-      <c r="F523" s="49"/>
-      <c r="AT523" s="52"/>
-      <c r="AY523" s="49"/>
-    </row>
-    <row r="524" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A524" s="48"/>
-      <c r="B524" s="49"/>
-      <c r="C524" s="49"/>
-      <c r="F524" s="49"/>
-      <c r="AT524" s="52"/>
-      <c r="AY524" s="49"/>
-    </row>
-    <row r="525" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A525" s="48"/>
-      <c r="B525" s="49"/>
-      <c r="C525" s="49"/>
-      <c r="F525" s="49"/>
-      <c r="AT525" s="52"/>
-      <c r="AY525" s="49"/>
-    </row>
-    <row r="526" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A526" s="48"/>
-      <c r="B526" s="49"/>
-      <c r="C526" s="49"/>
-      <c r="F526" s="49"/>
-      <c r="AT526" s="52"/>
-      <c r="AY526" s="49"/>
-    </row>
-    <row r="527" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A527" s="48"/>
-      <c r="B527" s="49"/>
-      <c r="C527" s="49"/>
-      <c r="F527" s="49"/>
-      <c r="AT527" s="52"/>
-      <c r="AY527" s="49"/>
-    </row>
-    <row r="528" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A528" s="48"/>
-      <c r="B528" s="49"/>
-      <c r="C528" s="49"/>
-      <c r="F528" s="49"/>
-      <c r="AT528" s="52"/>
-      <c r="AY528" s="49"/>
-    </row>
-    <row r="529" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A529" s="48"/>
-      <c r="B529" s="49"/>
-      <c r="C529" s="49"/>
-      <c r="F529" s="49"/>
-      <c r="AT529" s="52"/>
-      <c r="AY529" s="49"/>
-    </row>
-    <row r="530" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A530" s="48"/>
-      <c r="B530" s="49"/>
-      <c r="C530" s="49"/>
-      <c r="F530" s="49"/>
-      <c r="AT530" s="52"/>
-      <c r="AY530" s="49"/>
-    </row>
-    <row r="531" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A531" s="48"/>
-      <c r="B531" s="49"/>
-      <c r="C531" s="49"/>
-      <c r="F531" s="49"/>
-      <c r="AT531" s="52"/>
-      <c r="AY531" s="49"/>
-    </row>
-    <row r="532" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A532" s="48"/>
-      <c r="B532" s="49"/>
-      <c r="C532" s="49"/>
-      <c r="F532" s="49"/>
-      <c r="AT532" s="52"/>
-      <c r="AY532" s="49"/>
-    </row>
-    <row r="533" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A533" s="48"/>
-      <c r="B533" s="49"/>
-      <c r="C533" s="49"/>
-      <c r="F533" s="49"/>
-      <c r="AT533" s="52"/>
-      <c r="AY533" s="49"/>
-    </row>
-    <row r="534" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A534" s="48"/>
-      <c r="B534" s="49"/>
-      <c r="C534" s="49"/>
-      <c r="F534" s="49"/>
-      <c r="AT534" s="52"/>
-      <c r="AY534" s="49"/>
-    </row>
-    <row r="535" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A535" s="48"/>
-      <c r="B535" s="49"/>
-      <c r="C535" s="49"/>
-      <c r="F535" s="49"/>
-      <c r="AT535" s="52"/>
-      <c r="AY535" s="49"/>
-    </row>
-    <row r="536" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A536" s="48"/>
-      <c r="B536" s="49"/>
-      <c r="C536" s="49"/>
-      <c r="F536" s="49"/>
-      <c r="AT536" s="52"/>
-      <c r="AY536" s="49"/>
-    </row>
-    <row r="537" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A537" s="48"/>
-      <c r="B537" s="49"/>
-      <c r="C537" s="49"/>
-      <c r="F537" s="49"/>
-      <c r="AT537" s="52"/>
-      <c r="AY537" s="49"/>
-    </row>
-    <row r="538" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A538" s="48"/>
-      <c r="B538" s="49"/>
-      <c r="C538" s="49"/>
-      <c r="F538" s="49"/>
-      <c r="AT538" s="52"/>
-      <c r="AY538" s="49"/>
-    </row>
-    <row r="539" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A539" s="48"/>
-      <c r="B539" s="49"/>
-      <c r="C539" s="49"/>
-      <c r="F539" s="49"/>
-      <c r="AT539" s="52"/>
-      <c r="AY539" s="49"/>
-    </row>
-    <row r="540" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A540" s="48"/>
-      <c r="B540" s="49"/>
-      <c r="C540" s="49"/>
-      <c r="F540" s="49"/>
-      <c r="AT540" s="52"/>
-      <c r="AY540" s="49"/>
-    </row>
-    <row r="541" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A541" s="48"/>
-      <c r="B541" s="49"/>
-      <c r="C541" s="49"/>
-      <c r="F541" s="49"/>
-      <c r="AT541" s="52"/>
-      <c r="AY541" s="49"/>
-    </row>
-    <row r="542" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A542" s="48"/>
-      <c r="B542" s="49"/>
-      <c r="C542" s="49"/>
-      <c r="F542" s="49"/>
-      <c r="AT542" s="52"/>
-      <c r="AY542" s="49"/>
-    </row>
-    <row r="543" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A543" s="48"/>
-      <c r="B543" s="49"/>
-      <c r="C543" s="49"/>
-      <c r="F543" s="49"/>
-      <c r="AT543" s="52"/>
-      <c r="AY543" s="49"/>
-    </row>
-    <row r="544" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A544" s="48"/>
-      <c r="B544" s="49"/>
-      <c r="C544" s="49"/>
-      <c r="F544" s="49"/>
-      <c r="AT544" s="52"/>
-      <c r="AY544" s="49"/>
-    </row>
-    <row r="545" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A545" s="48"/>
-      <c r="B545" s="49"/>
-      <c r="C545" s="49"/>
-      <c r="F545" s="49"/>
-      <c r="AT545" s="52"/>
-      <c r="AY545" s="49"/>
-    </row>
-    <row r="546" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A546" s="48"/>
-      <c r="B546" s="49"/>
-      <c r="C546" s="49"/>
-      <c r="F546" s="49"/>
-      <c r="AT546" s="52"/>
-      <c r="AY546" s="49"/>
-    </row>
-    <row r="547" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A547" s="48"/>
-      <c r="B547" s="49"/>
-      <c r="C547" s="49"/>
-      <c r="F547" s="49"/>
-      <c r="AT547" s="52"/>
-      <c r="AY547" s="49"/>
-    </row>
-    <row r="548" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A548" s="48"/>
-      <c r="B548" s="49"/>
-      <c r="C548" s="49"/>
-      <c r="F548" s="49"/>
-      <c r="AT548" s="52"/>
-      <c r="AY548" s="49"/>
-    </row>
-    <row r="549" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A549" s="48"/>
-      <c r="B549" s="49"/>
-      <c r="C549" s="49"/>
-      <c r="F549" s="49"/>
-      <c r="AT549" s="52"/>
-      <c r="AY549" s="49"/>
-    </row>
-    <row r="550" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A550" s="48"/>
-      <c r="B550" s="49"/>
-      <c r="C550" s="49"/>
-      <c r="F550" s="49"/>
-      <c r="AT550" s="52"/>
-      <c r="AY550" s="49"/>
-    </row>
-    <row r="551" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A551" s="48"/>
-      <c r="B551" s="49"/>
-      <c r="C551" s="49"/>
-      <c r="F551" s="49"/>
-      <c r="AT551" s="52"/>
-      <c r="AY551" s="49"/>
-    </row>
-    <row r="552" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A552" s="48"/>
-      <c r="B552" s="49"/>
-      <c r="C552" s="49"/>
-      <c r="F552" s="49"/>
-      <c r="AT552" s="52"/>
-      <c r="AY552" s="49"/>
-    </row>
-    <row r="553" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A553" s="48"/>
-      <c r="B553" s="49"/>
-      <c r="C553" s="49"/>
-      <c r="F553" s="49"/>
-      <c r="AT553" s="52"/>
-      <c r="AY553" s="49"/>
-    </row>
-    <row r="554" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A554" s="48"/>
-      <c r="B554" s="49"/>
-      <c r="C554" s="49"/>
-      <c r="F554" s="49"/>
-      <c r="AT554" s="52"/>
-      <c r="AY554" s="49"/>
-    </row>
-    <row r="555" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A555" s="48"/>
-      <c r="B555" s="49"/>
-      <c r="C555" s="49"/>
-      <c r="F555" s="49"/>
-      <c r="AT555" s="52"/>
-      <c r="AY555" s="49"/>
-    </row>
-    <row r="556" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A556" s="48"/>
-      <c r="B556" s="49"/>
-      <c r="C556" s="49"/>
-      <c r="F556" s="49"/>
-      <c r="AT556" s="52"/>
-      <c r="AY556" s="49"/>
-    </row>
-    <row r="557" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A557" s="48"/>
-      <c r="B557" s="49"/>
-      <c r="C557" s="49"/>
-      <c r="F557" s="49"/>
-      <c r="AT557" s="52"/>
-      <c r="AY557" s="49"/>
-    </row>
-    <row r="558" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A558" s="48"/>
-      <c r="B558" s="49"/>
-      <c r="C558" s="49"/>
-      <c r="F558" s="49"/>
-      <c r="AT558" s="52"/>
-      <c r="AY558" s="49"/>
-    </row>
-    <row r="559" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A559" s="48"/>
-      <c r="B559" s="49"/>
-      <c r="C559" s="49"/>
-      <c r="F559" s="49"/>
-      <c r="AT559" s="52"/>
-      <c r="AY559" s="49"/>
-    </row>
-    <row r="560" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A560" s="48"/>
-      <c r="B560" s="49"/>
-      <c r="C560" s="49"/>
-      <c r="F560" s="49"/>
-      <c r="AT560" s="52"/>
-      <c r="AY560" s="49"/>
-    </row>
-    <row r="561" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A561" s="48"/>
-      <c r="B561" s="49"/>
-      <c r="C561" s="49"/>
-      <c r="F561" s="49"/>
-      <c r="AT561" s="52"/>
-      <c r="AY561" s="49"/>
-    </row>
-    <row r="562" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A562" s="48"/>
-      <c r="B562" s="49"/>
-      <c r="C562" s="49"/>
-      <c r="F562" s="49"/>
-      <c r="AT562" s="52"/>
-      <c r="AY562" s="49"/>
-    </row>
-    <row r="563" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A563" s="48"/>
-      <c r="B563" s="49"/>
-      <c r="C563" s="49"/>
-      <c r="F563" s="49"/>
-      <c r="AT563" s="52"/>
-      <c r="AY563" s="49"/>
-    </row>
-    <row r="564" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A564" s="48"/>
-      <c r="B564" s="49"/>
-      <c r="C564" s="49"/>
-      <c r="F564" s="49"/>
-      <c r="AT564" s="52"/>
-      <c r="AY564" s="49"/>
-    </row>
-    <row r="565" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A565" s="48"/>
-      <c r="B565" s="49"/>
-      <c r="C565" s="49"/>
-      <c r="F565" s="49"/>
-      <c r="AT565" s="52"/>
-      <c r="AY565" s="49"/>
-    </row>
-    <row r="566" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A566" s="48"/>
-      <c r="B566" s="49"/>
-      <c r="C566" s="49"/>
-      <c r="F566" s="49"/>
-      <c r="AT566" s="52"/>
-      <c r="AY566" s="49"/>
-    </row>
-    <row r="567" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A567" s="48"/>
-      <c r="B567" s="49"/>
-      <c r="C567" s="49"/>
-      <c r="F567" s="49"/>
-      <c r="AT567" s="52"/>
-      <c r="AY567" s="49"/>
-    </row>
-    <row r="568" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A568" s="48"/>
-      <c r="B568" s="49"/>
-      <c r="C568" s="49"/>
-      <c r="F568" s="49"/>
-      <c r="AT568" s="52"/>
-      <c r="AY568" s="49"/>
-    </row>
-    <row r="569" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A569" s="48"/>
-      <c r="B569" s="49"/>
-      <c r="C569" s="49"/>
-      <c r="F569" s="49"/>
-      <c r="AT569" s="52"/>
-      <c r="AY569" s="49"/>
-    </row>
-    <row r="570" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A570" s="48"/>
-      <c r="B570" s="49"/>
-      <c r="C570" s="49"/>
-      <c r="F570" s="49"/>
-      <c r="AT570" s="52"/>
-      <c r="AY570" s="49"/>
-    </row>
-    <row r="571" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A571" s="48"/>
-      <c r="B571" s="49"/>
-      <c r="C571" s="49"/>
-      <c r="F571" s="49"/>
-      <c r="AT571" s="52"/>
-      <c r="AY571" s="49"/>
-    </row>
-    <row r="572" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A572" s="48"/>
-      <c r="B572" s="49"/>
-      <c r="C572" s="49"/>
-      <c r="F572" s="49"/>
-      <c r="AT572" s="52"/>
-      <c r="AY572" s="49"/>
-    </row>
-    <row r="573" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A573" s="48"/>
-      <c r="B573" s="49"/>
-      <c r="C573" s="49"/>
-      <c r="F573" s="49"/>
-      <c r="AT573" s="52"/>
-      <c r="AY573" s="49"/>
-    </row>
-    <row r="574" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A574" s="48"/>
-      <c r="B574" s="49"/>
-      <c r="C574" s="49"/>
-      <c r="F574" s="49"/>
-      <c r="AT574" s="52"/>
-      <c r="AY574" s="49"/>
-    </row>
-    <row r="575" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A575" s="48"/>
-      <c r="B575" s="49"/>
-      <c r="C575" s="49"/>
-      <c r="F575" s="49"/>
-      <c r="AT575" s="52"/>
-      <c r="AY575" s="49"/>
-    </row>
-    <row r="576" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A576" s="48"/>
-      <c r="B576" s="49"/>
-      <c r="C576" s="49"/>
-      <c r="F576" s="49"/>
-      <c r="AT576" s="52"/>
-      <c r="AY576" s="49"/>
-    </row>
-    <row r="577" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A577" s="48"/>
-      <c r="B577" s="49"/>
-      <c r="C577" s="49"/>
-      <c r="F577" s="49"/>
-      <c r="AT577" s="52"/>
-      <c r="AY577" s="49"/>
-    </row>
-    <row r="578" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A578" s="48"/>
-      <c r="B578" s="49"/>
-      <c r="C578" s="49"/>
-      <c r="F578" s="49"/>
-      <c r="AT578" s="52"/>
-      <c r="AY578" s="49"/>
-    </row>
-    <row r="579" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A579" s="48"/>
-      <c r="B579" s="49"/>
-      <c r="C579" s="49"/>
-      <c r="F579" s="49"/>
-      <c r="AT579" s="52"/>
-      <c r="AY579" s="49"/>
-    </row>
-    <row r="580" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A580" s="48"/>
-      <c r="B580" s="49"/>
-      <c r="C580" s="49"/>
-      <c r="F580" s="49"/>
-      <c r="AT580" s="52"/>
-      <c r="AY580" s="49"/>
-    </row>
-    <row r="581" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A581" s="48"/>
-      <c r="B581" s="49"/>
-      <c r="C581" s="49"/>
-      <c r="F581" s="49"/>
-      <c r="AT581" s="52"/>
-      <c r="AY581" s="49"/>
-    </row>
-    <row r="582" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A582" s="48"/>
-      <c r="B582" s="49"/>
-      <c r="C582" s="49"/>
-      <c r="F582" s="49"/>
-      <c r="AT582" s="52"/>
-      <c r="AY582" s="49"/>
-    </row>
-    <row r="583" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A583" s="48"/>
-      <c r="B583" s="49"/>
-      <c r="C583" s="49"/>
-      <c r="F583" s="49"/>
-      <c r="AT583" s="52"/>
-      <c r="AY583" s="49"/>
-    </row>
-    <row r="584" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A584" s="48"/>
-      <c r="B584" s="49"/>
-      <c r="C584" s="49"/>
-      <c r="F584" s="49"/>
-      <c r="AT584" s="52"/>
-      <c r="AY584" s="49"/>
-    </row>
-    <row r="585" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A585" s="48"/>
-      <c r="B585" s="49"/>
-      <c r="C585" s="49"/>
-      <c r="F585" s="49"/>
-      <c r="AT585" s="52"/>
-      <c r="AY585" s="49"/>
-    </row>
-    <row r="586" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A586" s="48"/>
-      <c r="B586" s="49"/>
-      <c r="C586" s="49"/>
-      <c r="F586" s="49"/>
-      <c r="AT586" s="52"/>
-      <c r="AY586" s="49"/>
-    </row>
-    <row r="587" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A587" s="48"/>
-      <c r="B587" s="49"/>
-      <c r="C587" s="49"/>
-      <c r="F587" s="49"/>
-      <c r="AT587" s="52"/>
-      <c r="AY587" s="49"/>
-    </row>
-    <row r="588" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A588" s="48"/>
-      <c r="B588" s="49"/>
-      <c r="C588" s="49"/>
-      <c r="F588" s="49"/>
-      <c r="AT588" s="52"/>
-      <c r="AY588" s="49"/>
-    </row>
-    <row r="589" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A589" s="48"/>
-      <c r="B589" s="49"/>
-      <c r="C589" s="49"/>
-      <c r="F589" s="49"/>
-      <c r="AT589" s="52"/>
-      <c r="AY589" s="49"/>
-    </row>
-    <row r="590" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A590" s="48"/>
-      <c r="B590" s="49"/>
-      <c r="C590" s="49"/>
-      <c r="F590" s="49"/>
-      <c r="AT590" s="52"/>
-      <c r="AY590" s="49"/>
-    </row>
-    <row r="591" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A591" s="48"/>
-      <c r="B591" s="49"/>
-      <c r="C591" s="49"/>
-      <c r="F591" s="49"/>
-      <c r="AT591" s="52"/>
-      <c r="AY591" s="49"/>
-    </row>
-    <row r="592" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A592" s="48"/>
-      <c r="B592" s="49"/>
-      <c r="C592" s="49"/>
-      <c r="F592" s="49"/>
-      <c r="AT592" s="52"/>
-      <c r="AY592" s="49"/>
-    </row>
-    <row r="593" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A593" s="48"/>
-      <c r="B593" s="49"/>
-      <c r="C593" s="49"/>
-      <c r="F593" s="49"/>
-      <c r="AT593" s="52"/>
-      <c r="AY593" s="49"/>
-    </row>
-    <row r="594" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A594" s="48"/>
-      <c r="B594" s="49"/>
-      <c r="C594" s="49"/>
-      <c r="F594" s="49"/>
-      <c r="AT594" s="52"/>
-      <c r="AY594" s="49"/>
-    </row>
-    <row r="595" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A595" s="48"/>
-      <c r="B595" s="49"/>
-      <c r="C595" s="49"/>
-      <c r="F595" s="49"/>
-      <c r="AT595" s="52"/>
-      <c r="AY595" s="49"/>
-    </row>
-    <row r="596" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A596" s="48"/>
-      <c r="B596" s="49"/>
-      <c r="C596" s="49"/>
-      <c r="F596" s="49"/>
-      <c r="AT596" s="52"/>
-      <c r="AY596" s="49"/>
-    </row>
-    <row r="597" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A597" s="48"/>
-      <c r="B597" s="49"/>
-      <c r="C597" s="49"/>
-      <c r="F597" s="49"/>
-      <c r="AT597" s="52"/>
-      <c r="AY597" s="49"/>
-    </row>
-    <row r="598" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A598" s="48"/>
-      <c r="B598" s="49"/>
-      <c r="C598" s="49"/>
-      <c r="F598" s="49"/>
-      <c r="AT598" s="52"/>
-      <c r="AY598" s="49"/>
-    </row>
-    <row r="599" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A599" s="48"/>
-      <c r="B599" s="49"/>
-      <c r="C599" s="49"/>
-      <c r="F599" s="49"/>
-      <c r="AT599" s="52"/>
-      <c r="AY599" s="49"/>
-    </row>
-    <row r="600" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A600" s="48"/>
-      <c r="B600" s="49"/>
-      <c r="C600" s="49"/>
-      <c r="F600" s="49"/>
-      <c r="AT600" s="52"/>
-      <c r="AY600" s="49"/>
-    </row>
-    <row r="601" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A601" s="48"/>
-      <c r="B601" s="49"/>
-      <c r="C601" s="49"/>
-      <c r="F601" s="49"/>
-      <c r="AT601" s="52"/>
-      <c r="AY601" s="49"/>
-    </row>
-    <row r="602" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A602" s="48"/>
-      <c r="B602" s="49"/>
-      <c r="C602" s="49"/>
-      <c r="F602" s="49"/>
-      <c r="AT602" s="52"/>
-      <c r="AY602" s="49"/>
-    </row>
-    <row r="603" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A603" s="48"/>
-      <c r="B603" s="49"/>
-      <c r="C603" s="49"/>
-      <c r="F603" s="49"/>
-      <c r="AT603" s="52"/>
-      <c r="AY603" s="49"/>
-    </row>
-    <row r="604" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A604" s="48"/>
-      <c r="B604" s="49"/>
-      <c r="C604" s="49"/>
-      <c r="F604" s="49"/>
-      <c r="AT604" s="52"/>
-      <c r="AY604" s="49"/>
-    </row>
-    <row r="605" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A605" s="48"/>
-      <c r="B605" s="49"/>
-      <c r="C605" s="49"/>
-      <c r="F605" s="49"/>
-      <c r="AT605" s="52"/>
-      <c r="AY605" s="49"/>
-    </row>
-    <row r="606" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A606" s="48"/>
-      <c r="B606" s="49"/>
-      <c r="C606" s="49"/>
-      <c r="F606" s="49"/>
-      <c r="AT606" s="52"/>
-      <c r="AY606" s="49"/>
-    </row>
-    <row r="607" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A607" s="48"/>
-      <c r="B607" s="49"/>
-      <c r="C607" s="49"/>
-      <c r="F607" s="49"/>
-      <c r="AT607" s="52"/>
-      <c r="AY607" s="49"/>
-    </row>
-    <row r="608" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A608" s="48"/>
-      <c r="B608" s="49"/>
-      <c r="C608" s="49"/>
-      <c r="F608" s="49"/>
-      <c r="AT608" s="52"/>
-      <c r="AY608" s="49"/>
-    </row>
-    <row r="609" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A609" s="48"/>
-      <c r="B609" s="49"/>
-      <c r="C609" s="49"/>
-      <c r="F609" s="49"/>
-      <c r="AT609" s="52"/>
-      <c r="AY609" s="49"/>
-    </row>
-    <row r="610" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A610" s="48"/>
-      <c r="B610" s="49"/>
-      <c r="C610" s="49"/>
-      <c r="F610" s="49"/>
-      <c r="AT610" s="52"/>
-      <c r="AY610" s="49"/>
-    </row>
-    <row r="611" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A611" s="48"/>
-      <c r="B611" s="49"/>
-      <c r="C611" s="49"/>
-      <c r="F611" s="49"/>
-      <c r="AT611" s="52"/>
-      <c r="AY611" s="49"/>
-    </row>
-    <row r="612" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A612" s="48"/>
-      <c r="B612" s="49"/>
-      <c r="C612" s="49"/>
-      <c r="F612" s="49"/>
-      <c r="AT612" s="52"/>
-      <c r="AY612" s="49"/>
-    </row>
-    <row r="613" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A613" s="48"/>
-      <c r="B613" s="49"/>
-      <c r="C613" s="49"/>
-      <c r="F613" s="49"/>
-      <c r="AT613" s="52"/>
-      <c r="AY613" s="49"/>
-    </row>
-    <row r="614" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A614" s="48"/>
-      <c r="B614" s="49"/>
-      <c r="C614" s="49"/>
-      <c r="F614" s="49"/>
-      <c r="AT614" s="52"/>
-      <c r="AY614" s="49"/>
-    </row>
-    <row r="615" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A615" s="48"/>
-      <c r="B615" s="49"/>
-      <c r="C615" s="49"/>
-      <c r="F615" s="49"/>
-      <c r="AT615" s="52"/>
-      <c r="AY615" s="49"/>
-    </row>
-    <row r="616" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A616" s="48"/>
-      <c r="B616" s="49"/>
-      <c r="C616" s="49"/>
-      <c r="F616" s="49"/>
-      <c r="AT616" s="52"/>
-      <c r="AY616" s="49"/>
-    </row>
-    <row r="617" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A617" s="48"/>
-      <c r="B617" s="49"/>
-      <c r="C617" s="49"/>
-      <c r="F617" s="49"/>
-      <c r="AT617" s="52"/>
-      <c r="AY617" s="49"/>
-    </row>
-    <row r="618" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A618" s="48"/>
-      <c r="B618" s="49"/>
-      <c r="C618" s="49"/>
-      <c r="F618" s="49"/>
-      <c r="AT618" s="52"/>
-      <c r="AY618" s="49"/>
-    </row>
-    <row r="619" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A619" s="48"/>
-      <c r="B619" s="49"/>
-      <c r="C619" s="49"/>
-      <c r="F619" s="49"/>
-      <c r="AT619" s="52"/>
-      <c r="AY619" s="49"/>
-    </row>
-    <row r="620" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A620" s="48"/>
-      <c r="B620" s="49"/>
-      <c r="C620" s="49"/>
-      <c r="F620" s="49"/>
-      <c r="AT620" s="52"/>
-      <c r="AY620" s="49"/>
-    </row>
-    <row r="621" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A621" s="48"/>
-      <c r="B621" s="49"/>
-      <c r="C621" s="49"/>
-      <c r="F621" s="49"/>
-      <c r="AT621" s="52"/>
-      <c r="AY621" s="49"/>
-    </row>
-    <row r="622" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A622" s="48"/>
-      <c r="B622" s="49"/>
-      <c r="C622" s="49"/>
-      <c r="F622" s="49"/>
-      <c r="AT622" s="52"/>
-      <c r="AY622" s="49"/>
-    </row>
-    <row r="623" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A623" s="48"/>
-      <c r="B623" s="49"/>
-      <c r="C623" s="49"/>
-      <c r="F623" s="49"/>
-      <c r="AT623" s="52"/>
-      <c r="AY623" s="49"/>
-    </row>
-    <row r="624" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A624" s="48"/>
-      <c r="B624" s="49"/>
-      <c r="C624" s="49"/>
-      <c r="F624" s="49"/>
-      <c r="AT624" s="52"/>
-      <c r="AY624" s="49"/>
-    </row>
-    <row r="625" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A625" s="48"/>
-      <c r="B625" s="49"/>
-      <c r="C625" s="49"/>
-      <c r="F625" s="49"/>
-      <c r="AT625" s="52"/>
-      <c r="AY625" s="49"/>
-    </row>
-    <row r="626" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A626" s="48"/>
-      <c r="B626" s="49"/>
-      <c r="C626" s="49"/>
-      <c r="F626" s="49"/>
-      <c r="AT626" s="52"/>
-      <c r="AY626" s="49"/>
-    </row>
-    <row r="627" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A627" s="48"/>
-      <c r="B627" s="49"/>
-      <c r="C627" s="49"/>
-      <c r="F627" s="49"/>
-      <c r="AT627" s="52"/>
-      <c r="AY627" s="49"/>
-    </row>
-    <row r="628" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A628" s="48"/>
-      <c r="B628" s="49"/>
-      <c r="C628" s="49"/>
-      <c r="F628" s="49"/>
-      <c r="AT628" s="52"/>
-      <c r="AY628" s="49"/>
-    </row>
-    <row r="629" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A629" s="48"/>
-      <c r="B629" s="49"/>
-      <c r="C629" s="49"/>
-      <c r="F629" s="49"/>
-      <c r="AT629" s="52"/>
-      <c r="AY629" s="49"/>
-    </row>
-    <row r="630" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A630" s="48"/>
-      <c r="B630" s="49"/>
-      <c r="C630" s="49"/>
-      <c r="F630" s="49"/>
-      <c r="AT630" s="52"/>
-      <c r="AY630" s="49"/>
-    </row>
-    <row r="631" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A631" s="48"/>
-      <c r="B631" s="49"/>
-      <c r="C631" s="49"/>
-      <c r="F631" s="49"/>
-      <c r="AT631" s="52"/>
-      <c r="AY631" s="49"/>
-    </row>
-    <row r="632" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A632" s="48"/>
-      <c r="B632" s="49"/>
-      <c r="C632" s="49"/>
-      <c r="F632" s="49"/>
-      <c r="AT632" s="52"/>
-      <c r="AY632" s="49"/>
-    </row>
-    <row r="633" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A633" s="48"/>
-      <c r="B633" s="49"/>
-      <c r="C633" s="49"/>
-      <c r="F633" s="49"/>
-      <c r="AT633" s="52"/>
-      <c r="AY633" s="49"/>
-    </row>
-    <row r="634" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A634" s="48"/>
-      <c r="B634" s="49"/>
-      <c r="C634" s="49"/>
-      <c r="F634" s="49"/>
-      <c r="AT634" s="52"/>
-      <c r="AY634" s="49"/>
-    </row>
-    <row r="635" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A635" s="48"/>
-      <c r="B635" s="49"/>
-      <c r="C635" s="49"/>
-      <c r="F635" s="49"/>
-      <c r="AT635" s="52"/>
-      <c r="AY635" s="49"/>
-    </row>
-    <row r="636" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A636" s="48"/>
-      <c r="B636" s="49"/>
-      <c r="C636" s="49"/>
-      <c r="F636" s="49"/>
-      <c r="AT636" s="52"/>
-      <c r="AY636" s="49"/>
-    </row>
-    <row r="637" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A637" s="48"/>
-      <c r="B637" s="49"/>
-      <c r="C637" s="49"/>
-      <c r="F637" s="49"/>
-      <c r="AT637" s="52"/>
-      <c r="AY637" s="49"/>
-    </row>
-    <row r="638" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A638" s="48"/>
-      <c r="B638" s="49"/>
-      <c r="C638" s="49"/>
-      <c r="F638" s="49"/>
-      <c r="AT638" s="52"/>
-      <c r="AY638" s="49"/>
-    </row>
-    <row r="639" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A639" s="48"/>
-      <c r="B639" s="49"/>
-      <c r="C639" s="49"/>
-      <c r="F639" s="49"/>
-      <c r="AT639" s="52"/>
-      <c r="AY639" s="49"/>
-    </row>
-    <row r="640" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A640" s="48"/>
-      <c r="B640" s="49"/>
-      <c r="C640" s="49"/>
-      <c r="F640" s="49"/>
-      <c r="AT640" s="52"/>
-      <c r="AY640" s="49"/>
-    </row>
-    <row r="641" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A641" s="48"/>
-      <c r="B641" s="49"/>
-      <c r="C641" s="49"/>
-      <c r="F641" s="49"/>
-      <c r="AT641" s="52"/>
-      <c r="AY641" s="49"/>
-    </row>
-    <row r="642" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A642" s="48"/>
-      <c r="B642" s="49"/>
-      <c r="C642" s="49"/>
-      <c r="F642" s="49"/>
-      <c r="AT642" s="52"/>
-      <c r="AY642" s="49"/>
-    </row>
-    <row r="643" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A643" s="48"/>
-      <c r="B643" s="49"/>
-      <c r="C643" s="49"/>
-      <c r="F643" s="49"/>
-      <c r="AT643" s="52"/>
-      <c r="AY643" s="49"/>
-    </row>
-    <row r="644" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A644" s="48"/>
-      <c r="B644" s="49"/>
-      <c r="C644" s="49"/>
-      <c r="F644" s="49"/>
-      <c r="AT644" s="52"/>
-      <c r="AY644" s="49"/>
-    </row>
-    <row r="645" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A645" s="48"/>
-      <c r="B645" s="49"/>
-      <c r="C645" s="49"/>
-      <c r="F645" s="49"/>
-      <c r="AT645" s="52"/>
-      <c r="AY645" s="49"/>
-    </row>
-    <row r="646" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A646" s="48"/>
-      <c r="B646" s="49"/>
-      <c r="C646" s="49"/>
-      <c r="F646" s="49"/>
-      <c r="AT646" s="52"/>
-      <c r="AY646" s="49"/>
-    </row>
-    <row r="647" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A647" s="48"/>
-      <c r="B647" s="49"/>
-      <c r="C647" s="49"/>
-      <c r="F647" s="49"/>
-      <c r="AT647" s="52"/>
-      <c r="AY647" s="49"/>
-    </row>
-    <row r="648" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A648" s="48"/>
-      <c r="B648" s="49"/>
-      <c r="C648" s="49"/>
-      <c r="F648" s="49"/>
-      <c r="AT648" s="52"/>
-      <c r="AY648" s="49"/>
-    </row>
-    <row r="649" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A649" s="48"/>
-      <c r="B649" s="49"/>
-      <c r="C649" s="49"/>
-      <c r="F649" s="49"/>
-      <c r="AT649" s="52"/>
-      <c r="AY649" s="49"/>
-    </row>
-    <row r="650" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A650" s="48"/>
-      <c r="B650" s="49"/>
-      <c r="C650" s="49"/>
-      <c r="F650" s="49"/>
-      <c r="AT650" s="52"/>
-      <c r="AY650" s="49"/>
-    </row>
-    <row r="651" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A651" s="48"/>
-      <c r="B651" s="49"/>
-      <c r="C651" s="49"/>
-      <c r="F651" s="49"/>
-      <c r="AT651" s="52"/>
-      <c r="AY651" s="49"/>
-    </row>
-    <row r="652" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A652" s="48"/>
-      <c r="B652" s="49"/>
-      <c r="C652" s="49"/>
-      <c r="F652" s="49"/>
-      <c r="AT652" s="52"/>
-      <c r="AY652" s="49"/>
-    </row>
-    <row r="653" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A653" s="48"/>
-      <c r="B653" s="49"/>
-      <c r="C653" s="49"/>
-      <c r="F653" s="49"/>
-      <c r="AT653" s="52"/>
-      <c r="AY653" s="49"/>
-    </row>
-    <row r="654" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A654" s="48"/>
-      <c r="B654" s="49"/>
-      <c r="C654" s="49"/>
-      <c r="F654" s="49"/>
-      <c r="AT654" s="52"/>
-      <c r="AY654" s="49"/>
-    </row>
-    <row r="655" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A655" s="48"/>
-      <c r="B655" s="49"/>
-      <c r="C655" s="49"/>
-      <c r="F655" s="49"/>
-      <c r="AT655" s="52"/>
-      <c r="AY655" s="49"/>
-    </row>
-    <row r="656" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A656" s="48"/>
-      <c r="B656" s="49"/>
-      <c r="C656" s="49"/>
-      <c r="F656" s="49"/>
-      <c r="AT656" s="52"/>
-      <c r="AY656" s="49"/>
-    </row>
-    <row r="657" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A657" s="48"/>
-      <c r="B657" s="49"/>
-      <c r="C657" s="49"/>
-      <c r="F657" s="49"/>
-      <c r="AT657" s="52"/>
-      <c r="AY657" s="49"/>
-    </row>
-    <row r="658" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A658" s="48"/>
-      <c r="B658" s="49"/>
-      <c r="C658" s="49"/>
-      <c r="F658" s="49"/>
-      <c r="AT658" s="52"/>
-      <c r="AY658" s="49"/>
-    </row>
-    <row r="659" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A659" s="48"/>
-      <c r="B659" s="49"/>
-      <c r="C659" s="49"/>
-      <c r="F659" s="49"/>
-      <c r="AT659" s="52"/>
-      <c r="AY659" s="49"/>
-    </row>
-    <row r="660" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A660" s="48"/>
-      <c r="B660" s="49"/>
-      <c r="C660" s="49"/>
-      <c r="F660" s="49"/>
-      <c r="AT660" s="52"/>
-      <c r="AY660" s="49"/>
-    </row>
-    <row r="661" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A661" s="48"/>
-      <c r="B661" s="49"/>
-      <c r="C661" s="49"/>
-      <c r="F661" s="49"/>
-      <c r="AT661" s="52"/>
-      <c r="AY661" s="49"/>
-    </row>
-    <row r="662" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A662" s="48"/>
-      <c r="B662" s="49"/>
-      <c r="C662" s="49"/>
-      <c r="F662" s="49"/>
-      <c r="AT662" s="52"/>
-      <c r="AY662" s="49"/>
-    </row>
-    <row r="663" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A663" s="48"/>
-      <c r="B663" s="49"/>
-      <c r="C663" s="49"/>
-      <c r="F663" s="49"/>
-      <c r="AT663" s="52"/>
-      <c r="AY663" s="49"/>
-    </row>
-    <row r="664" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A664" s="48"/>
-      <c r="B664" s="49"/>
-      <c r="C664" s="49"/>
-      <c r="F664" s="49"/>
-      <c r="AT664" s="52"/>
-      <c r="AY664" s="49"/>
-    </row>
-    <row r="665" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A665" s="48"/>
-      <c r="B665" s="49"/>
-      <c r="C665" s="49"/>
-      <c r="F665" s="49"/>
-      <c r="AT665" s="52"/>
-      <c r="AY665" s="49"/>
-    </row>
-    <row r="666" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A666" s="48"/>
-      <c r="B666" s="49"/>
-      <c r="C666" s="49"/>
-      <c r="F666" s="49"/>
-      <c r="AT666" s="52"/>
-      <c r="AY666" s="49"/>
-    </row>
-    <row r="667" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A667" s="48"/>
-      <c r="B667" s="49"/>
-      <c r="C667" s="49"/>
-      <c r="F667" s="49"/>
-      <c r="AT667" s="52"/>
-      <c r="AY667" s="49"/>
-    </row>
-    <row r="668" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A668" s="48"/>
-      <c r="B668" s="49"/>
-      <c r="C668" s="49"/>
-      <c r="F668" s="49"/>
-      <c r="AT668" s="52"/>
-      <c r="AY668" s="49"/>
-    </row>
-    <row r="669" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A669" s="48"/>
-      <c r="B669" s="49"/>
-      <c r="C669" s="49"/>
-      <c r="F669" s="49"/>
-      <c r="AT669" s="52"/>
-      <c r="AY669" s="49"/>
-    </row>
-    <row r="670" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A670" s="48"/>
-      <c r="B670" s="49"/>
-      <c r="C670" s="49"/>
-      <c r="F670" s="49"/>
-      <c r="AT670" s="52"/>
-      <c r="AY670" s="49"/>
-    </row>
-    <row r="671" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A671" s="48"/>
-      <c r="B671" s="49"/>
-      <c r="C671" s="49"/>
-      <c r="F671" s="49"/>
-      <c r="AT671" s="52"/>
-      <c r="AY671" s="49"/>
-    </row>
-    <row r="672" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A672" s="48"/>
-      <c r="B672" s="49"/>
-      <c r="C672" s="49"/>
-      <c r="F672" s="49"/>
-      <c r="AT672" s="52"/>
-      <c r="AY672" s="49"/>
-    </row>
-    <row r="673" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A673" s="48"/>
-      <c r="B673" s="49"/>
-      <c r="C673" s="49"/>
-      <c r="F673" s="49"/>
-      <c r="AT673" s="52"/>
-      <c r="AY673" s="49"/>
-    </row>
-    <row r="674" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A674" s="48"/>
-      <c r="B674" s="49"/>
-      <c r="C674" s="49"/>
-      <c r="F674" s="49"/>
-      <c r="AT674" s="52"/>
-      <c r="AY674" s="49"/>
-    </row>
-    <row r="675" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A675" s="48"/>
-      <c r="B675" s="49"/>
-      <c r="C675" s="49"/>
-      <c r="F675" s="49"/>
-      <c r="AT675" s="52"/>
-      <c r="AY675" s="49"/>
-    </row>
-    <row r="676" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A676" s="48"/>
-      <c r="B676" s="49"/>
-      <c r="C676" s="49"/>
-      <c r="F676" s="49"/>
-      <c r="AT676" s="52"/>
-      <c r="AY676" s="49"/>
-    </row>
-    <row r="677" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A677" s="48"/>
-      <c r="B677" s="49"/>
-      <c r="C677" s="49"/>
-      <c r="F677" s="49"/>
-      <c r="AT677" s="52"/>
-      <c r="AY677" s="49"/>
-    </row>
-    <row r="678" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A678" s="48"/>
-      <c r="B678" s="49"/>
-      <c r="C678" s="49"/>
-      <c r="F678" s="49"/>
-      <c r="AT678" s="52"/>
-      <c r="AY678" s="49"/>
-    </row>
-    <row r="679" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A679" s="48"/>
-      <c r="B679" s="49"/>
-      <c r="C679" s="49"/>
-      <c r="F679" s="49"/>
-      <c r="AT679" s="52"/>
-      <c r="AY679" s="49"/>
-    </row>
-    <row r="680" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A680" s="48"/>
-      <c r="B680" s="49"/>
-      <c r="C680" s="49"/>
-      <c r="F680" s="49"/>
-      <c r="AT680" s="52"/>
-      <c r="AY680" s="49"/>
-    </row>
-    <row r="681" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A681" s="48"/>
-      <c r="B681" s="49"/>
-      <c r="C681" s="49"/>
-      <c r="F681" s="49"/>
-      <c r="AT681" s="52"/>
-      <c r="AY681" s="49"/>
-    </row>
-    <row r="682" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A682" s="48"/>
-      <c r="B682" s="49"/>
-      <c r="C682" s="49"/>
-      <c r="F682" s="49"/>
-      <c r="AT682" s="52"/>
-      <c r="AY682" s="49"/>
-    </row>
-    <row r="683" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A683" s="48"/>
-      <c r="B683" s="49"/>
-      <c r="C683" s="49"/>
-      <c r="F683" s="49"/>
-      <c r="AT683" s="52"/>
-      <c r="AY683" s="49"/>
-    </row>
-    <row r="684" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A684" s="48"/>
-      <c r="B684" s="49"/>
-      <c r="C684" s="49"/>
-      <c r="F684" s="49"/>
-      <c r="AT684" s="52"/>
-      <c r="AY684" s="49"/>
-    </row>
-    <row r="685" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A685" s="48"/>
-      <c r="B685" s="49"/>
-      <c r="C685" s="49"/>
-      <c r="F685" s="49"/>
-      <c r="AT685" s="52"/>
-      <c r="AY685" s="49"/>
-    </row>
-    <row r="686" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A686" s="48"/>
-      <c r="B686" s="49"/>
-      <c r="C686" s="49"/>
-      <c r="F686" s="49"/>
-      <c r="AT686" s="52"/>
-      <c r="AY686" s="49"/>
-    </row>
-    <row r="687" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A687" s="48"/>
-      <c r="B687" s="49"/>
-      <c r="C687" s="49"/>
-      <c r="F687" s="49"/>
-      <c r="AT687" s="52"/>
-      <c r="AY687" s="49"/>
-    </row>
-    <row r="688" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A688" s="48"/>
-      <c r="B688" s="49"/>
-      <c r="C688" s="49"/>
-      <c r="F688" s="49"/>
-      <c r="AT688" s="52"/>
-      <c r="AY688" s="49"/>
-    </row>
-    <row r="689" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A689" s="48"/>
-      <c r="B689" s="49"/>
-      <c r="C689" s="49"/>
-      <c r="F689" s="49"/>
-      <c r="AT689" s="52"/>
-      <c r="AY689" s="49"/>
-    </row>
-    <row r="690" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A690" s="48"/>
-      <c r="B690" s="49"/>
-      <c r="C690" s="49"/>
-      <c r="F690" s="49"/>
-      <c r="AT690" s="52"/>
-      <c r="AY690" s="49"/>
-    </row>
-    <row r="691" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A691" s="48"/>
-      <c r="B691" s="49"/>
-      <c r="C691" s="49"/>
-      <c r="F691" s="49"/>
-      <c r="AT691" s="52"/>
-      <c r="AY691" s="49"/>
-    </row>
-    <row r="692" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A692" s="48"/>
-      <c r="B692" s="49"/>
-      <c r="C692" s="49"/>
-      <c r="F692" s="49"/>
-      <c r="AT692" s="52"/>
-      <c r="AY692" s="49"/>
-    </row>
-    <row r="693" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A693" s="48"/>
-      <c r="B693" s="49"/>
-      <c r="C693" s="49"/>
-      <c r="F693" s="49"/>
-      <c r="AT693" s="52"/>
-      <c r="AY693" s="49"/>
-    </row>
-    <row r="694" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A694" s="48"/>
-      <c r="B694" s="49"/>
-      <c r="C694" s="49"/>
-      <c r="F694" s="49"/>
-      <c r="AT694" s="52"/>
-      <c r="AY694" s="49"/>
-    </row>
-    <row r="695" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A695" s="48"/>
-      <c r="B695" s="49"/>
-      <c r="C695" s="49"/>
-      <c r="F695" s="49"/>
-      <c r="AT695" s="52"/>
-      <c r="AY695" s="49"/>
-    </row>
-    <row r="696" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A696" s="48"/>
-      <c r="B696" s="49"/>
-      <c r="C696" s="49"/>
-      <c r="F696" s="49"/>
-      <c r="AT696" s="52"/>
-      <c r="AY696" s="49"/>
-    </row>
-    <row r="697" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A697" s="48"/>
-      <c r="B697" s="49"/>
-      <c r="C697" s="49"/>
-      <c r="F697" s="49"/>
-      <c r="AT697" s="52"/>
-      <c r="AY697" s="49"/>
-    </row>
-    <row r="698" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A698" s="48"/>
-      <c r="B698" s="49"/>
-      <c r="C698" s="49"/>
-      <c r="F698" s="49"/>
-      <c r="AT698" s="52"/>
-      <c r="AY698" s="49"/>
-    </row>
-    <row r="699" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A699" s="48"/>
-      <c r="B699" s="49"/>
-      <c r="C699" s="49"/>
-      <c r="F699" s="49"/>
-      <c r="AT699" s="52"/>
-      <c r="AY699" s="49"/>
-    </row>
-    <row r="700" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A700" s="48"/>
-      <c r="B700" s="49"/>
-      <c r="C700" s="49"/>
-      <c r="F700" s="49"/>
-      <c r="AT700" s="52"/>
-      <c r="AY700" s="49"/>
-    </row>
-    <row r="701" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A701" s="48"/>
-      <c r="B701" s="49"/>
-      <c r="C701" s="49"/>
-      <c r="F701" s="49"/>
-      <c r="AT701" s="52"/>
-      <c r="AY701" s="49"/>
-    </row>
-    <row r="702" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A702" s="48"/>
-      <c r="B702" s="49"/>
-      <c r="C702" s="49"/>
-      <c r="F702" s="49"/>
-      <c r="AT702" s="52"/>
-      <c r="AY702" s="49"/>
-    </row>
-    <row r="703" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A703" s="48"/>
-      <c r="B703" s="49"/>
-      <c r="C703" s="49"/>
-      <c r="F703" s="49"/>
-      <c r="AT703" s="52"/>
-      <c r="AY703" s="49"/>
-    </row>
-    <row r="704" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A704" s="48"/>
-      <c r="B704" s="49"/>
-      <c r="C704" s="49"/>
-      <c r="F704" s="49"/>
-      <c r="AT704" s="52"/>
-      <c r="AY704" s="49"/>
-    </row>
-    <row r="705" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A705" s="48"/>
-      <c r="B705" s="49"/>
-      <c r="C705" s="49"/>
-      <c r="F705" s="49"/>
-      <c r="AT705" s="52"/>
-      <c r="AY705" s="49"/>
-    </row>
-    <row r="706" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A706" s="48"/>
-      <c r="B706" s="49"/>
-      <c r="C706" s="49"/>
-      <c r="F706" s="49"/>
-      <c r="AT706" s="52"/>
-      <c r="AY706" s="49"/>
-    </row>
-    <row r="707" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A707" s="48"/>
-      <c r="B707" s="49"/>
-      <c r="C707" s="49"/>
-      <c r="F707" s="49"/>
-      <c r="AT707" s="52"/>
-      <c r="AY707" s="49"/>
-    </row>
-    <row r="708" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A708" s="48"/>
-      <c r="B708" s="49"/>
-      <c r="C708" s="49"/>
-      <c r="F708" s="49"/>
-      <c r="AT708" s="52"/>
-      <c r="AY708" s="49"/>
-    </row>
-    <row r="709" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A709" s="48"/>
-      <c r="B709" s="49"/>
-      <c r="C709" s="49"/>
-      <c r="F709" s="49"/>
-      <c r="AT709" s="52"/>
-      <c r="AY709" s="49"/>
-    </row>
-    <row r="710" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A710" s="48"/>
-      <c r="B710" s="49"/>
-      <c r="C710" s="49"/>
-      <c r="F710" s="49"/>
-      <c r="AT710" s="52"/>
-      <c r="AY710" s="49"/>
-    </row>
-    <row r="711" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A711" s="48"/>
-      <c r="B711" s="49"/>
-      <c r="C711" s="49"/>
-      <c r="F711" s="49"/>
-      <c r="AT711" s="52"/>
-      <c r="AY711" s="49"/>
-    </row>
-    <row r="712" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A712" s="48"/>
-      <c r="B712" s="49"/>
-      <c r="C712" s="49"/>
-      <c r="F712" s="49"/>
-      <c r="AT712" s="52"/>
-      <c r="AY712" s="49"/>
-    </row>
-    <row r="713" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A713" s="48"/>
-      <c r="B713" s="49"/>
-      <c r="C713" s="49"/>
-      <c r="F713" s="49"/>
-      <c r="AT713" s="52"/>
-      <c r="AY713" s="49"/>
-    </row>
-    <row r="714" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A714" s="48"/>
-      <c r="B714" s="49"/>
-      <c r="C714" s="49"/>
-      <c r="F714" s="49"/>
-      <c r="AT714" s="52"/>
-      <c r="AY714" s="49"/>
-    </row>
-    <row r="715" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A715" s="48"/>
-      <c r="B715" s="49"/>
-      <c r="C715" s="49"/>
-      <c r="F715" s="49"/>
-      <c r="AT715" s="52"/>
-      <c r="AY715" s="49"/>
-    </row>
-    <row r="716" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A716" s="48"/>
-      <c r="B716" s="49"/>
-      <c r="C716" s="49"/>
-      <c r="F716" s="49"/>
-      <c r="AT716" s="52"/>
-      <c r="AY716" s="49"/>
-    </row>
-    <row r="717" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A717" s="48"/>
-      <c r="B717" s="49"/>
-      <c r="C717" s="49"/>
-      <c r="F717" s="49"/>
-      <c r="AT717" s="52"/>
-      <c r="AY717" s="49"/>
-    </row>
-    <row r="718" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A718" s="48"/>
-      <c r="B718" s="49"/>
-      <c r="C718" s="49"/>
-      <c r="F718" s="49"/>
-      <c r="AT718" s="52"/>
-      <c r="AY718" s="49"/>
-    </row>
-    <row r="719" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A719" s="48"/>
-      <c r="B719" s="49"/>
-      <c r="C719" s="49"/>
-      <c r="F719" s="49"/>
-      <c r="AT719" s="52"/>
-      <c r="AY719" s="49"/>
-    </row>
-    <row r="720" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A720" s="48"/>
-      <c r="B720" s="49"/>
-      <c r="C720" s="49"/>
-      <c r="F720" s="49"/>
-      <c r="AT720" s="52"/>
-      <c r="AY720" s="49"/>
-    </row>
-    <row r="721" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A721" s="48"/>
-      <c r="B721" s="49"/>
-      <c r="C721" s="49"/>
-      <c r="F721" s="49"/>
-      <c r="AT721" s="52"/>
-      <c r="AY721" s="49"/>
-    </row>
-    <row r="722" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A722" s="48"/>
-      <c r="B722" s="49"/>
-      <c r="C722" s="49"/>
-      <c r="F722" s="49"/>
-      <c r="AT722" s="52"/>
-      <c r="AY722" s="49"/>
-    </row>
-    <row r="723" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A723" s="48"/>
-      <c r="B723" s="49"/>
-      <c r="C723" s="49"/>
-      <c r="F723" s="49"/>
-      <c r="AT723" s="52"/>
-      <c r="AY723" s="49"/>
-    </row>
-    <row r="724" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A724" s="48"/>
-      <c r="B724" s="49"/>
-      <c r="C724" s="49"/>
-      <c r="F724" s="49"/>
-      <c r="AT724" s="52"/>
-      <c r="AY724" s="49"/>
-    </row>
-    <row r="725" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A725" s="48"/>
-      <c r="B725" s="49"/>
-      <c r="C725" s="49"/>
-      <c r="F725" s="49"/>
-      <c r="AT725" s="52"/>
-      <c r="AY725" s="49"/>
-    </row>
-    <row r="726" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A726" s="48"/>
-      <c r="B726" s="49"/>
-      <c r="C726" s="49"/>
-      <c r="F726" s="49"/>
-      <c r="AT726" s="52"/>
-      <c r="AY726" s="49"/>
-    </row>
-    <row r="727" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A727" s="48"/>
-      <c r="B727" s="49"/>
-      <c r="C727" s="49"/>
-      <c r="F727" s="49"/>
-      <c r="AT727" s="52"/>
-      <c r="AY727" s="49"/>
-    </row>
-    <row r="728" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A728" s="48"/>
-      <c r="B728" s="49"/>
-      <c r="C728" s="49"/>
-      <c r="F728" s="49"/>
-      <c r="AT728" s="52"/>
-      <c r="AY728" s="49"/>
-    </row>
-    <row r="729" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A729" s="48"/>
-      <c r="B729" s="49"/>
-      <c r="C729" s="49"/>
-      <c r="F729" s="49"/>
-      <c r="AT729" s="52"/>
-      <c r="AY729" s="49"/>
-    </row>
-    <row r="730" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A730" s="48"/>
-      <c r="B730" s="49"/>
-      <c r="C730" s="49"/>
-      <c r="F730" s="49"/>
-      <c r="AT730" s="52"/>
-      <c r="AY730" s="49"/>
-    </row>
-    <row r="731" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A731" s="48"/>
-      <c r="B731" s="49"/>
-      <c r="C731" s="49"/>
-      <c r="F731" s="49"/>
-      <c r="AT731" s="52"/>
-      <c r="AY731" s="49"/>
-    </row>
-    <row r="732" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A732" s="48"/>
-      <c r="B732" s="49"/>
-      <c r="C732" s="49"/>
-      <c r="F732" s="49"/>
-      <c r="AT732" s="52"/>
-      <c r="AY732" s="49"/>
-    </row>
-    <row r="733" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A733" s="48"/>
-      <c r="B733" s="49"/>
-      <c r="C733" s="49"/>
-      <c r="F733" s="49"/>
-      <c r="AT733" s="52"/>
-      <c r="AY733" s="49"/>
-    </row>
-    <row r="734" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A734" s="48"/>
-      <c r="B734" s="49"/>
-      <c r="C734" s="49"/>
-      <c r="F734" s="49"/>
-      <c r="AT734" s="52"/>
-      <c r="AY734" s="49"/>
-    </row>
-    <row r="735" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A735" s="48"/>
-      <c r="B735" s="49"/>
-      <c r="C735" s="49"/>
-      <c r="F735" s="49"/>
-      <c r="AT735" s="52"/>
-      <c r="AY735" s="49"/>
-    </row>
-    <row r="736" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A736" s="48"/>
-      <c r="B736" s="49"/>
-      <c r="C736" s="49"/>
-      <c r="F736" s="49"/>
-      <c r="AT736" s="52"/>
-      <c r="AY736" s="49"/>
-    </row>
-    <row r="737" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A737" s="48"/>
-      <c r="B737" s="49"/>
-      <c r="C737" s="49"/>
-      <c r="F737" s="49"/>
-      <c r="AT737" s="52"/>
-      <c r="AY737" s="49"/>
-    </row>
-    <row r="738" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A738" s="48"/>
-      <c r="B738" s="49"/>
-      <c r="C738" s="49"/>
-      <c r="F738" s="49"/>
-      <c r="AT738" s="52"/>
-      <c r="AY738" s="49"/>
-    </row>
-    <row r="739" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A739" s="48"/>
-      <c r="B739" s="49"/>
-      <c r="C739" s="49"/>
-      <c r="F739" s="49"/>
-      <c r="AT739" s="52"/>
-      <c r="AY739" s="49"/>
-    </row>
-    <row r="740" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A740" s="48"/>
-      <c r="B740" s="49"/>
-      <c r="C740" s="49"/>
-      <c r="F740" s="49"/>
-      <c r="AT740" s="52"/>
-      <c r="AY740" s="49"/>
-    </row>
-    <row r="741" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A741" s="48"/>
-      <c r="B741" s="49"/>
-      <c r="C741" s="49"/>
-      <c r="F741" s="49"/>
-      <c r="AT741" s="52"/>
-      <c r="AY741" s="49"/>
-    </row>
-    <row r="742" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A742" s="48"/>
-      <c r="B742" s="49"/>
-      <c r="C742" s="49"/>
-      <c r="F742" s="49"/>
-      <c r="AT742" s="52"/>
-      <c r="AY742" s="49"/>
-    </row>
-    <row r="743" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A743" s="48"/>
-      <c r="B743" s="49"/>
-      <c r="C743" s="49"/>
-      <c r="F743" s="49"/>
-      <c r="AT743" s="52"/>
-      <c r="AY743" s="49"/>
-    </row>
-    <row r="744" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A744" s="48"/>
-      <c r="B744" s="49"/>
-      <c r="C744" s="49"/>
-      <c r="F744" s="49"/>
-      <c r="AT744" s="52"/>
-      <c r="AY744" s="49"/>
-    </row>
-    <row r="745" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A745" s="48"/>
-      <c r="B745" s="49"/>
-      <c r="C745" s="49"/>
-      <c r="F745" s="49"/>
-      <c r="AT745" s="52"/>
-      <c r="AY745" s="49"/>
-    </row>
-    <row r="746" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A746" s="48"/>
-      <c r="B746" s="49"/>
-      <c r="C746" s="49"/>
-      <c r="F746" s="49"/>
-      <c r="AT746" s="52"/>
-      <c r="AY746" s="49"/>
-    </row>
-    <row r="747" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A747" s="48"/>
-      <c r="B747" s="49"/>
-      <c r="C747" s="49"/>
-      <c r="F747" s="49"/>
-      <c r="AT747" s="52"/>
-      <c r="AY747" s="49"/>
-    </row>
-    <row r="748" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A748" s="48"/>
-      <c r="B748" s="49"/>
-      <c r="C748" s="49"/>
-      <c r="F748" s="49"/>
-      <c r="AT748" s="52"/>
-      <c r="AY748" s="49"/>
-    </row>
-    <row r="749" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A749" s="48"/>
-      <c r="B749" s="49"/>
-      <c r="C749" s="49"/>
-      <c r="F749" s="49"/>
-      <c r="AT749" s="52"/>
-      <c r="AY749" s="49"/>
-    </row>
-    <row r="750" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A750" s="48"/>
-      <c r="B750" s="49"/>
-      <c r="C750" s="49"/>
-      <c r="F750" s="49"/>
-      <c r="AT750" s="52"/>
-      <c r="AY750" s="49"/>
-    </row>
-    <row r="751" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A751" s="48"/>
-      <c r="B751" s="49"/>
-      <c r="C751" s="49"/>
-      <c r="F751" s="49"/>
-      <c r="AT751" s="52"/>
-      <c r="AY751" s="49"/>
-    </row>
-    <row r="752" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A752" s="48"/>
-      <c r="B752" s="49"/>
-      <c r="C752" s="49"/>
-      <c r="F752" s="49"/>
-      <c r="AT752" s="52"/>
-      <c r="AY752" s="49"/>
-    </row>
-    <row r="753" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A753" s="48"/>
-      <c r="B753" s="49"/>
-      <c r="C753" s="49"/>
-      <c r="F753" s="49"/>
-      <c r="AT753" s="52"/>
-      <c r="AY753" s="49"/>
-    </row>
-    <row r="754" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A754" s="48"/>
-      <c r="B754" s="49"/>
-      <c r="C754" s="49"/>
-      <c r="F754" s="49"/>
-      <c r="AT754" s="52"/>
-      <c r="AY754" s="49"/>
-    </row>
-    <row r="755" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A755" s="48"/>
-      <c r="B755" s="49"/>
-      <c r="C755" s="49"/>
-      <c r="F755" s="49"/>
-      <c r="AT755" s="52"/>
-      <c r="AY755" s="49"/>
-    </row>
-    <row r="756" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A756" s="48"/>
-      <c r="B756" s="49"/>
-      <c r="C756" s="49"/>
-      <c r="F756" s="49"/>
-      <c r="AT756" s="52"/>
-      <c r="AY756" s="49"/>
-    </row>
-    <row r="757" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A757" s="48"/>
-      <c r="B757" s="49"/>
-      <c r="C757" s="49"/>
-      <c r="F757" s="49"/>
-      <c r="AT757" s="52"/>
-      <c r="AY757" s="49"/>
-    </row>
-    <row r="758" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A758" s="48"/>
-      <c r="B758" s="49"/>
-      <c r="C758" s="49"/>
-      <c r="F758" s="49"/>
-      <c r="AT758" s="52"/>
-      <c r="AY758" s="49"/>
-    </row>
-    <row r="759" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A759" s="48"/>
-      <c r="B759" s="49"/>
-      <c r="C759" s="49"/>
-      <c r="F759" s="49"/>
-      <c r="AT759" s="52"/>
-      <c r="AY759" s="49"/>
-    </row>
-    <row r="760" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A760" s="48"/>
-      <c r="B760" s="49"/>
-      <c r="C760" s="49"/>
-      <c r="F760" s="49"/>
-      <c r="AT760" s="52"/>
-      <c r="AY760" s="49"/>
-    </row>
-    <row r="761" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A761" s="48"/>
-      <c r="B761" s="49"/>
-      <c r="C761" s="49"/>
-      <c r="F761" s="49"/>
-      <c r="AT761" s="52"/>
-      <c r="AY761" s="49"/>
-    </row>
-    <row r="762" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A762" s="48"/>
-      <c r="B762" s="49"/>
-      <c r="C762" s="49"/>
-      <c r="F762" s="49"/>
-      <c r="AT762" s="52"/>
-      <c r="AY762" s="49"/>
-    </row>
-    <row r="763" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A763" s="48"/>
-      <c r="B763" s="49"/>
-      <c r="C763" s="49"/>
-      <c r="F763" s="49"/>
-      <c r="AT763" s="52"/>
-      <c r="AY763" s="49"/>
-    </row>
-    <row r="764" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A764" s="48"/>
-      <c r="B764" s="49"/>
-      <c r="C764" s="49"/>
-      <c r="F764" s="49"/>
-      <c r="AT764" s="52"/>
-      <c r="AY764" s="49"/>
-    </row>
-    <row r="765" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A765" s="48"/>
-      <c r="B765" s="49"/>
-      <c r="C765" s="49"/>
-      <c r="F765" s="49"/>
-      <c r="AT765" s="52"/>
-      <c r="AY765" s="49"/>
-    </row>
-    <row r="766" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A766" s="48"/>
-      <c r="B766" s="49"/>
-      <c r="C766" s="49"/>
-      <c r="F766" s="49"/>
-      <c r="AT766" s="52"/>
-      <c r="AY766" s="49"/>
-    </row>
-    <row r="767" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A767" s="48"/>
-      <c r="B767" s="49"/>
-      <c r="C767" s="49"/>
-      <c r="F767" s="49"/>
-      <c r="AT767" s="52"/>
-      <c r="AY767" s="49"/>
-    </row>
-    <row r="768" spans="1:51" ht="17.25" customHeight="1">
-      <c r="A768" s="48"/>
-      <c r="B768" s="49"/>
-      <c r="C768" s="49"/>
-      <c r="F768" s="49"/>
-      <c r="AT768" s="52"/>
-      <c r="AY768" s="49"/>
-    </row>
+    <row r="3" ht="16.5" customHeight="1"/>
+    <row r="4" ht="16.5" customHeight="1"/>
+    <row r="5" ht="16.5" customHeight="1"/>
+    <row r="6" ht="16.5" customHeight="1"/>
+    <row r="7" ht="16.5" customHeight="1"/>
+    <row r="8" ht="16.5" customHeight="1"/>
+    <row r="9" ht="16.5" customHeight="1"/>
+    <row r="10" ht="16.5" customHeight="1"/>
+    <row r="11" ht="16.5" customHeight="1"/>
+    <row r="12" ht="16.5" customHeight="1"/>
+    <row r="13" ht="16.5" customHeight="1"/>
+    <row r="14" ht="17.25" customHeight="1"/>
+    <row r="15" ht="17.25" customHeight="1"/>
+    <row r="16" ht="17.25" customHeight="1"/>
+    <row r="17" ht="17.25" customHeight="1"/>
+    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1"/>
+    <row r="20" ht="17.25" customHeight="1"/>
+    <row r="21" ht="17.25" customHeight="1"/>
+    <row r="22" ht="17.25" customHeight="1"/>
+    <row r="23" ht="17.25" customHeight="1"/>
+    <row r="24" ht="17.25" customHeight="1"/>
+    <row r="25" ht="17.25" customHeight="1"/>
+    <row r="26" ht="17.25" customHeight="1"/>
+    <row r="27" ht="17.25" customHeight="1"/>
+    <row r="28" ht="17.25" customHeight="1"/>
+    <row r="29" ht="17.25" customHeight="1"/>
+    <row r="30" ht="17.25" customHeight="1"/>
+    <row r="31" ht="17.25" customHeight="1"/>
+    <row r="32" ht="17.25" customHeight="1"/>
+    <row r="33" ht="17.25" customHeight="1"/>
+    <row r="34" ht="17.25" customHeight="1"/>
+    <row r="35" ht="17.25" customHeight="1"/>
+    <row r="36" ht="17.25" customHeight="1"/>
+    <row r="37" ht="17.25" customHeight="1"/>
+    <row r="38" ht="17.25" customHeight="1"/>
+    <row r="39" ht="17.25" customHeight="1"/>
+    <row r="40" ht="17.25" customHeight="1"/>
+    <row r="41" ht="17.25" customHeight="1"/>
+    <row r="42" ht="17.25" customHeight="1"/>
+    <row r="43" ht="17.25" customHeight="1"/>
+    <row r="44" ht="17.25" customHeight="1"/>
+    <row r="45" ht="17.25" customHeight="1"/>
+    <row r="46" ht="17.25" customHeight="1"/>
+    <row r="47" ht="17.25" customHeight="1"/>
+    <row r="48" ht="17.25" customHeight="1"/>
+    <row r="49" ht="17.25" customHeight="1"/>
+    <row r="50" ht="17.25" customHeight="1"/>
+    <row r="51" ht="17.25" customHeight="1"/>
+    <row r="52" ht="17.25" customHeight="1"/>
+    <row r="53" ht="17.25" customHeight="1"/>
+    <row r="54" ht="17.25" customHeight="1"/>
+    <row r="55" ht="17.25" customHeight="1"/>
+    <row r="56" ht="17.25" customHeight="1"/>
+    <row r="57" ht="17.25" customHeight="1"/>
+    <row r="58" ht="17.25" customHeight="1"/>
+    <row r="59" ht="17.25" customHeight="1"/>
+    <row r="60" ht="17.25" customHeight="1"/>
+    <row r="61" ht="17.25" customHeight="1"/>
+    <row r="62" ht="17.25" customHeight="1"/>
+    <row r="63" ht="17.25" customHeight="1"/>
+    <row r="64" ht="17.25" customHeight="1"/>
+    <row r="65" ht="17.25" customHeight="1"/>
+    <row r="66" ht="17.25" customHeight="1"/>
+    <row r="67" ht="17.25" customHeight="1"/>
+    <row r="68" ht="17.25" customHeight="1"/>
+    <row r="69" ht="17.25" customHeight="1"/>
+    <row r="70" ht="17.25" customHeight="1"/>
+    <row r="71" ht="17.25" customHeight="1"/>
+    <row r="72" ht="17.25" customHeight="1"/>
+    <row r="73" ht="17.25" customHeight="1"/>
+    <row r="74" ht="17.25" customHeight="1"/>
+    <row r="75" ht="17.25" customHeight="1"/>
+    <row r="76" ht="17.25" customHeight="1"/>
+    <row r="77" ht="17.25" customHeight="1"/>
+    <row r="78" ht="17.25" customHeight="1"/>
+    <row r="79" ht="17.25" customHeight="1"/>
+    <row r="80" ht="17.25" customHeight="1"/>
+    <row r="81" ht="17.25" customHeight="1"/>
+    <row r="82" ht="17.25" customHeight="1"/>
+    <row r="83" ht="17.25" customHeight="1"/>
+    <row r="84" ht="17.25" customHeight="1"/>
+    <row r="85" ht="17.25" customHeight="1"/>
+    <row r="86" ht="17.25" customHeight="1"/>
+    <row r="87" ht="17.25" customHeight="1"/>
+    <row r="88" ht="17.25" customHeight="1"/>
+    <row r="89" ht="17.25" customHeight="1"/>
+    <row r="90" ht="17.25" customHeight="1"/>
+    <row r="91" ht="17.25" customHeight="1"/>
+    <row r="92" ht="17.25" customHeight="1"/>
+    <row r="93" ht="17.25" customHeight="1"/>
+    <row r="94" ht="17.25" customHeight="1"/>
+    <row r="95" ht="17.25" customHeight="1"/>
+    <row r="96" ht="17.25" customHeight="1"/>
+    <row r="97" ht="17.25" customHeight="1"/>
+    <row r="98" ht="17.25" customHeight="1"/>
+    <row r="99" ht="17.25" customHeight="1"/>
+    <row r="100" ht="17.25" customHeight="1"/>
+    <row r="101" ht="17.25" customHeight="1"/>
+    <row r="102" ht="17.25" customHeight="1"/>
+    <row r="103" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1"/>
+    <row r="105" ht="17.25" customHeight="1"/>
+    <row r="106" ht="17.25" customHeight="1"/>
+    <row r="107" ht="17.25" customHeight="1"/>
+    <row r="108" ht="17.25" customHeight="1"/>
+    <row r="109" ht="17.25" customHeight="1"/>
+    <row r="110" ht="17.25" customHeight="1"/>
+    <row r="111" ht="17.25" customHeight="1"/>
+    <row r="112" ht="17.25" customHeight="1"/>
+    <row r="113" ht="17.25" customHeight="1"/>
+    <row r="114" ht="17.25" customHeight="1"/>
+    <row r="115" ht="17.25" customHeight="1"/>
+    <row r="116" ht="17.25" customHeight="1"/>
+    <row r="117" ht="17.25" customHeight="1"/>
+    <row r="118" ht="17.25" customHeight="1"/>
+    <row r="119" ht="17.25" customHeight="1"/>
+    <row r="120" ht="17.25" customHeight="1"/>
+    <row r="121" ht="17.25" customHeight="1"/>
+    <row r="122" ht="17.25" customHeight="1"/>
+    <row r="123" ht="17.25" customHeight="1"/>
+    <row r="124" ht="17.25" customHeight="1"/>
+    <row r="125" ht="17.25" customHeight="1"/>
+    <row r="126" ht="17.25" customHeight="1"/>
+    <row r="127" ht="17.25" customHeight="1"/>
+    <row r="128" ht="17.25" customHeight="1"/>
+    <row r="129" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="131" ht="17.25" customHeight="1"/>
+    <row r="132" ht="17.25" customHeight="1"/>
+    <row r="133" ht="17.25" customHeight="1"/>
+    <row r="134" ht="17.25" customHeight="1"/>
+    <row r="135" ht="17.25" customHeight="1"/>
+    <row r="136" ht="17.25" customHeight="1"/>
+    <row r="137" ht="17.25" customHeight="1"/>
+    <row r="138" ht="17.25" customHeight="1"/>
+    <row r="139" ht="17.25" customHeight="1"/>
+    <row r="140" ht="17.25" customHeight="1"/>
+    <row r="141" ht="17.25" customHeight="1"/>
+    <row r="142" ht="17.25" customHeight="1"/>
+    <row r="143" ht="17.25" customHeight="1"/>
+    <row r="144" ht="17.25" customHeight="1"/>
+    <row r="145" ht="17.25" customHeight="1"/>
+    <row r="146" ht="17.25" customHeight="1"/>
+    <row r="147" ht="17.25" customHeight="1"/>
+    <row r="148" ht="17.25" customHeight="1"/>
+    <row r="149" ht="17.25" customHeight="1"/>
+    <row r="150" ht="17.25" customHeight="1"/>
+    <row r="151" ht="17.25" customHeight="1"/>
+    <row r="152" ht="17.25" customHeight="1"/>
+    <row r="153" ht="17.25" customHeight="1"/>
+    <row r="154" ht="17.25" customHeight="1"/>
+    <row r="155" ht="17.25" customHeight="1"/>
+    <row r="156" ht="17.25" customHeight="1"/>
+    <row r="157" ht="17.25" customHeight="1"/>
+    <row r="158" ht="17.25" customHeight="1"/>
+    <row r="159" ht="17.25" customHeight="1"/>
+    <row r="160" ht="17.25" customHeight="1"/>
+    <row r="161" ht="17.25" customHeight="1"/>
+    <row r="162" ht="17.25" customHeight="1"/>
+    <row r="163" ht="17.25" customHeight="1"/>
+    <row r="164" ht="17.25" customHeight="1"/>
+    <row r="165" ht="17.25" customHeight="1"/>
+    <row r="166" ht="17.25" customHeight="1"/>
+    <row r="167" ht="17.25" customHeight="1"/>
+    <row r="168" ht="17.25" customHeight="1"/>
+    <row r="169" ht="17.25" customHeight="1"/>
+    <row r="170" ht="17.25" customHeight="1"/>
+    <row r="171" ht="17.25" customHeight="1"/>
+    <row r="172" ht="17.25" customHeight="1"/>
+    <row r="173" ht="17.25" customHeight="1"/>
+    <row r="174" ht="17.25" customHeight="1"/>
+    <row r="175" ht="17.25" customHeight="1"/>
+    <row r="176" ht="17.25" customHeight="1"/>
+    <row r="177" ht="17.25" customHeight="1"/>
+    <row r="178" ht="17.25" customHeight="1"/>
+    <row r="179" ht="17.25" customHeight="1"/>
+    <row r="180" ht="17.25" customHeight="1"/>
+    <row r="181" ht="17.25" customHeight="1"/>
+    <row r="182" ht="17.25" customHeight="1"/>
+    <row r="183" ht="17.25" customHeight="1"/>
+    <row r="184" ht="17.25" customHeight="1"/>
+    <row r="185" ht="17.25" customHeight="1"/>
+    <row r="186" ht="17.25" customHeight="1"/>
+    <row r="187" ht="17.25" customHeight="1"/>
+    <row r="188" ht="17.25" customHeight="1"/>
+    <row r="189" ht="17.25" customHeight="1"/>
+    <row r="190" ht="17.25" customHeight="1"/>
+    <row r="191" ht="17.25" customHeight="1"/>
+    <row r="192" ht="17.25" customHeight="1"/>
+    <row r="193" ht="17.25" customHeight="1"/>
+    <row r="194" ht="17.25" customHeight="1"/>
+    <row r="195" ht="17.25" customHeight="1"/>
+    <row r="196" ht="17.25" customHeight="1"/>
+    <row r="197" ht="17.25" customHeight="1"/>
+    <row r="198" ht="17.25" customHeight="1"/>
+    <row r="199" ht="17.25" customHeight="1"/>
+    <row r="200" ht="17.25" customHeight="1"/>
+    <row r="201" ht="17.25" customHeight="1"/>
+    <row r="202" ht="17.25" customHeight="1"/>
+    <row r="203" ht="17.25" customHeight="1"/>
+    <row r="204" ht="17.25" customHeight="1"/>
+    <row r="205" ht="17.25" customHeight="1"/>
+    <row r="206" ht="17.25" customHeight="1"/>
+    <row r="207" ht="17.25" customHeight="1"/>
+    <row r="208" ht="17.25" customHeight="1"/>
+    <row r="209" ht="17.25" customHeight="1"/>
+    <row r="210" ht="17.25" customHeight="1"/>
+    <row r="211" ht="17.25" customHeight="1"/>
+    <row r="212" ht="17.25" customHeight="1"/>
+    <row r="213" ht="17.25" customHeight="1"/>
+    <row r="214" ht="17.25" customHeight="1"/>
+    <row r="215" ht="17.25" customHeight="1"/>
+    <row r="216" ht="17.25" customHeight="1"/>
+    <row r="217" ht="17.25" customHeight="1"/>
+    <row r="218" ht="17.25" customHeight="1"/>
+    <row r="219" ht="17.25" customHeight="1"/>
+    <row r="220" ht="17.25" customHeight="1"/>
+    <row r="221" ht="17.25" customHeight="1"/>
+    <row r="222" ht="17.25" customHeight="1"/>
+    <row r="223" ht="17.25" customHeight="1"/>
+    <row r="224" ht="17.25" customHeight="1"/>
+    <row r="225" ht="17.25" customHeight="1"/>
+    <row r="226" ht="17.25" customHeight="1"/>
+    <row r="227" ht="17.25" customHeight="1"/>
+    <row r="228" ht="17.25" customHeight="1"/>
+    <row r="229" ht="17.25" customHeight="1"/>
+    <row r="230" ht="17.25" customHeight="1"/>
+    <row r="231" ht="17.25" customHeight="1"/>
+    <row r="232" ht="17.25" customHeight="1"/>
+    <row r="233" ht="17.25" customHeight="1"/>
+    <row r="234" ht="17.25" customHeight="1"/>
+    <row r="235" ht="17.25" customHeight="1"/>
+    <row r="236" ht="17.25" customHeight="1"/>
+    <row r="237" ht="17.25" customHeight="1"/>
+    <row r="238" ht="17.25" customHeight="1"/>
+    <row r="239" ht="17.25" customHeight="1"/>
+    <row r="240" ht="17.25" customHeight="1"/>
+    <row r="241" ht="17.25" customHeight="1"/>
+    <row r="242" ht="17.25" customHeight="1"/>
+    <row r="243" ht="17.25" customHeight="1"/>
+    <row r="244" ht="17.25" customHeight="1"/>
+    <row r="245" ht="17.25" customHeight="1"/>
+    <row r="246" ht="17.25" customHeight="1"/>
+    <row r="247" ht="17.25" customHeight="1"/>
+    <row r="248" ht="17.25" customHeight="1"/>
+    <row r="249" ht="17.25" customHeight="1"/>
+    <row r="250" ht="17.25" customHeight="1"/>
+    <row r="251" ht="17.25" customHeight="1"/>
+    <row r="252" ht="17.25" customHeight="1"/>
+    <row r="253" ht="17.25" customHeight="1"/>
+    <row r="254" ht="17.25" customHeight="1"/>
+    <row r="255" ht="17.25" customHeight="1"/>
+    <row r="256" ht="17.25" customHeight="1"/>
+    <row r="257" ht="17.25" customHeight="1"/>
+    <row r="258" ht="17.25" customHeight="1"/>
+    <row r="259" ht="17.25" customHeight="1"/>
+    <row r="260" ht="17.25" customHeight="1"/>
+    <row r="261" ht="17.25" customHeight="1"/>
+    <row r="262" ht="17.25" customHeight="1"/>
+    <row r="263" ht="17.25" customHeight="1"/>
+    <row r="264" ht="17.25" customHeight="1"/>
+    <row r="265" ht="17.25" customHeight="1"/>
+    <row r="266" ht="17.25" customHeight="1"/>
+    <row r="267" ht="17.25" customHeight="1"/>
+    <row r="268" ht="17.25" customHeight="1"/>
+    <row r="269" ht="17.25" customHeight="1"/>
+    <row r="270" ht="17.25" customHeight="1"/>
+    <row r="271" ht="17.25" customHeight="1"/>
+    <row r="272" ht="17.25" customHeight="1"/>
+    <row r="273" ht="17.25" customHeight="1"/>
+    <row r="274" ht="17.25" customHeight="1"/>
+    <row r="275" ht="17.25" customHeight="1"/>
+    <row r="276" ht="17.25" customHeight="1"/>
+    <row r="277" ht="17.25" customHeight="1"/>
+    <row r="278" ht="17.25" customHeight="1"/>
+    <row r="279" ht="17.25" customHeight="1"/>
+    <row r="280" ht="17.25" customHeight="1"/>
+    <row r="281" ht="17.25" customHeight="1"/>
+    <row r="282" ht="17.25" customHeight="1"/>
+    <row r="283" ht="17.25" customHeight="1"/>
+    <row r="284" ht="17.25" customHeight="1"/>
+    <row r="285" ht="17.25" customHeight="1"/>
+    <row r="286" ht="17.25" customHeight="1"/>
+    <row r="287" ht="17.25" customHeight="1"/>
+    <row r="288" ht="17.25" customHeight="1"/>
+    <row r="289" ht="17.25" customHeight="1"/>
+    <row r="290" ht="17.25" customHeight="1"/>
+    <row r="291" ht="17.25" customHeight="1"/>
+    <row r="292" ht="17.25" customHeight="1"/>
+    <row r="293" ht="17.25" customHeight="1"/>
+    <row r="294" ht="17.25" customHeight="1"/>
+    <row r="295" ht="17.25" customHeight="1"/>
+    <row r="296" ht="17.25" customHeight="1"/>
+    <row r="297" ht="17.25" customHeight="1"/>
+    <row r="298" ht="17.25" customHeight="1"/>
+    <row r="299" ht="17.25" customHeight="1"/>
+    <row r="300" ht="17.25" customHeight="1"/>
+    <row r="301" ht="17.25" customHeight="1"/>
+    <row r="302" ht="17.25" customHeight="1"/>
+    <row r="303" ht="17.25" customHeight="1"/>
+    <row r="304" ht="17.25" customHeight="1"/>
+    <row r="305" ht="17.25" customHeight="1"/>
+    <row r="306" ht="17.25" customHeight="1"/>
+    <row r="307" ht="17.25" customHeight="1"/>
+    <row r="308" ht="17.25" customHeight="1"/>
+    <row r="309" ht="17.25" customHeight="1"/>
+    <row r="310" ht="17.25" customHeight="1"/>
+    <row r="311" ht="17.25" customHeight="1"/>
+    <row r="312" ht="17.25" customHeight="1"/>
+    <row r="313" ht="17.25" customHeight="1"/>
+    <row r="314" ht="17.25" customHeight="1"/>
+    <row r="315" ht="17.25" customHeight="1"/>
+    <row r="316" ht="17.25" customHeight="1"/>
+    <row r="317" ht="17.25" customHeight="1"/>
+    <row r="318" ht="17.25" customHeight="1"/>
+    <row r="319" ht="17.25" customHeight="1"/>
+    <row r="320" ht="17.25" customHeight="1"/>
+    <row r="321" ht="17.25" customHeight="1"/>
+    <row r="322" ht="17.25" customHeight="1"/>
+    <row r="323" ht="17.25" customHeight="1"/>
+    <row r="324" ht="17.25" customHeight="1"/>
+    <row r="325" ht="17.25" customHeight="1"/>
+    <row r="326" ht="17.25" customHeight="1"/>
+    <row r="327" ht="17.25" customHeight="1"/>
+    <row r="328" ht="17.25" customHeight="1"/>
+    <row r="329" ht="17.25" customHeight="1"/>
+    <row r="330" ht="17.25" customHeight="1"/>
+    <row r="331" ht="17.25" customHeight="1"/>
+    <row r="332" ht="17.25" customHeight="1"/>
+    <row r="333" ht="17.25" customHeight="1"/>
+    <row r="334" ht="17.25" customHeight="1"/>
+    <row r="335" ht="17.25" customHeight="1"/>
+    <row r="336" ht="17.25" customHeight="1"/>
+    <row r="337" ht="17.25" customHeight="1"/>
+    <row r="338" ht="17.25" customHeight="1"/>
+    <row r="339" ht="17.25" customHeight="1"/>
+    <row r="340" ht="17.25" customHeight="1"/>
+    <row r="341" ht="17.25" customHeight="1"/>
+    <row r="342" ht="17.25" customHeight="1"/>
+    <row r="343" ht="17.25" customHeight="1"/>
+    <row r="344" ht="17.25" customHeight="1"/>
+    <row r="345" ht="17.25" customHeight="1"/>
+    <row r="346" ht="17.25" customHeight="1"/>
+    <row r="347" ht="17.25" customHeight="1"/>
+    <row r="348" ht="17.25" customHeight="1"/>
+    <row r="349" ht="17.25" customHeight="1"/>
+    <row r="350" ht="17.25" customHeight="1"/>
+    <row r="351" ht="17.25" customHeight="1"/>
+    <row r="352" ht="17.25" customHeight="1"/>
+    <row r="353" ht="17.25" customHeight="1"/>
+    <row r="354" ht="17.25" customHeight="1"/>
+    <row r="355" ht="17.25" customHeight="1"/>
+    <row r="356" ht="17.25" customHeight="1"/>
+    <row r="357" ht="17.25" customHeight="1"/>
+    <row r="358" ht="17.25" customHeight="1"/>
+    <row r="359" ht="17.25" customHeight="1"/>
+    <row r="360" ht="17.25" customHeight="1"/>
+    <row r="361" ht="17.25" customHeight="1"/>
+    <row r="362" ht="17.25" customHeight="1"/>
+    <row r="363" ht="17.25" customHeight="1"/>
+    <row r="364" ht="17.25" customHeight="1"/>
+    <row r="365" ht="17.25" customHeight="1"/>
+    <row r="366" ht="17.25" customHeight="1"/>
+    <row r="367" ht="17.25" customHeight="1"/>
+    <row r="368" ht="17.25" customHeight="1"/>
+    <row r="369" ht="17.25" customHeight="1"/>
+    <row r="370" ht="17.25" customHeight="1"/>
+    <row r="371" ht="17.25" customHeight="1"/>
+    <row r="372" ht="17.25" customHeight="1"/>
+    <row r="373" ht="17.25" customHeight="1"/>
+    <row r="374" ht="17.25" customHeight="1"/>
+    <row r="375" ht="17.25" customHeight="1"/>
+    <row r="376" ht="17.25" customHeight="1"/>
+    <row r="377" ht="17.25" customHeight="1"/>
+    <row r="378" ht="17.25" customHeight="1"/>
+    <row r="379" ht="17.25" customHeight="1"/>
+    <row r="380" ht="17.25" customHeight="1"/>
+    <row r="381" ht="17.25" customHeight="1"/>
+    <row r="382" ht="17.25" customHeight="1"/>
+    <row r="383" ht="17.25" customHeight="1"/>
+    <row r="384" ht="17.25" customHeight="1"/>
+    <row r="385" ht="17.25" customHeight="1"/>
+    <row r="386" ht="17.25" customHeight="1"/>
+    <row r="387" ht="17.25" customHeight="1"/>
+    <row r="388" ht="17.25" customHeight="1"/>
+    <row r="389" ht="17.25" customHeight="1"/>
+    <row r="390" ht="17.25" customHeight="1"/>
+    <row r="391" ht="17.25" customHeight="1"/>
+    <row r="392" ht="17.25" customHeight="1"/>
+    <row r="393" ht="17.25" customHeight="1"/>
+    <row r="394" ht="17.25" customHeight="1"/>
+    <row r="395" ht="17.25" customHeight="1"/>
+    <row r="396" ht="17.25" customHeight="1"/>
+    <row r="397" ht="17.25" customHeight="1"/>
+    <row r="398" ht="17.25" customHeight="1"/>
+    <row r="399" ht="17.25" customHeight="1"/>
+    <row r="400" ht="17.25" customHeight="1"/>
+    <row r="401" ht="17.25" customHeight="1"/>
+    <row r="402" ht="17.25" customHeight="1"/>
+    <row r="403" ht="17.25" customHeight="1"/>
+    <row r="404" ht="17.25" customHeight="1"/>
+    <row r="405" ht="17.25" customHeight="1"/>
+    <row r="406" ht="17.25" customHeight="1"/>
+    <row r="407" ht="17.25" customHeight="1"/>
+    <row r="408" ht="17.25" customHeight="1"/>
+    <row r="409" ht="17.25" customHeight="1"/>
+    <row r="410" ht="17.25" customHeight="1"/>
+    <row r="411" ht="17.25" customHeight="1"/>
+    <row r="412" ht="17.25" customHeight="1"/>
+    <row r="413" ht="17.25" customHeight="1"/>
+    <row r="414" ht="17.25" customHeight="1"/>
+    <row r="415" ht="17.25" customHeight="1"/>
+    <row r="416" ht="17.25" customHeight="1"/>
+    <row r="417" ht="17.25" customHeight="1"/>
+    <row r="418" ht="17.25" customHeight="1"/>
+    <row r="419" ht="17.25" customHeight="1"/>
+    <row r="420" ht="17.25" customHeight="1"/>
+    <row r="421" ht="17.25" customHeight="1"/>
+    <row r="422" ht="17.25" customHeight="1"/>
+    <row r="423" ht="17.25" customHeight="1"/>
+    <row r="424" ht="17.25" customHeight="1"/>
+    <row r="425" ht="17.25" customHeight="1"/>
+    <row r="426" ht="17.25" customHeight="1"/>
+    <row r="427" ht="17.25" customHeight="1"/>
+    <row r="428" ht="17.25" customHeight="1"/>
+    <row r="429" ht="17.25" customHeight="1"/>
+    <row r="430" ht="17.25" customHeight="1"/>
+    <row r="431" ht="17.25" customHeight="1"/>
+    <row r="432" ht="17.25" customHeight="1"/>
+    <row r="433" ht="17.25" customHeight="1"/>
+    <row r="434" ht="17.25" customHeight="1"/>
+    <row r="435" ht="17.25" customHeight="1"/>
+    <row r="436" ht="17.25" customHeight="1"/>
+    <row r="437" ht="17.25" customHeight="1"/>
+    <row r="438" ht="17.25" customHeight="1"/>
+    <row r="439" ht="17.25" customHeight="1"/>
+    <row r="440" ht="17.25" customHeight="1"/>
+    <row r="441" ht="17.25" customHeight="1"/>
+    <row r="442" ht="17.25" customHeight="1"/>
+    <row r="443" ht="17.25" customHeight="1"/>
+    <row r="444" ht="17.25" customHeight="1"/>
+    <row r="445" ht="17.25" customHeight="1"/>
+    <row r="446" ht="17.25" customHeight="1"/>
+    <row r="447" ht="17.25" customHeight="1"/>
+    <row r="448" ht="17.25" customHeight="1"/>
+    <row r="449" ht="17.25" customHeight="1"/>
+    <row r="450" ht="17.25" customHeight="1"/>
+    <row r="451" ht="17.25" customHeight="1"/>
+    <row r="452" ht="17.25" customHeight="1"/>
+    <row r="453" ht="17.25" customHeight="1"/>
+    <row r="454" ht="17.25" customHeight="1"/>
+    <row r="455" ht="17.25" customHeight="1"/>
+    <row r="456" ht="17.25" customHeight="1"/>
+    <row r="457" ht="17.25" customHeight="1"/>
+    <row r="458" ht="17.25" customHeight="1"/>
+    <row r="459" ht="17.25" customHeight="1"/>
+    <row r="460" ht="17.25" customHeight="1"/>
+    <row r="461" ht="17.25" customHeight="1"/>
+    <row r="462" ht="17.25" customHeight="1"/>
+    <row r="463" ht="17.25" customHeight="1"/>
+    <row r="464" ht="17.25" customHeight="1"/>
+    <row r="465" ht="17.25" customHeight="1"/>
+    <row r="466" ht="17.25" customHeight="1"/>
+    <row r="467" ht="17.25" customHeight="1"/>
+    <row r="468" ht="17.25" customHeight="1"/>
+    <row r="469" ht="17.25" customHeight="1"/>
+    <row r="470" ht="17.25" customHeight="1"/>
+    <row r="471" ht="17.25" customHeight="1"/>
+    <row r="472" ht="17.25" customHeight="1"/>
+    <row r="473" ht="17.25" customHeight="1"/>
+    <row r="474" ht="17.25" customHeight="1"/>
+    <row r="475" ht="17.25" customHeight="1"/>
+    <row r="476" ht="17.25" customHeight="1"/>
+    <row r="477" ht="17.25" customHeight="1"/>
+    <row r="478" ht="17.25" customHeight="1"/>
+    <row r="479" ht="17.25" customHeight="1"/>
+    <row r="480" ht="17.25" customHeight="1"/>
+    <row r="481" ht="17.25" customHeight="1"/>
+    <row r="482" ht="17.25" customHeight="1"/>
+    <row r="483" ht="17.25" customHeight="1"/>
+    <row r="484" ht="17.25" customHeight="1"/>
+    <row r="485" ht="17.25" customHeight="1"/>
+    <row r="486" ht="17.25" customHeight="1"/>
+    <row r="487" ht="17.25" customHeight="1"/>
+    <row r="488" ht="17.25" customHeight="1"/>
+    <row r="489" ht="17.25" customHeight="1"/>
+    <row r="490" ht="17.25" customHeight="1"/>
+    <row r="491" ht="17.25" customHeight="1"/>
+    <row r="492" ht="17.25" customHeight="1"/>
+    <row r="493" ht="17.25" customHeight="1"/>
+    <row r="494" ht="17.25" customHeight="1"/>
+    <row r="495" ht="17.25" customHeight="1"/>
+    <row r="496" ht="17.25" customHeight="1"/>
+    <row r="497" ht="17.25" customHeight="1"/>
+    <row r="498" ht="17.25" customHeight="1"/>
+    <row r="499" ht="17.25" customHeight="1"/>
+    <row r="500" ht="17.25" customHeight="1"/>
+    <row r="501" ht="17.25" customHeight="1"/>
+    <row r="502" ht="17.25" customHeight="1"/>
+    <row r="503" ht="17.25" customHeight="1"/>
+    <row r="504" ht="17.25" customHeight="1"/>
+    <row r="505" ht="17.25" customHeight="1"/>
+    <row r="506" ht="17.25" customHeight="1"/>
+    <row r="507" ht="17.25" customHeight="1"/>
+    <row r="508" ht="17.25" customHeight="1"/>
+    <row r="509" ht="17.25" customHeight="1"/>
+    <row r="510" ht="17.25" customHeight="1"/>
+    <row r="511" ht="17.25" customHeight="1"/>
+    <row r="512" ht="17.25" customHeight="1"/>
+    <row r="513" ht="17.25" customHeight="1"/>
+    <row r="514" ht="17.25" customHeight="1"/>
+    <row r="515" ht="17.25" customHeight="1"/>
+    <row r="516" ht="17.25" customHeight="1"/>
+    <row r="517" ht="17.25" customHeight="1"/>
+    <row r="518" ht="17.25" customHeight="1"/>
+    <row r="519" ht="17.25" customHeight="1"/>
+    <row r="520" ht="17.25" customHeight="1"/>
+    <row r="521" ht="17.25" customHeight="1"/>
+    <row r="522" ht="17.25" customHeight="1"/>
+    <row r="523" ht="17.25" customHeight="1"/>
+    <row r="524" ht="17.25" customHeight="1"/>
+    <row r="525" ht="17.25" customHeight="1"/>
+    <row r="526" ht="17.25" customHeight="1"/>
+    <row r="527" ht="17.25" customHeight="1"/>
+    <row r="528" ht="17.25" customHeight="1"/>
+    <row r="529" ht="17.25" customHeight="1"/>
+    <row r="530" ht="17.25" customHeight="1"/>
+    <row r="531" ht="17.25" customHeight="1"/>
+    <row r="532" ht="17.25" customHeight="1"/>
+    <row r="533" ht="17.25" customHeight="1"/>
+    <row r="534" ht="17.25" customHeight="1"/>
+    <row r="535" ht="17.25" customHeight="1"/>
+    <row r="536" ht="17.25" customHeight="1"/>
+    <row r="537" ht="17.25" customHeight="1"/>
+    <row r="538" ht="17.25" customHeight="1"/>
+    <row r="539" ht="17.25" customHeight="1"/>
+    <row r="540" ht="17.25" customHeight="1"/>
+    <row r="541" ht="17.25" customHeight="1"/>
+    <row r="542" ht="17.25" customHeight="1"/>
+    <row r="543" ht="17.25" customHeight="1"/>
+    <row r="544" ht="17.25" customHeight="1"/>
+    <row r="545" ht="17.25" customHeight="1"/>
+    <row r="546" ht="17.25" customHeight="1"/>
+    <row r="547" ht="17.25" customHeight="1"/>
+    <row r="548" ht="17.25" customHeight="1"/>
+    <row r="549" ht="17.25" customHeight="1"/>
+    <row r="550" ht="17.25" customHeight="1"/>
+    <row r="551" ht="17.25" customHeight="1"/>
+    <row r="552" ht="17.25" customHeight="1"/>
+    <row r="553" ht="17.25" customHeight="1"/>
+    <row r="554" ht="17.25" customHeight="1"/>
+    <row r="555" ht="17.25" customHeight="1"/>
+    <row r="556" ht="17.25" customHeight="1"/>
+    <row r="557" ht="17.25" customHeight="1"/>
+    <row r="558" ht="17.25" customHeight="1"/>
+    <row r="559" ht="17.25" customHeight="1"/>
+    <row r="560" ht="17.25" customHeight="1"/>
+    <row r="561" ht="17.25" customHeight="1"/>
+    <row r="562" ht="17.25" customHeight="1"/>
+    <row r="563" ht="17.25" customHeight="1"/>
+    <row r="564" ht="17.25" customHeight="1"/>
+    <row r="565" ht="17.25" customHeight="1"/>
+    <row r="566" ht="17.25" customHeight="1"/>
+    <row r="567" ht="17.25" customHeight="1"/>
+    <row r="568" ht="17.25" customHeight="1"/>
+    <row r="569" ht="17.25" customHeight="1"/>
+    <row r="570" ht="17.25" customHeight="1"/>
+    <row r="571" ht="17.25" customHeight="1"/>
+    <row r="572" ht="17.25" customHeight="1"/>
+    <row r="573" ht="17.25" customHeight="1"/>
+    <row r="574" ht="17.25" customHeight="1"/>
+    <row r="575" ht="17.25" customHeight="1"/>
+    <row r="576" ht="17.25" customHeight="1"/>
+    <row r="577" ht="17.25" customHeight="1"/>
+    <row r="578" ht="17.25" customHeight="1"/>
+    <row r="579" ht="17.25" customHeight="1"/>
+    <row r="580" ht="17.25" customHeight="1"/>
+    <row r="581" ht="17.25" customHeight="1"/>
+    <row r="582" ht="17.25" customHeight="1"/>
+    <row r="583" ht="17.25" customHeight="1"/>
+    <row r="584" ht="17.25" customHeight="1"/>
+    <row r="585" ht="17.25" customHeight="1"/>
+    <row r="586" ht="17.25" customHeight="1"/>
+    <row r="587" ht="17.25" customHeight="1"/>
+    <row r="588" ht="17.25" customHeight="1"/>
+    <row r="589" ht="17.25" customHeight="1"/>
+    <row r="590" ht="17.25" customHeight="1"/>
+    <row r="591" ht="17.25" customHeight="1"/>
+    <row r="592" ht="17.25" customHeight="1"/>
+    <row r="593" ht="17.25" customHeight="1"/>
+    <row r="594" ht="17.25" customHeight="1"/>
+    <row r="595" ht="17.25" customHeight="1"/>
+    <row r="596" ht="17.25" customHeight="1"/>
+    <row r="597" ht="17.25" customHeight="1"/>
+    <row r="598" ht="17.25" customHeight="1"/>
+    <row r="599" ht="17.25" customHeight="1"/>
+    <row r="600" ht="17.25" customHeight="1"/>
+    <row r="601" ht="17.25" customHeight="1"/>
+    <row r="602" ht="17.25" customHeight="1"/>
+    <row r="603" ht="17.25" customHeight="1"/>
+    <row r="604" ht="17.25" customHeight="1"/>
+    <row r="605" ht="17.25" customHeight="1"/>
+    <row r="606" ht="17.25" customHeight="1"/>
+    <row r="607" ht="17.25" customHeight="1"/>
+    <row r="608" ht="17.25" customHeight="1"/>
+    <row r="609" ht="17.25" customHeight="1"/>
+    <row r="610" ht="17.25" customHeight="1"/>
+    <row r="611" ht="17.25" customHeight="1"/>
+    <row r="612" ht="17.25" customHeight="1"/>
+    <row r="613" ht="17.25" customHeight="1"/>
+    <row r="614" ht="17.25" customHeight="1"/>
+    <row r="615" ht="17.25" customHeight="1"/>
+    <row r="616" ht="17.25" customHeight="1"/>
+    <row r="617" ht="17.25" customHeight="1"/>
+    <row r="618" ht="17.25" customHeight="1"/>
+    <row r="619" ht="17.25" customHeight="1"/>
+    <row r="620" ht="17.25" customHeight="1"/>
+    <row r="621" ht="17.25" customHeight="1"/>
+    <row r="622" ht="17.25" customHeight="1"/>
+    <row r="623" ht="17.25" customHeight="1"/>
+    <row r="624" ht="17.25" customHeight="1"/>
+    <row r="625" ht="17.25" customHeight="1"/>
+    <row r="626" ht="17.25" customHeight="1"/>
+    <row r="627" ht="17.25" customHeight="1"/>
+    <row r="628" ht="17.25" customHeight="1"/>
+    <row r="629" ht="17.25" customHeight="1"/>
+    <row r="630" ht="17.25" customHeight="1"/>
+    <row r="631" ht="17.25" customHeight="1"/>
+    <row r="632" ht="17.25" customHeight="1"/>
+    <row r="633" ht="17.25" customHeight="1"/>
+    <row r="634" ht="17.25" customHeight="1"/>
+    <row r="635" ht="17.25" customHeight="1"/>
+    <row r="636" ht="17.25" customHeight="1"/>
+    <row r="637" ht="17.25" customHeight="1"/>
+    <row r="638" ht="17.25" customHeight="1"/>
+    <row r="639" ht="17.25" customHeight="1"/>
+    <row r="640" ht="17.25" customHeight="1"/>
+    <row r="641" ht="17.25" customHeight="1"/>
+    <row r="642" ht="17.25" customHeight="1"/>
+    <row r="643" ht="17.25" customHeight="1"/>
+    <row r="644" ht="17.25" customHeight="1"/>
+    <row r="645" ht="17.25" customHeight="1"/>
+    <row r="646" ht="17.25" customHeight="1"/>
+    <row r="647" ht="17.25" customHeight="1"/>
+    <row r="648" ht="17.25" customHeight="1"/>
+    <row r="649" ht="17.25" customHeight="1"/>
+    <row r="650" ht="17.25" customHeight="1"/>
+    <row r="651" ht="17.25" customHeight="1"/>
+    <row r="652" ht="17.25" customHeight="1"/>
+    <row r="653" ht="17.25" customHeight="1"/>
+    <row r="654" ht="17.25" customHeight="1"/>
+    <row r="655" ht="17.25" customHeight="1"/>
+    <row r="656" ht="17.25" customHeight="1"/>
+    <row r="657" ht="17.25" customHeight="1"/>
+    <row r="658" ht="17.25" customHeight="1"/>
+    <row r="659" ht="17.25" customHeight="1"/>
+    <row r="660" ht="17.25" customHeight="1"/>
+    <row r="661" ht="17.25" customHeight="1"/>
+    <row r="662" ht="17.25" customHeight="1"/>
+    <row r="663" ht="17.25" customHeight="1"/>
+    <row r="664" ht="17.25" customHeight="1"/>
+    <row r="665" ht="17.25" customHeight="1"/>
+    <row r="666" ht="17.25" customHeight="1"/>
+    <row r="667" ht="17.25" customHeight="1"/>
+    <row r="668" ht="17.25" customHeight="1"/>
+    <row r="669" ht="17.25" customHeight="1"/>
+    <row r="670" ht="17.25" customHeight="1"/>
+    <row r="671" ht="17.25" customHeight="1"/>
+    <row r="672" ht="17.25" customHeight="1"/>
+    <row r="673" ht="17.25" customHeight="1"/>
+    <row r="674" ht="17.25" customHeight="1"/>
+    <row r="675" ht="17.25" customHeight="1"/>
+    <row r="676" ht="17.25" customHeight="1"/>
+    <row r="677" ht="17.25" customHeight="1"/>
+    <row r="678" ht="17.25" customHeight="1"/>
+    <row r="679" ht="17.25" customHeight="1"/>
+    <row r="680" ht="17.25" customHeight="1"/>
+    <row r="681" ht="17.25" customHeight="1"/>
+    <row r="682" ht="17.25" customHeight="1"/>
+    <row r="683" ht="17.25" customHeight="1"/>
+    <row r="684" ht="17.25" customHeight="1"/>
+    <row r="685" ht="17.25" customHeight="1"/>
+    <row r="686" ht="17.25" customHeight="1"/>
+    <row r="687" ht="17.25" customHeight="1"/>
+    <row r="688" ht="17.25" customHeight="1"/>
+    <row r="689" ht="17.25" customHeight="1"/>
+    <row r="690" ht="17.25" customHeight="1"/>
+    <row r="691" ht="17.25" customHeight="1"/>
+    <row r="692" ht="17.25" customHeight="1"/>
+    <row r="693" ht="17.25" customHeight="1"/>
+    <row r="694" ht="17.25" customHeight="1"/>
+    <row r="695" ht="17.25" customHeight="1"/>
+    <row r="696" ht="17.25" customHeight="1"/>
+    <row r="697" ht="17.25" customHeight="1"/>
+    <row r="698" ht="17.25" customHeight="1"/>
+    <row r="699" ht="17.25" customHeight="1"/>
+    <row r="700" ht="17.25" customHeight="1"/>
+    <row r="701" ht="17.25" customHeight="1"/>
+    <row r="702" ht="17.25" customHeight="1"/>
+    <row r="703" ht="17.25" customHeight="1"/>
+    <row r="704" ht="17.25" customHeight="1"/>
+    <row r="705" ht="17.25" customHeight="1"/>
+    <row r="706" ht="17.25" customHeight="1"/>
+    <row r="707" ht="17.25" customHeight="1"/>
+    <row r="708" ht="17.25" customHeight="1"/>
+    <row r="709" ht="17.25" customHeight="1"/>
+    <row r="710" ht="17.25" customHeight="1"/>
+    <row r="711" ht="17.25" customHeight="1"/>
+    <row r="712" ht="17.25" customHeight="1"/>
+    <row r="713" ht="17.25" customHeight="1"/>
+    <row r="714" ht="17.25" customHeight="1"/>
+    <row r="715" ht="17.25" customHeight="1"/>
+    <row r="716" ht="17.25" customHeight="1"/>
+    <row r="717" ht="17.25" customHeight="1"/>
+    <row r="718" ht="17.25" customHeight="1"/>
+    <row r="719" ht="17.25" customHeight="1"/>
+    <row r="720" ht="17.25" customHeight="1"/>
+    <row r="721" ht="17.25" customHeight="1"/>
+    <row r="722" ht="17.25" customHeight="1"/>
+    <row r="723" ht="17.25" customHeight="1"/>
+    <row r="724" ht="17.25" customHeight="1"/>
+    <row r="725" ht="17.25" customHeight="1"/>
+    <row r="726" ht="17.25" customHeight="1"/>
+    <row r="727" ht="17.25" customHeight="1"/>
+    <row r="728" ht="17.25" customHeight="1"/>
+    <row r="729" ht="17.25" customHeight="1"/>
+    <row r="730" ht="17.25" customHeight="1"/>
+    <row r="731" ht="17.25" customHeight="1"/>
+    <row r="732" ht="17.25" customHeight="1"/>
+    <row r="733" ht="17.25" customHeight="1"/>
+    <row r="734" ht="17.25" customHeight="1"/>
+    <row r="735" ht="17.25" customHeight="1"/>
+    <row r="736" ht="17.25" customHeight="1"/>
+    <row r="737" ht="17.25" customHeight="1"/>
+    <row r="738" ht="17.25" customHeight="1"/>
+    <row r="739" ht="17.25" customHeight="1"/>
+    <row r="740" ht="17.25" customHeight="1"/>
+    <row r="741" ht="17.25" customHeight="1"/>
+    <row r="742" ht="17.25" customHeight="1"/>
+    <row r="743" ht="17.25" customHeight="1"/>
+    <row r="744" ht="17.25" customHeight="1"/>
+    <row r="745" ht="17.25" customHeight="1"/>
+    <row r="746" ht="17.25" customHeight="1"/>
+    <row r="747" ht="17.25" customHeight="1"/>
+    <row r="748" ht="17.25" customHeight="1"/>
+    <row r="749" ht="17.25" customHeight="1"/>
+    <row r="750" ht="17.25" customHeight="1"/>
+    <row r="751" ht="17.25" customHeight="1"/>
+    <row r="752" ht="17.25" customHeight="1"/>
+    <row r="753" ht="17.25" customHeight="1"/>
+    <row r="754" ht="17.25" customHeight="1"/>
+    <row r="755" ht="17.25" customHeight="1"/>
+    <row r="756" ht="17.25" customHeight="1"/>
+    <row r="757" ht="17.25" customHeight="1"/>
+    <row r="758" ht="17.25" customHeight="1"/>
+    <row r="759" ht="17.25" customHeight="1"/>
+    <row r="760" ht="17.25" customHeight="1"/>
+    <row r="761" ht="17.25" customHeight="1"/>
+    <row r="762" ht="17.25" customHeight="1"/>
+    <row r="763" ht="17.25" customHeight="1"/>
+    <row r="764" ht="17.25" customHeight="1"/>
+    <row r="765" ht="17.25" customHeight="1"/>
+    <row r="766" ht="17.25" customHeight="1"/>
+    <row r="767" ht="17.25" customHeight="1"/>
+    <row r="768" ht="17.25" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:AZ2" xr:uid="{8F16929E-2D58-43E9-9D74-4058F48FC83B}"/>
   <phoneticPr fontId="9" type="noConversion"/>
